--- a/sougei-gem/設定シート.xlsx
+++ b/sougei-gem/設定シート.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="①施設・車両設定" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="②利用者一覧" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_payload" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet name="①施設・車両設定" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="②利用者一覧" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="_payload" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -1307,7 +1307,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:AM4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>IyAtKi0gY29kaW5nOiB1dGYtOCAtKi0KIiIi6YCB6L+O44Gu6YWN6LuK44KS57WE44KA44K544Kv44Oq44OX44OI77yI6YCB6L+O44OK44OT44Go5ZCM44GY5omL6aCG77yJCgrkvb/jgYTmlrkKICDkuIvjga7jgIzlhaXlipvjgI3jgaDjgZHjgpLmm7jjgY3mj5vjgYjjgablrp/ooYzjgZnjgovjgILjg63jgrjjg4Pjgq/lgbTjga/jgYTjgZjjgonjgarjgYTjgIIKICDluqfmqJnjga8gKOe3r+W6piwg57WM5bqmKSDjga7poIbjgILnt6/luqbjgYwzNOOAnDQ144CB57WM5bqm44GMMTI544CcMTQ244Gu56+E5Zuy44CCCgrlh7rlipsKICDou4rjgZTjgajjga7pgIHov47ooajvvIjkuZfjgovpoIbjg7vliLDnnYDjg7vlh7rnmbrvvInjgIHmnKrlibLlvZPjgIHogbflk6Hjga7libLjgorlvZPjgabjgIIKIiIiCgppbXBvcnQgbWF0aCwgcmFuZG9tCgojIOOBk+OBruODleOCoeOCpOODq+OBrueJiOOAguabuOOBjeaPm+OBiOOBquOBhOOBk+OBqOOAggojIOWHuuWKm+OBrjHooYznm67jgavlh7rjgovjga7jgafjgIHjgaHjgoPjgpPjgajjgZPjga7jg5XjgqHjgqTjg6vjgYzlrp/ooYzjgZXjgozjgZ/jgYvnorroqo3jgafjgY3jgovjgIIKTE9HSUNfVkVSU0lPTiA9ICcyMDI2LTA5LTE1JwoKIyDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZAKIyDlhaXlipvjgIDjgZPjgZPjgaDjgZHmm7jjgY3mj5vjgYjjgosKIyDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZAKCkNPTkZJRyA9IHsKICAgICdtb2RlJzogICAgICfku4vorbcnLCAgICAgICAgICAgICAgIyAn5LuL6K23JyDjgYsgJ+aUvuODh+OCpCcKICAgICd0cmlwJzogICAgICfjgYrov47jgYgnLCAgICAgICAgICAgICMgJ+OBiui/juOBiCcg44GLICfjgYrpgIHjgoonCiAgICAjIGZhY2lsaXR5IOOBq+OBr+OAkOS6i+alreaJgOOBruS9j+aJgOOAkeOCkuWFpeOCjOOCi+OAguWun+a4rOihqChSRUFMKeOBruOCreODvOOBqOS4gOWtl+S4gOWPpeOBneOCjeOBiOOCi+OBk+OBqOOAggogICAgIyDmlr3oqK3lkI3jgpLlhaXjgozjgovjgajlrp/muKzooajjgpLlvJXjgZHjgarjgY/jgarjgorjgIHnsr7luqbjgYzokL3jgaHjgovjgIIKICAgICdmYWNpbGl0eSc6ICAgICAgJ+S4reWkrueUujEtMS0xJywKICAgICdmYWNpbGl0eV9uYW1lJzogJycsICAgICAgICAgICAgICMg6KGo56S655So44Gu5pa96Kit5ZCN77yI5Lu75oSP44CC56m644Gq44KJ5L2P5omA44KS6KGo56S677yJCiAgICAnZmFjX3Bvcyc6ICAoMzQuNzE4MCwgMTM2LjkxMDUpLCAjIOS6i+alreaJgOOBruW6p+aomQogICAgJ2RlcGFydCc6ICAgJzk6MDAnLCAgICAgICAgICAgICAgIyDkuIDmlonlh7rnmbrmmYLliLvvvIjku4vorbfvvIkKICAgICdhdXRvX2RlcGFydCc6IE5vbmUsICAgICAgICAgICAgICMgTm9uZe+8neaUvuODh+OCpOOBquOCieiHquWLleOAglRydWUvRmFsc2Xjgaflm7rlrprjgoLjgafjgY3jgosKICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICMg6Ieq5YuV44Gu44Go44GN44CB5LqL5qWt5omA44Gu5Ye655m65pmC5Yi744GvCiAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAjIOOAjOacgOWIneOBruOBiui/juOBiOaZguWIuyDiiJIg44Gd44GT44G+44Gn44Gu56e75YuV5pmC6ZaT44CN44Gn6YCG566X44GZ44KLCiAgICAnc3RvcCc6ICAgICAxMCwgICAgICAgICAgICAgICAgICAjIOS5l+mZjeOBq+OBi+OBi+OCi+aZgumWk++8iOWIhu+8iQogICAgJ3R1cm4nOiAgICAgNSwgICAgICAgICAgICAgICAgICAgIyAx5L6/4oaSMuS+v+OBruaKmOOCiui/lOOBl++8iOWIhu+8iQogICAgJ2ZhY3Rvcic6ICAgMy4wLCAgICAgICAgICAgICAgICAgIyDnm7Tnt5oxa23jgYLjgZ/jgorjga7liIbmlbDjgILjgYLjgajjgaflkIjjgo/jgZvjgosKICAgICd1c2VfcnVuMic6IFRydWUsICAgICAgICAgICAgICAgICMgMuS+v+OCkuS9v+OBhuOBiwogICAgJ3NlZWQnOiAgICAgMCwgICAgICAgICAgICAgICAgICAgIyDmr47lm57lkIzjgZjntZDmnpzjgavjgZnjgovjgZ/jgoHjga7nqK7jgILlpInjgYjjgarjgYQKfQoKIyDou4rkuKHjgIBjYXA95Yip55So6ICF5a6a5ZOhIC8gd2NfbWF4PeOBhuOBoei7iuOBhOOBmeWumuWToSAvIHdjX3NlYXRzPei7iuOBhOOBmTHlj7DjgYzkvb/jgYbluK3mlbAKIyAgICAgICB3YWxrZXJfbWF4PeatqeihjOWZqOOBruS4iumZkO+8iE5vbmXvvJ3liLbpmZDjgarjgZfvvIkgLyBoZWxwZXI95re75LmX5ZOh44GM5LmX44KM44KL44GLClZFSElDTEVTID0gWwogICAgeyduYW1lJzogJzHlj7fou4onLCAnY2FwJzogNiwgJ3djX21heCc6IDIsICd3Y19zZWF0cyc6IDIsICd3YWxrZXJfbWF4JzogMiwgICAgJ2hlbHBlcic6IFRydWV9LAogICAgeyduYW1lJzogJzLlj7fou4onLCAnY2FwJzogNCwgJ3djX21heCc6IDEsICd3Y19zZWF0cyc6IDIsICd3YWxrZXJfbWF4JzogMSwgICAgJ2hlbHBlcic6IFRydWV9LAogICAgeyduYW1lJzogJzPlj7fou4onLCAnY2FwJzogNywgJ3djX21heCc6IDAsICd3Y19zZWF0cyc6IDEsICd3YWxrZXJfbWF4JzogTm9uZSwgJ2hlbHBlcic6IEZhbHNlfSwKXQoKIyDliKnnlKjogIXjgIBtb2I9J3djJ++8iOi7iuOBhOOBme+8iS8nd2Fsa2VyJ++8iOatqeihjOWZqO+8iS8nJ++8iOOBquOBl++8iQojICAgICAgICAgdGFyZ2V0PeOBiui/juOBiOaZguWIu+OBruaMh+Wumu+8iCcn44Gq44KJ5oyH5a6a44Gq44GX77yJClVTRVJTID0gWwogICAgeyduYW1lJzogJ+mdkuacqCDkuIDpg44nLCAnYWRkcic6ICfmoZznlLoyLTQtMScsICAgJ3Bvcyc6ICgzNC43MjEzLCAxMzYuOTAyMSksICdtb2InOiAnd2MnLCAgICAgJ3RhcmdldCc6ICcnfSwKICAgIHsnbmFtZSc6ICfnn7PnlLAg6Iqx5a2QJywgJ2FkZHInOiAn5qGc55S6Mi00LTEnLCAgICdwb3MnOiAoMzQuNzIxMywgMTM2LjkwMjEpLCAnbW9iJzogJycsICAgICAgICd0YXJnZXQnOiAnJ30sCiAgICB7J25hbWUnOiAn5LiK5Y6fIOS4iemDjicsICdhZGRyJzogJ+ahnOeUujUtMicsICAgICAncG9zJzogKDM0LjcyNTUsIDEzNi44OTc3KSwgJ21vYic6ICd3YWxrZXInLCAndGFyZ2V0JzogJyd9LAogICAgeyduYW1lJzogJ+axn+WPoyDjgojjgZcnLCAnYWRkcic6ICfkuK3lpK7nlLozLTcnLCAgICdwb3MnOiAoMzQuNzE2NSwgMTM2LjkxNDIpLCAnbW9iJzogJycsICAgICAgICd0YXJnZXQnOiAnOTozMCd9LAogICAgeyduYW1lJzogJ+Wkp+ilvyDkupTpg44nLCAnYWRkcic6ICfmnbHnlLo0LTMnLCAgICAgJ3Bvcyc6ICgzNC43MDUxLCAxMzYuOTM4OCksICdtb2InOiAnd2MnLCAgICAgJ3RhcmdldCc6ICcnfSwKICAgIHsnbmFtZSc6ICfliqDol6Qg44OP44OrJywgJ2FkZHInOiAn6Iul6JGJ55S6MS0xMicsICAncG9zJzogKDM0LjczMDIsIDEzNi45MjEwKSwgJ21vYic6ICcnLCAgICAgICAndGFyZ2V0JzogJyd9LAogICAgeyduYW1lJzogJ+acqOS4iyDkuIPmtbcnLCAnYWRkcic6ICfoi6XokYnnlLoxLTE1JywgICdwb3MnOiAoMzQuNzMxMCwgMTM2LjkyMjUpLCAnbW9iJzogJ3dhbGtlcicsICd0YXJnZXQnOiAnJ30sCiAgICB7J25hbWUnOiAn54aK6LC3IOWFq+mHjScsICdhZGRyJzogJ+adseeUujQtMycsICAgICAncG9zJzogKDM0LjcwNTEsIDEzNi45Mzg4KSwgJ21vYic6ICcnLCAgICAgICAndGFyZ2V0JzogJyd9LAogICAgeyduYW1lJzogJ+Wwj+axoCDkuZ3luIInLCAnYWRkcic6ICfopb/nlLo2LTEnLCAgICAgJ3Bvcyc6ICgzNC43MTI4LCAxMzYuODg0MCksICdtb2InOiAnJywgICAgICAgJ3RhcmdldCc6ICcnfSwKICAgIHsnbmFtZSc6ICfkvZDol6Qg44Go44KBJywgJ2FkZHInOiAn6KW/55S6Ni04JywgICAgICdwb3MnOiAoMzQuNzE0MSwgMTM2Ljg4MjIpLCAnbW9iJzogJ3djJywgICAgICd0YXJnZXQnOiAnJ30sCl0KCiMg6IG35ZOh44CAcm9sZT0nZHJpdmVyJ++8iOmBi+i7ouaJi++8iS8naGVscGVyJ++8iOaUr+aPtOWToeODu+S7i+itt+iBt+WToe+8iQpTVEFGRiA9IFsKICAgIHsnbmFtZSc6ICflsbHnlLAg5aSq6YOOJywgICAncm9sZSc6ICdkcml2ZXInfSwKICAgIHsnbmFtZSc6ICfkvZDjgIXmnKgg5qyh6YOOJywgJ3JvbGUnOiAnZHJpdmVyJ30sCiAgICB7J25hbWUnOiAn5Lit5p2RIOS4ieS7oycsICAgJ3JvbGUnOiAnZHJpdmVyJ30sCiAgICB7J25hbWUnOiAn5bCP5p6XIOiJr+WtkCcsICAgJ3JvbGUnOiAnaGVscGVyJ30sCiAgICB7J25hbWUnOiAn5rih6L66IOe+juWSsicsICAgJ3JvbGUnOiAnaGVscGVyJ30sCl0KCiMg5LyR6LuK44O75qyg5bit44O75qyg5Yuk44CA5ZCN5YmN44KS44Gd44Gu44G+44G+5Lim44G544KLCk9GRl9WRUhJQ0xFUyA9IFtdCk9GRl9VU0VSUyAgICA9IFtdCk9GRl9TVEFGRiAgICA9IFtdCgojIOWun+a4rOOBruenu+WLleaZgumWk++8iOWIhu+8ieOAguOCueODl+ODrOODg+ODieOCt+ODvOODiOOBruOAjOKRoyDlrp/muKzmmYLplpPjgpLlj5bjgovjgI3jgafkvZzjgaPjgZ/ooajjgpLjgZPjgZPjgavosrzjgovjgIIKIyDjgq3jg7zjga8gKOWHuueZuuOBruS9j+aJgCwg5Yiw552A44Gu5L2P5omAKeOAguWQjOOBmOWMuumWk+OBr+W+gOW+qeOBqeOBoeOCieOBp+OCguWQjOOBmOWApOOCkuS9v+OBhuOAggojIOOBk+OBk+OBq+eEoeOBhOWMuumWk+OBoOOBkeOAgeebtOe3mui3nemboiDDlyBmYWN0b3Ig44Gn6KaL56mN44KC44KL44CCClJFQUwgPSB7CiAgICAjICgn5Lit5aSu55S6MS0xLTEnLCAn5qGc55S6Mi00LTEnKTogNCwKICAgICMgKCfmoZznlLoyLTQtMScsICAgJ+ahnOeUujUtMicpOiAgIDYsCn0KCiMg5L+C5pWw77yIZmFjdG9y77yJ44KS5ZCI44KP44Gb44KL44Gf44KB44Gu5a6f5ris44OH44O844K/CiMg5a6f6Zqb44Gr5L2V5YiG44GL44GL44KL44GL5YiG44GL44Gj44Gm44GE44KL5Yy66ZaT44KS5Lim44G544Gm44CB5pyA5b6M44GuIGNhbGlicmF0ZSgpIOOCkuacieWKueOBq+OBmeOCi+OBqAojIOOBiuOBmeOBmeOCgeOBriBmYWN0b3Ig44GM5Ye644KL44CCM+OAnDXljLrplpPjgYLjgozjgbDljYHliIbjgIIKQ0FMSUJSQVRJT04gPSBbCiAgICAjICjlh7rnmbrjga7luqfmqJksIOWIsOedgOOBruW6p+aomSwg5a6f6Zqb44Gr44GL44GL44KL5YiGKQogICAgIyAoKDM0LjcxODAsIDEzNi45MTA1KSwgKDM0LjcyMTMsIDEzNi45MDIxKSwgOSksCl0KCiMgMuS+v+OBq+WIhuOBkeOCi+WIpOaWreOBruOBl+OBjeOBhOWApO+8iOmAgei/juODiuODk+OBqOWQjOOBmOWApO+8iQpSVU4yX01JTl9TVE9QUyA9IDYgICAgIyDjgZPjgozmnKrmuoDjga7ou5LmlbDjgarjgonjgIHmmYLnn63nm67nmoTjgafjga/liIbjgZHjgarjgYQKUlVOMl9SRVFfR0FJTiAgPSAxMCAgICMg5bmz5Z2H44Gn44GT44KM5Lul5LiK5pep44GP44Gq44KL44GT44Go77yI5YiG77yJClJVTjJfTUFYX0xPU1MgID0gMTAgICAjIOacgOW+jOOBruaWueOBjOOBk+OCjOS7peS4iumBheOBj+OBquOCi+OBquOCieWIhuOBkeOBquOBhO+8iOWIhu+8iQoKIyDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZAKIyDjgZPjgZPjgYvjgonkuIvjga/jg63jgrjjg4Pjgq/jgILmm7jjgY3mj5vjgYjjgarjgYQKIyDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZAKCmRlZiB0b19tKHMpOgogICAgIiIiJzk6MzAnIOKGkiA1NzDjgILnqbrjgoTkuI3mraPjgarjgokgTm9uZSIiIgogICAgaWYgbm90IHM6IHJldHVybiBOb25lCiAgICB0cnk6CiAgICAgICAgaCwgbSA9IHN0cihzKS5zcGxpdCgnOicpCiAgICAgICAgcmV0dXJuIGludChoKSAqIDYwICsgaW50KG0pCiAgICBleGNlcHQgRXhjZXB0aW9uOgogICAgICAgIHJldHVybiBOb25lCgpkZWYgdG9faG0obSk6CiAgICAiIiI1NzAg4oaSICc5OjMwJyIiIgogICAgaWYgbSBpcyBOb25lOiByZXR1cm4gJycKICAgIG0gPSBpbnQocm91bmQobSkpCiAgICByZXR1cm4gJyVkOiUwMmQnICUgKG0gLy8gNjAsIG0gJSA2MCkKCmRlZiBoYXZlcnNpbmVfa20oYSwgYik6CiAgICAiIiIy54K56ZaT44Gu55u057ea6Led6Zui77yIa23vvIkiIiIKICAgIGlmIGEgaXMgTm9uZSBvciBiIGlzIE5vbmU6IHJldHVybiAwLjAKICAgIGxhdDEsIGxvbjEgPSBtYXRoLnJhZGlhbnMoYVswXSksIG1hdGgucmFkaWFucyhhWzFdKQogICAgbGF0MiwgbG9uMiA9IG1hdGgucmFkaWFucyhiWzBdKSwgbWF0aC5yYWRpYW5zKGJbMV0pCiAgICBkbGF0LCBkbG9uID0gbGF0MiAtIGxhdDEsIGxvbjIgLSBsb24xCiAgICBoID0gbWF0aC5zaW4oZGxhdC8yKSoqMiArIG1hdGguY29zKGxhdDEpKm1hdGguY29zKGxhdDIpKm1hdGguc2luKGRsb24vMikqKjIKICAgIHJldHVybiAyICogNjM3MS4wICogbWF0aC5hc2luKG1pbigxLjAsIG1hdGguc3FydChoKSkpCgojIOWun+a4rOOCkuS9v+OBiOOBn+WbnuaVsOOBqOOAgeebtOe3muOBp+imi+epjeOCguOBo+OBn+WbnuaVsO+8iOacgOW+jOOBq+WGheios+OCkuWHuuOBme+8iQpMRUdfU1RBVFMgPSB7J3JlYWwnOiAwLCAnZXN0JzogMH0KCmRlZiBsZWdtaW4oYSwgYiwgYWE9JycsIGFiPScnKToKICAgICIiIuenu+WLleaZgumWk++8iOWIhu+8ieOAggogICAgICAgYWEsIGFiIOOBq+S9j+aJgOOCkua4oeOBmeOBqOOAgeOBvuOBmuWun+a4rOihqCBSRUFMIOOCkuimi+OCi+OAggogICAgICAg54Sh44GR44KM44Gw55u057ea6Led6ZuiIMOXIGZhY3RvciDjgafopovnqY3jgoLjgovjgIIiIiIKICAgIGlmIGFhIGFuZCBhYiBhbmQgYWEgPT0gYWI6IHJldHVybiAwCiAgICBpZiBhYSBhbmQgYWI6CiAgICAgICAgdiA9IFJFQUwuZ2V0KChhYSwgYWIpKQogICAgICAgIGlmIHYgaXMgTm9uZTogdiA9IFJFQUwuZ2V0KChhYiwgYWEpKSAgICAgIyDpgIblkJHjgY3jgoLlkIzjgZjlgKTjgajjgZfjgabkvb/jgYYKICAgICAgICBpZiB2IGlzIG5vdCBOb25lOgogICAgICAgICAgICBMRUdfU1RBVFNbJ3JlYWwnXSArPSAxCiAgICAgICAgICAgIHJldHVybiBtYXgoMCwgaW50KHJvdW5kKHYpKSkKICAgIGlmIGEgaXMgTm9uZSBvciBiIGlzIE5vbmU6IHJldHVybiAwCiAgICBpZiBhID09IGI6IHJldHVybiAwCiAgICBMRUdfU1RBVFNbJ2VzdCddICs9IDEKICAgIHJldHVybiBtYXgoMSwgaW50KHJvdW5kKGhhdmVyc2luZV9rbShhLCBiKSAqIENPTkZJR1snZmFjdG9yJ10pKSkKCmRlZiB3YWxrZXJfbWF4KHYpOgogICAgdyA9IHYuZ2V0KCd3YWxrZXJfbWF4JykKICAgIHJldHVybiA5OSBpZiB3IGlzIE5vbmUgZWxzZSBpbnQodykKCmRlZiBjYXBfYXQodiwgd2MpOgogICAgIiIi6LuK44GE44GZd2Plj7DjgpLovInjgZvjgZ/jgajjgY3jgavkuZfjgozjgovkurrmlbAiIiIKICAgIHJldHVybiBpbnQodlsnY2FwJ10pIC0gKGludCh2LmdldCgnd2Nfc2VhdHMnLCAxKSkgLSAxKSAqIHdjCgpkZWYgY2FuX2ZpdCh2LCBsb2FkLCBncm91cCk6CiAgICAiIiJsb2FkPSjkurrmlbAsIOi7iuOBhOOBmSwg5q2p6KGM5ZmoKSDjga7ou4rjgasgZ3JvdXAg44KS6Laz44Gb44KL44GLIiIiCiAgICBuLCB3Yywgd2sgPSBsb2FkCiAgICBmb3IgYyBpbiBncm91cDoKICAgICAgICBpZiBjWydtb2InXSA9PSAnd2MnOiAgICAgICB3YyArPSAxCiAgICAgICAgZWxpZiBjWydtb2InXSA9PSAnd2Fsa2VyJzogd2sgKz0gMQogICAgICAgIG4gKz0gMQogICAgaWYgd2MgPiBpbnQodi5nZXQoJ3djX21heCcsIDApKTogcmV0dXJuIEZhbHNlCiAgICBpZiB3ayA+IHdhbGtlcl9tYXgodik6ICAgICAgICAgICByZXR1cm4gRmFsc2UKICAgIGxpbSA9IGNhcF9hdCh2LCB3YykKICAgIHJldHVybiBsaW0gPiAwIGFuZCBuIDw9IGxpbQoKZGVmIGFkZF9sb2FkKGxvYWQsIGdyb3VwKToKICAgIG4sIHdjLCB3ayA9IGxvYWQKICAgIGZvciBjIGluIGdyb3VwOgogICAgICAgIGlmIGNbJ21vYiddID09ICd3Yyc6ICAgICAgIHdjICs9IDEKICAgICAgICBlbGlmIGNbJ21vYiddID09ICd3YWxrZXInOiB3ayArPSAxCiAgICAgICAgbiArPSAxCiAgICByZXR1cm4gKG4sIHdjLCB3aykKCmRlZiBmaXRfY291bnQodiwgdXNlcnMpOgogICAgIiIi5YWI6aCt44GL44KJ6aCG44Gr44CB5L2V5Lq644G+44Gn5LmX44KM44KL44GLIiIiCiAgICBsb2FkID0gKDAsIDAsIDApCiAgICBuID0gMAogICAgZm9yIGMgaW4gdXNlcnM6CiAgICAgICAgaWYgbm90IGNhbl9maXQodiwgbG9hZCwgW2NdKTogYnJlYWsKICAgICAgICBsb2FkID0gYWRkX2xvYWQobG9hZCwgW2NdKTsgbiArPSAxCiAgICByZXR1cm4gbgoKZGVmIHJ1bnNfYWxsb3dlZCgpOgogICAgIiIiMeWPsOOBjOS9leS+v+OBvuOBp+i1sOOCjOOCi+OBiyIiIgogICAgcmV0dXJuIDIgaWYgKENPTkZJR1sndXNlX3J1bjInXSBhbmQgQ09ORklHWydtb2RlJ10gPT0gJ+S7i+ittycpIGVsc2UgMQoKZGVmIGZpdHNfaW5fcnVucyh2LCB1c2VycywgcnVucyk6CiAgICAiIiJ1c2VycyDjgpIgcnVucyDkvr/jgb7jgafjgavlj47jgoHjgonjgozjgovjgYvvvIjpoIbnlarjganjgYrjgorjgavoqbDjgoHjgabjgYTjgY/vvIkiIiIKICAgIHJlc3QgPSBsaXN0KHVzZXJzKQogICAgZm9yIF8gaW4gcmFuZ2UocnVucyk6CiAgICAgICAgaWYgbm90IHJlc3Q6IHJldHVybiBUcnVlCiAgICAgICAgayA9IGZpdF9jb3VudCh2LCByZXN0KQogICAgICAgIGlmIGsgPT0gMDogcmV0dXJuIEZhbHNlCiAgICAgICAgcmVzdCA9IHJlc3RbazpdCiAgICByZXR1cm4gbm90IHJlc3QKCmRlZiB3aHlfbm90KHYsIGdyb3VwKToKICAgICIiIuS5l+OCjOOBquOBhOeQhueUsSIiIgogICAgd2MgPSBzdW0oMSBmb3IgYyBpbiBncm91cCBpZiBjWydtb2InXSA9PSAnd2MnKQogICAgd2sgPSBzdW0oMSBmb3IgYyBpbiBncm91cCBpZiBjWydtb2InXSA9PSAnd2Fsa2VyJykKICAgIGlmIHdjIGFuZCBpbnQodi5nZXQoJ3djX21heCcsIDApKSA9PSAwOiByZXR1cm4gJ+i7iuOBhOOBmeS4jeWPrycKICAgIGlmIHdjID4gaW50KHYuZ2V0KCd3Y19tYXgnLCAwKSk6ICAgICAgICByZXR1cm4gJ+i7iuOBhOOBmeWumuWToScKICAgIGlmIHdrID4gd2Fsa2VyX21heCh2KTogICAgICAgICAgICAgICAgICByZXR1cm4gJ+atqeihjOWZqOOBruS4iumZkCcKICAgIHJldHVybiAn5a6a5ZOhJwoKCiMg4pSA4pSAIOaJi+mghjHjgIDjgb7jgajjgb7jgorjgpLkvZzjgovvvIjkvY/miYDvvIvjgYrov47jgYjmmYLliLvjgYzlkIzjgZjkurrjga/lkIzjgZjou4rjga7pgKPntprjgZfjgZ/poIbnlarvvInilIDilIAKZGVmIG1ha2VfZ3JvdXBzKHVzZXJzKToKICAgIGJhZyA9IHt9CiAgICBmb3IgYyBpbiB1c2VyczoKICAgICAgICBrID0gKGNbJ2FkZHInXSwgY1sndGFyZ2V0J10pCiAgICAgICAgYmFnLnNldGRlZmF1bHQoaywgW10pLmFwcGVuZChjKQogICAgZ3MgPSBsaXN0KGJhZy52YWx1ZXMoKSkKICAgICMg44GK6L+O44GI5pmC5Yi744Gu5pep44GE6aCG44CC5oyH5a6a44Gq44GX44Gv5pyA5b6MCiAgICBncy5zb3J0KGtleT1sYW1iZGEgZzogKHRvX20oZ1swXVsndGFyZ2V0J10pIGlmIHRvX20oZ1swXVsndGFyZ2V0J10pIGlzIG5vdCBOb25lIGVsc2UgOTkqNjApKQogICAgcmV0dXJuIGdzCgoKIyDilIDilIAg5omL6aCGM+OAgOi7iuWGheOBrumghueVqu+8iOacgOi/keWCjeOBp+OBvuOCj+OCiuOAgeaMh+WumuaZguWIu++8j+WIsOedgOimi+i+vOOBv+OBp+S4puOBueabv+OBiO+8ieKUgOKUgApkZWYgb3JkZXJfc3RvcHMoZ3JvdXBfaWR4cywgZ3JvdXBzLCBkZXBhcnRfbWluKToKICAgIGlmIGxlbihncm91cF9pZHhzKSA8PSAxOiByZXR1cm4gbGlzdChncm91cF9pZHhzKQogICAgaXRlbXMgPSBbeydwb3MnOiBncm91cHNbZ2ldWzBdWydwb3MnXSwKICAgICAgICAgICAgICAnYWRkcic6IGdyb3Vwc1tnaV1bMF0uZ2V0KCdhZGRyJywgJycpLAogICAgICAgICAgICAgICd0YXJnZXQnOiBuZXh0KChjWyd0YXJnZXQnXSBmb3IgYyBpbiBncm91cHNbZ2ldIGlmIGNbJ3RhcmdldCddKSwgJycpfQogICAgICAgICAgICAgZm9yIGdpIGluIGdyb3VwX2lkeHNdCgogICAgIyDikaAg5pyA6L+R5YKN5rOV44Gn5LiA5ZGo44Gu6aCG55Wq44KS5L2c44KLCiAgICByZXN0LCBubiA9IGxpc3QocmFuZ2UobGVuKGl0ZW1zKSkpLCBbXQogICAgY3VyLCBjdXJfYSA9IENPTkZJR1snZmFjX3BvcyddLCBDT05GSUdbJ2ZhY2lsaXR5J10KICAgIHdoaWxlIHJlc3Q6CiAgICAgICAgYmksIGJtID0gMCwgZmxvYXQoJ2luZicpCiAgICAgICAgZm9yIGssIGlkeCBpbiBlbnVtZXJhdGUocmVzdCk6CiAgICAgICAgICAgIG0gPSBsZWdtaW4oY3VyLCBpdGVtc1tpZHhdWydwb3MnXSwgY3VyX2EsIGl0ZW1zW2lkeF1bJ2FkZHInXSkKICAgICAgICAgICAgaWYgbSA8IGJtOiBibSwgYmkgPSBtLCBrCiAgICAgICAgcGljayA9IHJlc3QucG9wKGJpKTsgbm4uYXBwZW5kKHBpY2spCiAgICAgICAgY3VyLCBjdXJfYSA9IGl0ZW1zW3BpY2tdWydwb3MnXSwgaXRlbXNbcGlja11bJ2FkZHInXQoKICAgICMg4pGhIOOBneOBrumghuOBp+WbnuOBo+OBn+OBqOOBjeOBruWIsOedgOimi+i+vOOBvwogICAgZXRhLCB0ID0ge30sIGRlcGFydF9taW4KICAgIHByZXYsIHByZXZfYSA9IENPTkZJR1snZmFjX3BvcyddLCBDT05GSUdbJ2ZhY2lsaXR5J10KICAgIGZvciBpIGluIG5uOgogICAgICAgIHQgKz0gbGVnbWluKHByZXYsIGl0ZW1zW2ldWydwb3MnXSwgcHJldl9hLCBpdGVtc1tpXVsnYWRkciddKQogICAgICAgIGV0YVtpXSA9IHQKICAgICAgICB0ICs9IENPTkZJR1snc3RvcCddCiAgICAgICAgcHJldiwgcHJldl9hID0gaXRlbXNbaV1bJ3BvcyddLCBpdGVtc1tpXVsnYWRkciddCgogICAgIyDikaIg5oyH5a6a5pmC5Yi7</t>
+          <t>IyAtKi0gY29kaW5nOiB1dGYtOCAtKi0KIiIi6YCB6L+O44Gu6YWN6LuK44KS57WE44KA44K544Kv44Oq44OX44OI77yI6YCB6L+O44OK44OT44Go5ZCM44GY5omL6aCG77yJCgrkvb/jgYTmlrkKICDkuIvjga7jgIzlhaXlipvjgI3jgaDjgZHjgpLmm7jjgY3mj5vjgYjjgablrp/ooYzjgZnjgovjgILjg63jgrjjg4Pjgq/lgbTjga/jgYTjgZjjgonjgarjgYTjgIIKICDluqfmqJnjga8gKOe3r+W6piwg57WM5bqmKSDjga7poIbjgILnt6/luqbjgYwzNOOAnDQ144CB57WM5bqm44GMMTI544CcMTQ244Gu56+E5Zuy44CCCgrlh7rlipsKICDou4rjgZTjgajjga7pgIHov47ooajvvIjkuZfjgovpoIbjg7vliLDnnYDjg7vlh7rnmbrvvInjgIHmnKrlibLlvZPjgIHogbflk6Hjga7libLjgorlvZPjgabjgIIKIiIiCgppbXBvcnQgbWF0aCwgcmFuZG9tCgojIOOBk+OBruODleOCoeOCpOODq+OBrueJiOOAguabuOOBjeaPm+OBiOOBquOBhOOBk+OBqOOAggojIOWHuuWKm+OBrjHooYznm67jgavlh7rjgovjga7jgafjgIHjgaHjgoPjgpPjgajjgZPjga7jg5XjgqHjgqTjg6vjgYzlrp/ooYzjgZXjgozjgZ/jgYvnorroqo3jgafjgY3jgovjgIIKTE9HSUNfVkVSU0lPTiA9ICcyMDI2LTA5LTI0JwoKIyDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZAKIyDlhaXlipvjgIDjgZPjgZPjgaDjgZHmm7jjgY3mj5vjgYjjgosKIyDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZAKCkNPTkZJRyA9IHsKICAgICdtb2RlJzogICAgICfku4vorbcnLCAgICAgICAgICAgICAgIyAn5LuL6K23JyDjgYsgJ+aUvuODh+OCpCcKICAgICd0cmlwJzogICAgICfjgYrov47jgYgnLCAgICAgICAgICAgICMgJ+OBiui/juOBiCcg44GLICfjgYrpgIHjgoonCiAgICAjIGZhY2lsaXR5IOOBq+OBr+OAkOS6i+alreaJgOOBruS9j+aJgOOAkeOCkuWFpeOCjOOCi+OAguWun+a4rOihqChSRUFMKeOBruOCreODvOOBqOS4gOWtl+S4gOWPpeOBneOCjeOBiOOCi+OBk+OBqOOAggogICAgIyDmlr3oqK3lkI3jgpLlhaXjgozjgovjgajlrp/muKzooajjgpLlvJXjgZHjgarjgY/jgarjgorjgIHnsr7luqbjgYzokL3jgaHjgovjgIIKICAgICdmYWNpbGl0eSc6ICAgICAgJ+S4reWkrueUujEtMS0xJywKICAgICdmYWNpbGl0eV9uYW1lJzogJycsICAgICAgICAgICAgICMg6KGo56S655So44Gu5pa96Kit5ZCN77yI5Lu75oSP44CC56m644Gq44KJ5L2P5omA44KS6KGo56S677yJCiAgICAnZmFjX3Bvcyc6ICAoMzQuNzE4MCwgMTM2LjkxMDUpLCAjIOS6i+alreaJgOOBruW6p+aomQogICAgJ2RlcGFydCc6ICAgJzk6MDAnLCAgICAgICAgICAgICAgIyDkuIDmlonlh7rnmbrmmYLliLvvvIjku4vorbfvvIkKICAgICdhdXRvX2RlcGFydCc6IE5vbmUsICAgICAgICAgICAgICMgTm9uZe+8neaUvuODh+OCpOOBquOCieiHquWLleOAglRydWUvRmFsc2Xjgaflm7rlrprjgoLjgafjgY3jgosKICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICMg6Ieq5YuV44Gu44Go44GN44CB5LqL5qWt5omA44Gu5Ye655m65pmC5Yi744GvCiAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAjIOOAjOacgOWIneOBruOBiui/juOBiOaZguWIuyDiiJIg44Gd44GT44G+44Gn44Gu56e75YuV5pmC6ZaT44CN44Gn6YCG566X44GZ44KLCiAgICAnc3RvcCc6ICAgICAxMCwgICAgICAgICAgICAgICAgICAjIOS5l+mZjeOBq+OBi+OBi+OCi+aZgumWk++8iOWIhu+8iQogICAgJ3R1cm4nOiAgICAgNSwgICAgICAgICAgICAgICAgICAgIyAx5L6/4oaSMuS+v+OBruaKmOOCiui/lOOBl++8iOWIhu+8iQogICAgJ2ZhY3Rvcic6ICAgMy4wLCAgICAgICAgICAgICAgICAgIyDnm7Tnt5oxa23jgYLjgZ/jgorjga7liIbmlbDjgILjgYLjgajjgaflkIjjgo/jgZvjgosKICAgICd1c2VfcnVuMic6IFRydWUsICAgICAgICAgICAgICAgICMgMuS+v+OCkuS9v+OBhuOBiwogICAgJ3NlZWQnOiAgICAgMCwgICAgICAgICAgICAgICAgICAgIyDmr47lm57lkIzjgZjntZDmnpzjgavjgZnjgovjgZ/jgoHjga7nqK7jgILlpInjgYjjgarjgYQKfQoKIyDou4rkuKHjgIBjYXA95Yip55So6ICF5a6a5ZOhIC8gd2NfbWF4PeOBhuOBoei7iuOBhOOBmeWumuWToSAvIHdjX3NlYXRzPei7iuOBhOOBmTHlj7DjgYzkvb/jgYbluK3mlbAKIyAgICAgICB3YWxrZXJfbWF4PeatqeihjOWZqOOBruS4iumZkO+8iE5vbmXvvJ3liLbpmZDjgarjgZfvvIkKVkVISUNMRVMgPSBbCiAgICB7J25hbWUnOiAnMeWPt+i7iicsICdjYXAnOiA2LCAnd2NfbWF4JzogMiwgJ3djX3NlYXRzJzogMiwgJ3dhbGtlcl9tYXgnOiAyfSwKICAgIHsnbmFtZSc6ICcy5Y+36LuKJywgJ2NhcCc6IDQsICd3Y19tYXgnOiAxLCAnd2Nfc2VhdHMnOiAyLCAnd2Fsa2VyX21heCc6IDF9LAogICAgeyduYW1lJzogJzPlj7fou4onLCAnY2FwJzogNywgJ3djX21heCc6IDAsICd3Y19zZWF0cyc6IDEsICd3YWxrZXJfbWF4JzogTm9uZX0sCl0KCiMg5Yip55So6ICF44CAbW9iPSd3YyfvvIjou4rjgYTjgZnvvIkvJ3dhbGtlcifvvIjmranooYzlmajvvIkvJyfvvIjjgarjgZfvvIkKIyAgICAgICAgIHRhcmdldD3jgYrov47jgYjmmYLliLvjga7mjIflrprvvIgnJ+OBquOCieaMh+WumuOBquOBl++8iQpVU0VSUyA9IFsKICAgIHsnbmFtZSc6ICfpnZLmnKgg5LiA6YOOJywgJ2FkZHInOiAn5qGc55S6Mi00LTEnLCAgICdwb3MnOiAoMzQuNzIxMywgMTM2LjkwMjEpLCAnbW9iJzogJ3djJywgICAgICd0YXJnZXQnOiAnJ30sCiAgICB7J25hbWUnOiAn55+z55SwIOiKseWtkCcsICdhZGRyJzogJ+ahnOeUujItNC0xJywgICAncG9zJzogKDM0LjcyMTMsIDEzNi45MDIxKSwgJ21vYic6ICcnLCAgICAgICAndGFyZ2V0JzogJyd9LAogICAgeyduYW1lJzogJ+S4iuWOnyDkuInpg44nLCAnYWRkcic6ICfmoZznlLo1LTInLCAgICAgJ3Bvcyc6ICgzNC43MjU1LCAxMzYuODk3NyksICdtb2InOiAnd2Fsa2VyJywgJ3RhcmdldCc6ICcnfSwKICAgIHsnbmFtZSc6ICfmsZ/lj6Mg44KI44GXJywgJ2FkZHInOiAn5Lit5aSu55S6My03JywgICAncG9zJzogKDM0LjcxNjUsIDEzNi45MTQyKSwgJ21vYic6ICcnLCAgICAgICAndGFyZ2V0JzogJzk6MzAnfSwKICAgIHsnbmFtZSc6ICflpKfopb8g5LqU6YOOJywgJ2FkZHInOiAn5p2x55S6NC0zJywgICAgICdwb3MnOiAoMzQuNzA1MSwgMTM2LjkzODgpLCAnbW9iJzogJ3djJywgICAgICd0YXJnZXQnOiAnJ30sCiAgICB7J25hbWUnOiAn5Yqg6JekIOODj+ODqycsICdhZGRyJzogJ+iLpeiRieeUujEtMTInLCAgJ3Bvcyc6ICgzNC43MzAyLCAxMzYuOTIxMCksICdtb2InOiAnJywgICAgICAgJ3RhcmdldCc6ICcnfSwKICAgIHsnbmFtZSc6ICfmnKjkuIsg5LiD5rW3JywgJ2FkZHInOiAn6Iul6JGJ55S6MS0xNScsICAncG9zJzogKDM0LjczMTAsIDEzNi45MjI1KSwgJ21vYic6ICd3YWxrZXInLCAndGFyZ2V0JzogJyd9LAogICAgeyduYW1lJzogJ+eGiuiwtyDlhavph40nLCAnYWRkcic6ICfmnbHnlLo0LTMnLCAgICAgJ3Bvcyc6ICgzNC43MDUxLCAxMzYuOTM4OCksICdtb2InOiAnJywgICAgICAgJ3RhcmdldCc6ICcnfSwKICAgIHsnbmFtZSc6ICflsI/msaAg5Lmd5biCJywgJ2FkZHInOiAn6KW/55S6Ni0xJywgICAgICdwb3MnOiAoMzQuNzEyOCwgMTM2Ljg4NDApLCAnbW9iJzogJycsICAgICAgICd0YXJnZXQnOiAnJ30sCiAgICB7J25hbWUnOiAn5L2Q6JekIOOBqOOCgScsICdhZGRyJzogJ+ilv+eUujYtOCcsICAgICAncG9zJzogKDM0LjcxNDEsIDEzNi44ODIyKSwgJ21vYic6ICd3YycsICAgICAndGFyZ2V0JzogJyd9LApdCgojIOS8kei7iuODu+asoOW4reOAgOWQjeWJjeOCkuOBneOBruOBvuOBvuS4puOBueOCiwpPRkZfVkVISUNMRVMgPSBbXQpPRkZfVVNFUlMgICAgPSBbXQoKIyDlrp/muKzjga7np7vli5XmmYLplpPvvIjliIbvvInjgILjgrnjg5fjg6zjg4Pjg4njgrfjg7zjg4jjga7jgIzikaMg5a6f5ris5pmC6ZaT44KS5Y+W44KL44CN44Gn5L2c44Gj44Gf6KGo44KS44GT44GT44Gr6LK844KL44CCCiMg44Kt44O844GvICjlh7rnmbrjga7kvY/miYAsIOWIsOedgOOBruS9j+aJgCnjgILlkIzjgZjljLrplpPjga/lvoDlvqnjganjgaHjgonjgafjgoLlkIzjgZjlgKTjgpLkvb/jgYbjgIIKIyDjgZPjgZPjgavnhKHjgYTljLrplpPjgaDjgZHjgIHnm7Tnt5rot53pm6Igw5cgZmFjdG9yIOOBp+imi+epjeOCguOCi+OAggpSRUFMID0gewogICAgIyAoJ+S4reWkrueUujEtMS0xJywgJ+ahnOeUujItNC0xJyk6IDQsCiAgICAjICgn5qGc55S6Mi00LTEnLCAgICfmoZznlLo1LTInKTogICA2LAp9CgojIOS/guaVsO+8iGZhY3Rvcu+8ieOCkuWQiOOCj+OBm+OCi+OBn+OCgeOBruWun+a4rOODh+ODvOOCvwojIOWun+mam+OBq+S9leWIhuOBi+OBi+OCi+OBi+WIhuOBi+OBo+OBpuOBhOOCi+WMuumWk+OCkuS4puOBueOBpuOAgeacgOW+jOOBriBjYWxpYnJhdGUoKSDjgpLmnInlirnjgavjgZnjgovjgagKIyDjgYrjgZnjgZnjgoHjga4gZmFjdG9yIOOBjOWHuuOCi+OAgjPjgJw15Yy66ZaT44GC44KM44Gw5Y2B5YiG44CCCkNBTElCUkFUSU9OID0gWwogICAgIyAo5Ye655m644Gu5bqn5qiZLCDliLDnnYDjga7luqfmqJksIOWun+mam+OBq+OBi+OBi+OCi+WIhikKICAgICMgKCgzNC43MTgwLCAxMzYuOTEwNSksICgzNC43MjEzLCAxMzYuOTAyMSksIDkpLApdCgojIDLkvr/jgavliIbjgZHjgovliKTmlq3jga7jgZfjgY3jgYTlgKTvvIjpgIHov47jg4rjg5PjgajlkIzjgZjlgKTvvIkKUlVOMl9NSU5fU1RPUFMgPSA2ICAgICMg44GT44KM5pyq5rqA44Gu6LuS5pWw44Gq44KJ44CB5pmC55+t55uu55qE44Gn44Gv5YiG44GR44Gq44GEClJVTjJfUkVRX0dBSU4gID0gMTAgICAjIOW5s+Wdh+OBp+OBk+OCjOS7peS4iuaXqeOBj+OBquOCi+OBk+OBqO+8iOWIhu+8iQpSVU4yX01BWF9MT1NTICA9IDEwICAgIyDmnIDlvozjga7mlrnjgYzjgZPjgozku6XkuIrpgYXjgY/jgarjgovjgarjgonliIbjgZHjgarjgYTvvIjliIbvvIkKCiMg4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQCiMg44GT44GT44GL44KJ5LiL44Gv44Ot44K444OD44Kv44CC5pu444GN5o+b44GI44Gq44GECiMg4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQCgpkZWYgdG9fbShzKToKICAgICIiIic5OjMwJyDihpIgNTcw44CC56m644KE5LiN5q2j44Gq44KJIE5vbmUiIiIKICAgIGlmIG5vdCBzOiByZXR1cm4gTm9uZQogICAgdHJ5OgogICAgICAgIGgsIG0gPSBzdHIocykuc3BsaXQoJzonKQogICAgICAgIHJldHVybiBpbnQoaCkgKiA2MCArIGludChtKQogICAgZXhjZXB0IEV4Y2VwdGlvbjoKICAgICAgICByZXR1cm4gTm9uZQoKZGVmIHRvX2htKG0pOgogICAgIiIiNTcwIOKGkiAnOTozMCciIiIKICAgIGlmIG0gaXMgTm9uZTogcmV0dXJuICcnCiAgICBtID0gaW50KHJvdW5kKG0pKQogICAgcmV0dXJuICclZDolMDJkJyAlIChtIC8vIDYwLCBtICUgNjApCgpkZWYgaGF2ZXJzaW5lX2ttKGEsIGIpOgogICAgIiIiMueCuemWk+OBruebtOe3mui3nembou+8iGtt77yJIiIiCiAgICBpZiBhIGlzIE5vbmUgb3IgYiBpcyBOb25lOiByZXR1cm4gMC4wCiAgICBsYXQxLCBsb24xID0gbWF0aC5yYWRpYW5zKGFbMF0pLCBtYXRoLnJhZGlhbnMoYVsxXSkKICAgIGxhdDIsIGxvbjIgPSBtYXRoLnJhZGlhbnMoYlswXSksIG1hdGgucmFkaWFucyhiWzFdKQogICAgZGxhdCwgZGxvbiA9IGxhdDIgLSBsYXQxLCBsb24yIC0gbG9uMQogICAgaCA9IG1hdGguc2luKGRsYXQvMikqKjIgKyBtYXRoLmNvcyhsYXQxKSptYXRoLmNvcyhsYXQyKSptYXRoLnNpbihkbG9uLzIpKioyCiAgICByZXR1cm4gMiAqIDYzNzEuMCAqIG1hdGguYXNpbihtaW4oMS4wLCBtYXRoLnNxcnQoaCkpKQoKIyDlrp/muKzjgpLkvb/jgYjjgZ/lm57mlbDjgajjgIHnm7Tnt5rjgafopovnqY3jgoLjgaPjgZ/lm57mlbDvvIjmnIDlvozjgavlhoXoqLPjgpLlh7rjgZnvvIkKTEVHX1NUQVRTID0geydyZWFsJzogMCwgJ2VzdCc6IDB9CgpkZWYgbGVnbWluKGEsIGIsIGFhPScnLCBhYj0nJyk6CiAgICAiIiLnp7vli5XmmYLplpPvvIjliIbvvInjgIIKICAgICAgIGFhLCBhYiDjgavkvY/miYDjgpLmuKHjgZnjgajjgIHjgb7jgZrlrp/muKzooaggUkVBTCDjgpLopovjgovjgIIKICAgICAgIOeEoeOBkeOCjOOBsOebtOe3mui3nemboiDDlyBmYWN0b3Ig44Gn6KaL56mN44KC44KL44CCIiIiCiAgICBpZiBhYSBhbmQgYWIgYW5kIGFhID09IGFiOiByZXR1cm4gMAogICAgaWYgYWEgYW5kIGFiOgogICAgICAgIHYgPSBSRUFMLmdldCgoYWEsIGFiKSkKICAgICAgICBpZiB2IGlzIE5vbmU6IHYgPSBSRUFMLmdldCgoYWIsIGFhKSkgICAgICMg6YCG5ZCR44GN44KC5ZCM44GY5YCk44Go44GX44Gm5L2/44GGCiAgICAgICAgaWYgdiBpcyBub3QgTm9uZToKICAgICAgICAgICAgTEVHX1NUQVRTWydyZWFsJ10gKz0gMQogICAgICAgICAgICByZXR1cm4gbWF4KDAsIGludChyb3VuZCh2KSkpCiAgICBpZiBhIGlzIE5vbmUgb3IgYiBpcyBOb25lOiByZXR1cm4gMAogICAgaWYgYSA9PSBiOiByZXR1cm4gMAogICAgTEVHX1NUQVRTWydlc3QnXSArPSAxCiAgICByZXR1cm4gbWF4KDEsIGludChyb3VuZChoYXZlcnNpbmVfa20oYSwgYikgKiBDT05GSUdbJ2ZhY3RvciddKSkpCgpkZWYgd2Fsa2VyX21heCh2KToKICAgIHcgPSB2LmdldCgnd2Fsa2VyX21heCcpCiAgICByZXR1cm4gOTkgaWYgdyBpcyBOb25lIGVsc2UgaW50KHcpCgpkZWYgY2FwX2F0KHYsIHdjKToKICAgICIiIui7iuOBhOOBmXdj5Y+w44KS6LyJ44Gb44Gf44Go44GN44Gr5LmX44KM44KL5Lq65pWwIiIiCiAgICByZXR1cm4gaW50KHZbJ2NhcCddKSAtIChpbnQodi5nZXQoJ3djX3NlYXRzJywgMSkpIC0gMSkgKiB3YwoKZGVmIGNhbl9maXQodiwgbG9hZCwgZ3JvdXApOgogICAgIiIibG9hZD0o5Lq65pWwLCDou4rjgYTjgZksIOatqeihjOWZqCkg44Gu6LuK44GrIGdyb3VwIOOCkui2s+OBm+OCi+OBiyIiIgogICAgbiwgd2MsIHdrID0gbG9hZAogICAgZm9yIGMgaW4gZ3JvdXA6CiAgICAgICAgaWYgY1snbW9iJ10gPT0gJ3djJzogICAgICAgd2MgKz0gMQogICAgICAgIGVsaWYgY1snbW9iJ10gPT0gJ3dhbGtlcic6IHdrICs9IDEKICAgICAgICBuICs9IDEKICAgIGlmIHdjID4gaW50KHYuZ2V0KCd3Y19tYXgnLCAwKSk6IHJldHVybiBGYWxzZQogICAgaWYgd2sgPiB3YWxrZXJfbWF4KHYpOiAgICAgICAgICAgcmV0dXJuIEZhbHNlCiAgICBsaW0gPSBjYXBfYXQodiwgd2MpCiAgICByZXR1cm4gbGltID4gMCBhbmQgbiA8PSBsaW0KCmRlZiBhZGRfbG9hZChsb2FkLCBncm91cCk6CiAgICBuLCB3Yywgd2sgPSBsb2FkCiAgICBmb3IgYyBpbiBncm91cDoKICAgICAgICBpZiBjWydtb2InXSA9PSAnd2MnOiAgICAgICB3YyArPSAxCiAgICAgICAgZWxpZiBjWydtb2InXSA9PSAnd2Fsa2VyJzogd2sgKz0gMQogICAgICAgIG4gKz0gMQogICAgcmV0dXJuIChuLCB3Yywgd2spCgpkZWYgZml0X2NvdW50KHYsIHVzZXJzKToKICAgICIiIuWFiOmgreOBi+OCiemghuOBq+OAgeS9leS6uuOBvuOBp+S5l+OCjOOCi+OBiyIiIgogICAgbG9hZCA9ICgwLCAwLCAwKQogICAgbiA9IDAKICAgIGZvciBjIGluIHVzZXJzOgogICAgICAgIGlmIG5vdCBjYW5fZml0KHYsIGxvYWQsIFtjXSk6IGJyZWFrCiAgICAgICAgbG9hZCA9IGFkZF9sb2FkKGxvYWQsIFtjXSk7IG4gKz0gMQogICAgcmV0dXJuIG4KCmRlZiBydW5zX2FsbG93ZWQoKToKICAgICIiIjHlj7DjgYzkvZXkvr/jgb7jgafotbDjgozjgovjgYsiIiIKICAgIHJldHVybiAyIGlmIChDT05GSUdbJ3VzZV9ydW4yJ10gYW5kIENPTkZJR1snbW9kZSddID09ICfku4vorbcnKSBlbHNlIDEKCmRlZiBmaXRzX2luX3J1bnModiwgdXNlcnMsIHJ1bnMpOgogICAgIiIidXNlcnMg44KSIHJ1bnMg5L6/44G+44Gn44Gr5Y+O44KB44KJ44KM44KL44GL77yI6aCG55Wq44Gp44GK44KK44Gr6Kmw44KB44Gm44GE44GP77yJIiIiCiAgICByZXN0ID0gbGlzdCh1c2VycykKICAgIGZvciBfIGluIHJhbmdlKHJ1bnMpOgogICAgICAgIGlmIG5vdCByZXN0OiByZXR1cm4gVHJ1ZQogICAgICAgIGsgPSBmaXRfY291bnQodiwgcmVzdCkKICAgICAgICBpZiBrID09IDA6IHJldHVybiBGYWxzZQogICAgICAgIHJlc3QgPSByZXN0W2s6XQogICAgcmV0dXJuIG5vdCByZXN0CgpkZWYgd2h5X25vdCh2LCBncm91cCk6CiAgICAiIiLkuZfjgozjgarjgYTnkIbnlLEiIiIKICAgIHdjID0gc3VtKDEgZm9yIGMgaW4gZ3JvdXAgaWYgY1snbW9iJ10gPT0gJ3djJykKICAgIHdrID0gc3VtKDEgZm9yIGMgaW4gZ3JvdXAgaWYgY1snbW9iJ10gPT0gJ3dhbGtlcicpCiAgICBpZiB3YyBhbmQgaW50KHYuZ2V0KCd3Y19tYXgnLCAwKSkgPT0gMDogcmV0dXJuICfou4rjgYTjgZnkuI3lj68nCiAgICBpZiB3YyA+IGludCh2LmdldCgnd2NfbWF4JywgMCkpOiAgICAgICAgcmV0dXJuICfou4rjgYTjgZnlrprlk6EnCiAgICBpZiB3ayA+IHdhbGtlcl9tYXgodik6ICAgICAgICAgICAgICAgICAgcmV0dXJuICfmranooYzlmajjga7kuIrpmZAnCiAgICByZXR1cm4gJ+WumuWToScKCgojIOKUgOKUgCDmiYvpoIYx44CA44G+44Go44G+44KK44KS5L2c44KL77yI5L2P5omA77yL44GK6L+O44GI5pmC5Yi744GM5ZCM44GY5Lq644Gv5ZCM44GY6LuK44Gu6YCj57aa44GX44Gf6aCG55Wq77yJ4pSA4pSACmRlZiBtYWtlX2dyb3Vwcyh1c2Vycyk6CiAgICBiYWcgPSB7fQogICAgZm9yIGMgaW4gdXNlcnM6CiAgICAgICAgayA9IChjWydhZGRyJ10sIGNbJ3RhcmdldCddKQogICAgICAgIGJhZy5zZXRkZWZhdWx0KGssIFtdKS5hcHBlbmQoYykKICAgIGdzID0gbGlzdChiYWcudmFsdWVzKCkpCiAgICAjIOOBiui/juOBiOaZguWIu+OBruaXqeOBhOmghuOAguaMh+WumuOBquOBl+OBr+acgOW+jAogICAgZ3Muc29ydChrZXk9bGFtYmRhIGc6ICh0b19tKGdbMF1bJ3RhcmdldCddKSBpZiB0b19tKGdbMF1bJ3RhcmdldCddKSBpcyBub3QgTm9uZSBlbHNlIDk5KjYwKSkKICAgIHJldHVybiBncwoKCiMg4pSA4pSAIOaJi+mghjPjgIDou4rlhoXjga7poIbnlarvvIjmnIDov5Hlgo3jgafjgb7jgo/jgorjgIHmjIflrprmmYLliLvvvI/liLDnnYDopovovrzjgb/jgafkuKbjgbnmm7/jgYjvvInilIDilIAKZGVmIG9yZGVyX3N0b3BzKGdyb3VwX2lkeHMsIGdyb3VwcywgZGVwYXJ0X21pbik6CiAgICBpZiBsZW4oZ3JvdXBfaWR4cykgPD0gMTogcmV0dXJuIGxpc3QoZ3JvdXBfaWR4cykKICAgIGl0ZW1zID0gW3sncG9zJzogZ3JvdXBzW2dpXVswXVsncG9zJ10sCiAgICAgICAgICAgICAgJ2FkZHInOiBncm91cHNbZ2ldWzBdLmdldCgnYWRkcicsICcnKSwKICAgICAgICAgICAgICAndGFyZ2V0JzogbmV4dCgoY1sndGFyZ2V0J10gZm9yIGMgaW4gZ3JvdXBzW2dpXSBpZiBjWyd0YXJnZXQnXSksICcnKX0KICAgICAgICAgICAgIGZvciBnaSBpbiBncm91cF9pZHhzXQoKICAgICMg4pGgIOacgOi/keWCjeazleOBp+S4gOWRqOOBrumghueVquOCkuS9nOOCiwogICAgcmVzdCwgbm4gPSBsaXN0KHJhbmdlKGxlbihpdGVtcykpKSwgW10KICAgIGN1ciwgY3VyX2EgPSBDT05GSUdbJ2ZhY19wb3MnXSwgQ09ORklHWydmYWNpbGl0eSddCiAgICB3aGlsZSByZXN0OgogICAgICAgIGJpLCBibSA9IDAsIGZsb2F0KCdpbmYnKQogICAgICAgIGZvciBrLCBpZHggaW4gZW51bWVyYXRlKHJlc3QpOgogICAgICAgICAgICBtID0gbGVnbWluKGN1ciwgaXRlbXNbaWR4XVsncG9zJ10sIGN1cl9hLCBpdGVtc1tpZHhdWydhZGRyJ10pCiAgICAgICAgICAgIGlmIG0gPCBibTogYm0sIGJpID0gbSwgawogICAgICAgIHBpY2sgPSByZXN0LnBvcChiaSk7IG5uLmFwcGVuZChwaWNrKQogICAgICAgIGN1ciwgY3VyX2EgPSBpdGVtc1twaWNrXVsncG9zJ10sIGl0ZW1zW3BpY2tdWydhZGRyJ10KCiAgICAjIOKRoSDjgZ3jga7poIbjgaflm57jgaPjgZ/jgajjgY3jga7liLDnnYDopovovrzjgb8KICAgIGV0YSwgdCA9IHt9LCBkZXBhcnRfbWluCiAgICBwcmV2LCBwcmV2X2EgPSBDT05GSUdbJ2ZhY19wb3MnXSwgQ09ORklHWydmYWNpbGl0eSddCiAgICBmb3IgaSBpbiBubjoKICAgICAgICB0ICs9IGxlZ21pbihwcmV2LCBpdGVtc1tpXVsncG9zJ10sIHByZXZfYSwgaXRlbXNbaV1bJ2FkZHInXSkKICAgICAgICBldGFbaV0gPSB0CiAgICAgICAgdCArPSBDT05GSUdbJ3N0b3AnXQogICAgICAgIHByZXYsIHByZXZfYSA9IGl0ZW1zW2ldWydwb3MnXSwgaXRlbXNbaV1bJ2FkZHInXQoKICAgICMg4pGiIOaMh+WumuaZguWIu+OBjOOBguOCjOOBsOOBneOCjOOAgeeEoeOBkeOCjOOBsOimi+i+vOOBv+OBp+S4puOBueabv+OBiAogICAga2V5ZWQgPSBbXQogICAgZm9yIHBvcywgaSBpbiBlbnVtZXJhdGUobm4pOgogICAgICAgIHRnID0gdG9fbShpdGVtc1tpXVsndGFyZ2V0J10pCiAgICAgICAga2V5ZWQuYXBwZW5kKCh0ZyBpZiB0ZyBpcyBub3QgTm9uZSBlbHNlIGV0YVtpXSwgcG9zLCBpKSkKICAgIGtleWVkLnNvcnQoKQogICAgcmV0dXJuIFtncm91cF9pZHhzW3hbMl1dIGZvciB4IGluIGtleWVkXQoKCmRlZiByb3V0ZV9taW51dGVzKGdyb3VwX2lkeHMsIGdyb3Vwcyk6CiAgICAiIiLkuovmpa3miYDjgpLlh7rjgablhajlk6HjgpLlm57jgorjgIHkuovmpa3miYDjgbjluLDjgovjgb7jgafjga7np7vli5XmmYLplpPjga7lkIjoqIjjgIIKICAgICAgIOW4sOOCiuOBruWMuumWk+OCguWFpeOCjOOCi+OAguWFpeOCjOOBquOBhOOBqOOAgeac</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>44GM44GC44KM44Gw44Gd44KM44CB54Sh44GR44KM44Gw6KaL6L6844G/44Gn5Lim44G55pu/44GICiAgICBrZXllZCA9IFtdCiAgICBmb3IgcG9zLCBpIGluIGVudW1lcmF0ZShubik6CiAgICAgICAgdGcgPSB0b19tKGl0ZW1zW2ldWyd0YXJnZXQnXSkKICAgICAgICBrZXllZC5hcHBlbmQoKHRnIGlmIHRnIGlzIG5vdCBOb25lIGVsc2UgZXRhW2ldLCBwb3MsIGkpKQogICAga2V5ZWQuc29ydCgpCiAgICByZXR1cm4gW2dyb3VwX2lkeHNbeFsyXV0gZm9yIHggaW4ga2V5ZWRdCgoKZGVmIHJvdXRlX21pbnV0ZXMoZ3JvdXBfaWR4cywgZ3JvdXBzKToKICAgICIiIuS6i+alreaJgOOCkuWHuuOBpuWFqOWToeOCkuWbnuOCiuOAgeS6i+alreaJgOOBuOW4sOOCi+OBvuOBp+OBruenu+WLleaZgumWk+OBruWQiOioiOOAggogICAgICAg5biw44KK44Gu5Yy66ZaT44KC5YWl44KM44KL44CC5YWl44KM44Gq44GE44Go44CB5pyA5b6M44Gu44GK5a6F44GM5LqL5qWt5omA44GL44KJ6YGg44GE5qGI44KSCiAgICAgICDpgbjjgpPjgafjgZfjgb7jgYTjgIHlrp/pmpvjga7mi5jmnZ/mmYLplpPjgYzplbfjgY/jgarjgosiIiIKICAgIGlmIG5vdCBncm91cF9pZHhzOiByZXR1cm4gMAogICAgdG90YWwgPSAwCiAgICBwcmV2LCBwcmV2X2EgPSBDT05GSUdbJ2ZhY19wb3MnXSwgQ09ORklHWydmYWNpbGl0eSddCiAgICBmb3IgZ2kgaW4gZ3JvdXBfaWR4czoKICAgICAgICBjID0gZ3JvdXBzW2dpXVswXQogICAgICAgIHRvdGFsICs9IGxlZ21pbihwcmV2LCBjWydwb3MnXSwgcHJldl9hLCBjLmdldCgnYWRkcicsICcnKSkKICAgICAgICBwcmV2LCBwcmV2X2EgPSBjWydwb3MnXSwgYy5nZXQoJ2FkZHInLCAnJykKICAgIHRvdGFsICs9IGxlZ21pbihwcmV2LCBDT05GSUdbJ2ZhY19wb3MnXSwgcHJldl9hLCBDT05GSUdbJ2ZhY2lsaXR5J10pICAgIyDluLDjgooKICAgIHJldHVybiB0b3RhbAoKZGVmIG9yZF9tYXAoYXNzaWduLCBncm91cHMsIHZlaGljbGVzLCBkZXBhcnRfbWluKToKICAgIG0gPSB7dmk6IFtdIGZvciB2aSBpbiByYW5nZShsZW4odmVoaWNsZXMpKX0KICAgIGZvciBnaSwgdmkgaW4gZW51bWVyYXRlKGFzc2lnbik6CiAgICAgICAgaWYgdmkgPj0gMDogbVt2aV0uYXBwZW5kKGdpKQogICAgZm9yIHZpIGluIG06CiAgICAgICAgbVt2aV0gPSBvcmRlcl9zdG9wcyhtW3ZpXSwgZ3JvdXBzLCBkZXBhcnRfbWluKQogICAgcmV0dXJuIG0KClJVTjJfUEVOQUxUWSA9IDYwICAgIyAy5L6/44GM5b+F6KaB44Gr44Gq44KL6YWN6LuK44Gr44Gv44CB44GT44Gu44G244KT5LiN5Yip44Gq54K544KS44Gk44GR44KLCgpkZWYgdG90YWxfc2NvcmUoYXNzaWduLCBncm91cHMsIHZlaGljbGVzLCBkZXBhcnRfbWluKToKICAgICIiIuenu+WLleaZgumWk+OBruWQiOioiOOAgjLkvr/jgYzlv4XopoHjgavjgarjgovou4rjgYzjgYLjgozjgbDjg5rjg4rjg6vjg4bjgqPjgpLotrPjgZkKICAgICAgIO+8iOi7iuOBjOi2s+OCiuOBpuOBhOOCi+OBruOBq+eEoemnhOOBqzLkvr/jgbjliIbjgZHjgarjgYTjgojjgYbjgavjgZnjgovjgZ/jgoHvvIkiIiIKICAgIG9tID0gb3JkX21hcChhc3NpZ24sIGdyb3VwcywgdmVoaWNsZXMsIGRlcGFydF9taW4pCiAgICB0b3RhbCA9IHN1bShyb3V0ZV9taW51dGVzKGdpcywgZ3JvdXBzKSBmb3IgZ2lzIGluIG9tLnZhbHVlcygpIGlmIGdpcykKICAgIGZvciB2aSwgdiBpbiBlbnVtZXJhdGUodmVoaWNsZXMpOgogICAgICAgIHNlcSA9IFtjIGZvciBnaSBpbiBvbS5nZXQodmksIFtdKSBmb3IgYyBpbiBncm91cHNbZ2ldXQogICAgICAgIGlmIHNlcSBhbmQgbm90IGZpdHNfaW5fcnVucyh2LCBzZXEsIDEpOgogICAgICAgICAgICB0b3RhbCArPSBSVU4yX1BFTkFMVFkKICAgIHJldHVybiB0b3RhbAoKCiMg4pSA4pSAIOaJi+mghjLjgIDosqrmrLLms5XjgaflibLjgorlvZPjgabjgosg4pSA4pSACmRlZiBncmVlZHkoZ3JvdXBzLCB2ZWhpY2xlcyk6CiAgICBsb2FkID0gWygwLCAwLCAwKV0gKiBsZW4odmVoaWNsZXMpCiAgICBoZWxkID0gW1tdIGZvciBfIGluIHZlaGljbGVzXSAgICAgICAgIyDjgZ3jga7ou4rjgavkuZfjgZvjgovjgajmsbrjgoHjgZ/mlrnvvIjkvr/jgpLliIbjgZHjgovliY3vvIkKICAgIGxhc3QgPSBbTm9uZV0gKiBsZW4odmVoaWNsZXMpCiAgICBhc3NpZ24sIHVuYXNzaWduZWQgPSBbLTFdICogbGVuKGdyb3VwcyksIFtdCiAgICBydW5zID0gcnVuc19hbGxvd2VkKCkKCiAgICAjIOS7i+itt+OBr+i7iuOBhOOBmeODu+atqeihjOWZqOOBruaWueOCkuWFiOOBq+WJsuOCiuW9k+OBpuOCi++8iOW+jOWbnuOBl+OBq+OBmeOCi+OBqOS5l+OCjOOCi+i7iuOBjOWfi+OBvuOCi++8iQogICAgb3JkZXIgPSBzb3J0ZWQocmFuZ2UobGVuKGdyb3VwcykpLAogICAgICAgICAgICAgICAgICAga2V5PWxhbWJkYSBnaTogKDAgaWYgYW55KGNbJ21vYiddIGZvciBjIGluIGdyb3Vwc1tnaV0pIGVsc2UgMSwgZ2kpKSBcCiAgICAgICAgICAgIGlmIENPTkZJR1snbW9kZSddID09ICfku4vorbcnIGVsc2UgbGlzdChyYW5nZShsZW4oZ3JvdXBzKSkpCgogICAgZm9yIGdpIGluIG9yZGVyOgogICAgICAgIGcgPSBncm91cHNbZ2ldCiAgICAgICAgZ3QgPSB0b19tKGdbMF1bJ3RhcmdldCddKQogICAgICAgIGd0ID0gZ3QgaWYgZ3QgaXMgbm90IE5vbmUgZWxzZSA5OSAqIDYwCiAgICAgICAgYmVzdCwgYmVzdF9zYyA9IC0xLCBmbG9hdCgnaW5mJykKICAgICAgICBmb3IgdmksIHYgaW4gZW51bWVyYXRlKHZlaGljbGVzKToKICAgICAgICAgICAgaWYgbm90IGNhbl9maXQodiwgbG9hZFt2aV0sIGcpOiBjb250aW51ZQogICAgICAgICAgICB0ZGlmZiA9IDAgaWYgbGFzdFt2aV0gaXMgTm9uZSBlbHNlIGFicyhndCAtIGxhc3RbdmldKQogICAgICAgICAgICBwZW5hbHR5ID0gMTAwMDAgaWYgKGxhc3RbdmldIGlzIG5vdCBOb25lIGFuZCB0ZGlmZiA+IDMwKSBlbHNlIDAKICAgICAgICAgICAgc2MgPSBwZW5hbHR5ICsgbG9hZFt2aV1bMF0KICAgICAgICAgICAgaWYgc2MgPCBiZXN0X3NjOiBiZXN0X3NjLCBiZXN0ID0gc2MsIHZpCiAgICAgICAgaWYgYmVzdCA8IDAgYW5kIHJ1bnMgPiAxOgogICAgICAgICAgICAjIDHkvr/jgavjga/lhaXjgonjgarjgYQg4oaSIDLkvr/jgb7jgafkvb/jgYjjgbDlj47jgb7jgovou4rjgpLmjqLjgZnvvIjjgYTjgaHjgbDjgpPnqbrjgYTjgabjgYTjgovou4rjgbjvvIkKICAgICAgICAgICAgZm9yIHZpLCB2IGluIGVudW1lcmF0ZSh2ZWhpY2xlcyk6CiAgICAgICAgICAgICAgICBpZiBub3QgZml0c19pbl9ydW5zKHYsIGhlbGRbdmldICsgZywgcnVucyk6IGNvbnRpbnVlCiAgICAgICAgICAgICAgICBpZiBiZXN0IDwgMCBvciBsb2FkW3ZpXVswXSA8IGxvYWRbYmVzdF1bMF06IGJlc3QgPSB2aQogICAgICAgIGlmIGJlc3QgPCAwOgogICAgICAgICAgICAjIDLkvr/jgpLkvb/jgaPjgabjgoLlhaXjgonjgarjgYQg4oaSIOWumuWToeOCkui2heOBiOOBleOBm+OBmuacquWJsuW9k+OBq+OBmeOCiwogICAgICAgICAgICByZWFzb25zID0gc29ydGVkKHt3aHlfbm90KHYsIGcpIGZvciB2IGluIHZlaGljbGVzfSkgb3IgWyfou4rkuKHjgarjgZcnXQogICAgICAgICAgICB1bmFzc2lnbmVkLmFwcGVuZCgoZywgJ+WFqOi7iuOBqOOCgicgKyAn44O7Jy5qb2luKHJlYXNvbnMpKSkKICAgICAgICAgICAgY29udGludWUKICAgICAgICBhc3NpZ25bZ2ldID0gYmVzdAogICAgICAgIGxvYWRbYmVzdF0gPSBhZGRfbG9hZChsb2FkW2Jlc3RdLCBnKQogICAgICAgIGhlbGRbYmVzdF0gPSBoZWxkW2Jlc3RdICsgZwogICAgICAgIGxhc3RbYmVzdF0gPSBndAogICAgcmV0dXJuIGFzc2lnbiwgdW5hc3NpZ25lZAoKCiMg4pSA4pSAIOaJi+mghjTjgIDntYTjgb/nm7TjgZfjgabmlLnlloTjgZnjgovvvIjpgIHov47jg4rjg5PjgajlkIzjgZjjgrfjg6Pjg4Pjg5Xjg6vlj43lvqnvvInilIDilIAKZGVmIGlzX3ZhbGlkKGFzc2lnbiwgZ3JvdXBzLCB2ZWhpY2xlcyk6CiAgICBydW5zID0gcnVuc19hbGxvd2VkKCkKICAgIHNlYXRzID0gW1tdIGZvciBfIGluIHZlaGljbGVzXQogICAgZm9yIGdpLCB2aSBpbiBlbnVtZXJhdGUoYXNzaWduKToKICAgICAgICBpZiB2aSA8IDA6IGNvbnRpbnVlCiAgICAgICAgaWYgdmkgPj0gbGVuKHZlaGljbGVzKTogcmV0dXJuIEZhbHNlCiAgICAgICAgc2VhdHNbdmldID0gc2VhdHNbdmldICsgZ3JvdXBzW2dpXQogICAgZm9yIHZpLCB2IGluIGVudW1lcmF0ZSh2ZWhpY2xlcyk6CiAgICAgICAgaWYgc2VhdHNbdmldIGFuZCBub3QgZml0c19pbl9ydW5zKHYsIHNlYXRzW3ZpXSwgcnVucyk6IHJldHVybiBGYWxzZQogICAgIyDlkIzjgZjou4rjga7kuK3jgafjgIHpmqPjgorlkIjjgYbjgYrov47jgYjmmYLliLvjga7lt67jgYwzMOWIhuOCkui2heOBiOOBquOBhOOBiwogICAgIyDvvIjmmYLliLvjga7mjIflrprjgYzjgYLjgovntYTjganjgYbjgZfjgaDjgZHjgafmr5TjgbnjgovjgILmjIflrprjgarjgZfjgpIw5YiG5omx44GE44GZ44KL44Go5YWo6YOo44Gv44GY44GL44KM44KL77yJCiAgICBmb3IgdmkgaW4gcmFuZ2UobGVuKHZlaGljbGVzKSk6CiAgICAgICAgdHMgPSBzb3J0ZWQodCBmb3IgdCBpbiAodG9fbShncm91cHNbZ2ldWzBdWyd0YXJnZXQnXSkKICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICBmb3IgZ2ksIHYgaW4gZW51bWVyYXRlKGFzc2lnbikgaWYgdiA9PSB2aSkKICAgICAgICAgICAgICAgICAgICBpZiB0IGlzIG5vdCBOb25lKQogICAgICAgIGZvciBpIGluIHJhbmdlKDEsIGxlbih0cykpOgogICAgICAgICAgICBpZiB0c1tpXSAtIHRzW2ktMV0gPiAzMDogcmV0dXJuIEZhbHNlCiAgICByZXR1cm4gVHJ1ZQoKZGVmIGltcHJvdmUoYXNzaWduLCBncm91cHMsIHZlaGljbGVzLCBkZXBhcnRfbWluLCBpdGVycz00MDAwKToKICAgIHJuZCA9IHJhbmRvbS5SYW5kb20oQ09ORklHWydzZWVkJ10pCiAgICBiZXN0ID0gbGlzdChhc3NpZ24pCiAgICBiZXN0X3NjID0gdG90YWxfc2NvcmUoYmVzdCwgZ3JvdXBzLCB2ZWhpY2xlcywgZGVwYXJ0X21pbikKICAgIGxpdmUgPSBbZ2kgZm9yIGdpLCB2aSBpbiBlbnVtZXJhdGUoYmVzdCkgaWYgdmkgPj0gMF0KICAgIGlmIGxlbihsaXZlKSA8IDI6IHJldHVybiBiZXN0LCBiZXN0X3NjLCAwCiAgICBpbXByb3ZlZCA9IDAKICAgIGZvciBfIGluIHJhbmdlKGl0ZXJzKToKICAgICAgICB0cmlhbCA9IGxpc3QoYmVzdCkKICAgICAgICBpZiBybmQucmFuZG9tKCkgPCAwLjU6CiAgICAgICAgICAgIGEsIGIgPSBybmQuc2FtcGxlKGxpdmUsIDIpCiAgICAgICAgICAgIHRyaWFsW2FdLCB0cmlhbFtiXSA9IHRyaWFsW2JdLCB0cmlhbFthXQogICAgICAgIGVsc2U6CiAgICAgICAgICAgIGdpID0gcm5kLmNob2ljZShsaXZlKQogICAgICAgICAgICB0cmlhbFtnaV0gPSBybmQucmFuZHJhbmdlKGxlbih2ZWhpY2xlcykpCiAgICAgICAgaWYgbm90IGlzX3ZhbGlkKHRyaWFsLCBncm91cHMsIHZlaGljbGVzKTogY29udGludWUKICAgICAgICBzYyA9IHRvdGFsX3Njb3JlKHRyaWFsLCBncm91cHMsIHZlaGljbGVzLCBkZXBhcnRfbWluKQogICAgICAgIGlmIHNjIDwgYmVzdF9zYzoKICAgICAgICAgICAgYmVzdCwgYmVzdF9zYyA9IHRyaWFsLCBzYwogICAgICAgICAgICBpbXByb3ZlZCArPSAxCiAgICByZXR1cm4gYmVzdCwgYmVzdF9zYywgaW1wcm92ZWQKCgpkZWYg6YCG566X44GZ44KLX+OBiygpOgogICAgIiIi5Ye655m65pmC5Yi744KS6YCG566X44GZ44KL44GL44Gp44GG44GL44CC5pei5a6a44Gn44Gv5pS+44OH44Kk44Gu44Go44GN44Gg44GR6YCG566X44GZ44KLIiIiCiAgICBhID0gQ09ORklHLmdldCgnYXV0b19kZXBhcnQnKQogICAgcmV0dXJuIChDT05GSUdbJ21vZGUnXSA9PSAn5pS+44OH44KkJykgaWYgYSBpcyBOb25lIGVsc2UgYm9vbChhKQoKZGVmIGRlcGFydF9mb3Ioc2VxLCBkZWZhdWx0X21pbik6CiAgICAiIiLmnIDliJ3jga7jgYrlroXjga7mjIflrprmmYLliLvjgavplpPjgavlkIjjgYblh7rnmbrmmYLliLvjgpLpgIbnrpfjgZnjgovjgIIKICAgICAgIOaMh+WumuaZguWIu+OBjOeEoeOBkeOCjOOBsOOAgeioreWumuOBleOCjOOBn+S4gOaWieWHuueZuuaZguWIu+OCkuOBneOBruOBvuOBvuS9v+OBhiIiIgogICAgaWYgbm90IHNlcSBvciBub3Qg6YCG566X44GZ44KLX+OBiygpOiByZXR1cm4gZGVmYXVsdF9taW4KICAgIHRnID0gdG9fbShzZXFbMF1bJ3RhcmdldCddKQogICAgaWYgdGcgaXMgTm9uZTogcmV0dXJuIGRlZmF1bHRfbWluCiAgICAjIOOBk+OBk+OBr+OAjOS9leWIhuWJjeOBq+WHuuOCjOOBsOOCiOOBhOOBi+OAjeOBruS4i+iqv+OBueOBquOBruOBp+OAgei1sOihjOWMuumWk+OBqOOBl+OBpuOBr+aVsOOBiOOBquOBhAogICAga2VlcCA9IGRpY3QoTEVHX1NUQVRTKQogICAgdHJhdmVsID0gbGVnbWluKENPTkZJR1snZmFjX3BvcyddLCBzZXFbMF1bJ3BvcyddLAogICAgICAgICAgICAgICAgICAgIENPTkZJR1snZmFjaWxpdHknXSwgc2VxWzBdLmdldCgnYWRkcicsICcnKSkKICAgIExFR19TVEFUUy51cGRhdGUoa2VlcCkKICAgIHJldHVybiBtYXgoMCwgdGcgLSB0cmF2ZWwpCgoKIyDilIDilIAg5omL6aCGNeOAgOaZguWIu+OCkuioiOeul+OBmeOCiyDilIDilIAKZGVmIGJ1aWxkX3NjaGVkdWxlKHNlcSwgZGVwYXJ0X21pbik6CiAgICAiIiJzZXE95LmX44KL6aCG44Gu5Yip55So6ICF44Oq44K544OIIOKGkiAoW+ihjF0sIOW4sOedgOaZguWIuykKCiAgICDlkIzjgZjloLTmiYDjgafntprjgZHjgabkuZfjgovmlrnjga8x5Zue44Gu5YGc6LuK44Gn44G+44Go44KB44Gm5LmX44Gb44KL44CCCiAgICDvvIgy5Lq644GE44Gm44KC5YGc6LuK44GvMeWbnuOAguS5l+mZjeaZgumWk+OCkuS6uuaVsOWIhuOBi+OBkeOBquOBhO+8iQogICAgIiIiCiAgICByb3dzLCB0ID0gW10sIGRlcGFydF9taW4KICAgIHByZXYsIHByZXZfYSA9IENPTkZJR1snZmFjX3BvcyddLCBDT05GSUdbJ2ZhY2lsaXR5J10KICAgIGkgPSAwCiAgICB3aGlsZSBpIDwgbGVuKHNlcSk6CiAgICAgICAgIyDloLTmiYDjgajmjIflrprmmYLliLvjgYzlkIzjgZjjgafntprjgYTjgabjgYTjgovmlrnjgpLjgbLjgajjgb7jgajjgoHjgavjgZnjgosKICAgICAgICBrZXkgPSAoc2VxW2ldWydwb3MnXSwgc2VxW2ldWyd0YXJnZXQnXSkKICAgICAgICBqID0gaQogICAgICAgIHdoaWxlIGogKyAxIDwgbGVuKHNlcSkgYW5kIChzZXFbaisxXVsncG9zJ10sIHNlcVtqKzFdWyd0YXJnZXQnXSkgPT0ga2V5OgogICAgICAgICAgICBqICs9IDEKICAgICAgICBjaHVuayA9IHNlcVtpOmorMV0KCiAgICAgICAgdHJhdmVsID0gbGVnbWluKHByZXYsIGNodW5rWzBdWydwb3MnXSwgcHJldl9hLCBjaHVua1swXS5nZXQoJ2FkZHInLCAnJykpCiAgICAgICAgdCArPSB0cmF2ZWwKICAgICAgICBhcnJpdmUsIHdhaXQgPSB0LCAwCiAgICAgICAgdGcgPSB0b19tKGNodW5rWzBdWyd0YXJnZXQnXSkKICAgICAgICBpZiB0ZyBpcyBub3QgTm9uZSBhbmQgdGcgPiBhcnJpdmU6CiAgICAgICAgICAgIHdhaXQgPSB0ZyAtIGFycml2ZSAgICAgICAgICAjIOaXqeOBj+edgOOBhOOBn+OBruOBp+aMh+WumuaZguWIu+OBvuOBp+W+heOBpAogICAgICAgICAgICBhcnJpdmUgPSB0ZwogICAgICAgIHQgPSBhcnJpdmUgKyBDT05GSUdbJ3N0b3AnXSAgICAgIyDlgZzou4ox5Zue44G244KT44Gu5LmX6ZmN5pmC6ZaTCiAgICAgICAgbGF0ZSA9IChhcnJpdmUgLSB0ZykgaWYgKHRnIGlzIG5vdCBOb25lIGFuZCBhcnJpdmUgPiB0ZykgZWxzZSAwCiAgICAgICAgZm9yIGssIGMgaW4gZW51bWVyYXRlKGNodW5rKToKICAgICAgICAgICAgcm93cy5hcHBlbmQoeydjJzogYywgJ2Fycml2ZSc6IGFycml2ZSwgJ2RlcGFydCc6IHQsCiAgICAgICAgICAgICAgICAgICAgICAgICAnd2FpdCc6IHdhaXQgaWYgayA9PSAwIGVsc2UgMCwgJ2xhdGUnOiBsYXRlLAogICAgICAgICAgICAgICAgICAgICAgICAgJ3RyYXZlbCc6IHRyYXZlbCBpZiBrID09IDAgZWxzZSAwLAogICAgICAgICAgICAgICAgICAgICAgICAgJ3NhbWUnOiBrID4gMH0pCiAgICAgICAgcHJldiwgcHJldl9hID0gY2h1bmtbMF1bJ3BvcyddLCBjaHVua1swXS5nZXQoJ2FkZHInLCAnJykKICAgICAgICBpID0gaiArIDEKICAgIGJhY2sgPSB0ICsgKGxlZ21pbihwcmV2LCBDT05GSUdbJ2ZhY19wb3MnXSwgcHJldl9hLCBDT05GSUdbJ2ZhY2lsaXR5J10pIGlmIHNlcSBlbHNlIDApCiAgICByZXR1cm4gcm93cywgYmFjawoKCiMg4pSA4pSAIOaJi+mghjbjgIAy5L6/44KS5L2/44GG44GL5Yik5pat44GZ44KLIOKUgOKUgApkZWYgc3BsaXRfcnVuMihzZXEsIHYsIGRlcGFydF9taW4pOgogICAgIiIi5oi744KK5YCkICgx5L6/LCAy5L6/LCDnkIbnlLEp44CC5YiG44GR44Gq44GE44Gq44KJMuS+v+OBr+epuiIiIgogICAgaWYgbm90IENPTkZJR1sndXNlX3J1bjInXSBvciBDT05GSUdbJ21vZGUnXSAhPSAn5LuL6K23JzoKICAgICAgICByZXR1cm4gc2VxLCBbXSwgJycKCiAgICAjIOKRoCAx5L6/44Gr5LmX44KK5YiH44KJ44Gq44GE44G244KT44Gv5b+F44GaMuS+v+OBuAogICAgZml0MSA9IGZpdF9jb3VudCh2LCBzZXEpCiAgICBpZiBmaXQxIDwgbGVuKHNlcSk6CiAgICAgICAgcmVzdCA9IHNlcVtmaXQxOl0KICAgICAgICBmaXQyID0gZml0X2NvdW50KHYsIHJlc3QpCiAgICAgICAgcmV0dXJuIHNlcVs6Zml0MV0sIHJlc3RbOmZpdDJdLCAnMeS+v+OBq+S5l+OCiuWIh+OCieOBquOBhOOBn+OCgScKCiAgICAjIOKRoSA26LuS5Lul5LiK44GC44KL44Go44GN44Gg44GR44CB5YiG44GR44Gf44G744GG44GM5pep44GE44GL44KS6KaL44KLCiAgICBzdG9wcyA9IGxlbih7Y1snYWRkciddIGZvciBjIGluIHNlcX0pCiAgICBpZiBzdG9wcyA8IFJVTjJfTUlOX1NUT1BTOgogICAgICAgIHJldHVybiBzZXEsIFtdLCAnJwoKICAgIGJhc2Vfcm93cywgXyA9IGJ1aWxkX3NjaGVkdWxlKHNlcSwgZGVwYXJ0X21pbikKICAgIGJhc2VfYXZnICA9IHN1bShyWydhcnJpdmUnXSBmb3IgciBpbiBiYXNlX3Jvd3MpIC8gbGVuKGJhc2Vfcm93cykKICAgIGJhc2VfbGFzdCA9IG1heChyWydhcnJpdmUnXSBmb3IgciBpbiBiYXNlX3Jvd3MpCgogICAgYmVzdCA9IE5vbmUKICAgIGZvciBjdXQgaW4gcmFuZ2UoMSwgbGVuKHNlcSkpOgogICAgICAgIGEsIGIgPSBzZXFbOmN1dF0sIHNlcVtjdXQ6XQogICAgICAgIGlmIGZpdF9jb3VudCh2LCBhKSA8IGxlbihhKSBvciBmaXRfY291bnQodiwgYikgPCBsZW4oYik6IGNvbnRpbnVlCiAgICAgICAgcmEsIGJhY2sgPSBidWlsZF9zY2hlZHVsZShhLCBkZXBhcnRfbWluKQogICAgICAgIHJiLCBfICAgID0gYnVpbGRfc2NoZWR1bGUoYiwgYmFjayArIENPTkZJR1sndHVybiddKQogICAgICAgIHJvd3MgPSByYSArIHJiCiAgICAgICAgYXZnICA9IHN1bShyWydhcnJpdmUnXSBmb3IgciBpbiByb3dzKSAvIGxlbihyb3dzKQogICAgICAgIGxhc3QgPSBtYXgoclsnYXJyaXZlJ10gZm9yIHIgaW4gcm93cykKICAgICAgICBnYWluID0gYmFzZV9hdmcgLSBhdmcKICAgICAgICBsb3NzID0gbGFzdCAtIGJhc2VfbGFzdAogICAgICAgIGlmIGdhaW4gPj0gUlVOMl9SRVFfR0FJTiBhbmQgbG9zcyA8IFJVTjJfTUFYX0xPU1M6CiAgICAgICAgICAgIGlmIGJlc3QgaXMgTm9uZSBvciBnYWluID4gYmVzdFswXToKICAgICAgICAgICAgICAgIGJlc3QgPSAoZ2FpbiwgYSwgYikKICAgIGlmIGJlc3Q6CiAgICAgICAgcmV0dXJuIGJlc3RbMV0sIGJlc3RbMl0sICfliIbjgZHjgZ/jgbvjgYbjgYzlubPlnYfjgaclZOWIhuaXqeOBhOOBn+OCgScgJSByb3VuZChiZXN0WzBdKQogICAgcmV0dXJuIHNlcSwgW10sICcnCgoKIyDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZAKIyDlrp/ooYwKIyDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZAKCmRlZiBydW4oKToKICAgIHZlaGljbGVzID0gW3YgZm9yIHYgaW4gVkVISUNMRVMgaWYgdlsnbmFtZSddIG5vdCBpbiBPRkZfVkVISUNMRVNdCiAgICB1c2VycyAgICA9IFtjIGZvciBjIGluIFVTRVJTICAgIGlmIGNbJ25hbWUnXSBub3QgaW4gT0ZGX1VTRVJTXQogICAgc3RhZmYgICAgPSBbcyBmb3IgcyBpbiBTVEFGRiAgICBpZiBzWyduYW1lJ10gbm90IGluIE9GRl9TVEFGRl0KICAgIGlmIG5vdCB2ZWhpY2xlczogcHJpbnQoJ+i1sOOCjOOCi+i7iuOBjOOBguOCiuOBvuOBm+OCkycpOyByZXR1cm4KICAgIGlmIG5vdCB1c2VyczogICAgcHJpbnQoJ+mAgei/juOBmeOCi+aWueOBjOOBhOOBvuOBm+OCkycpOyByZXR1cm4KCiAgICAjIOWun+a4rOihqOOBjOOBguOCi+OBruOBq+S6i+alreaJgOOBruS9j+aJgOOBjOWZm+OBv+WQiOOBo+OBpuOBhOOBquOBhOOBqOOAgem7meOBo+OBpueyvuW6puOBjOiQveOBoeOCi+OAggogICAgIyDotbDjgovliY3jgavmsJfjgaXjgZHjgovjgojjgYbjgIHjgZPjgZPjgafnorrjgYvjgoHjgovjgIIKICAgIHdhcm5fY2ZnID0gW10KICAgIGlmIFJFQUw6CiAgICAgICAga2V5cyA9IHNldCgpCiAgICAgICAgZm9yIGEsIGIgaW4gUkVBTDoga2V5cy5hZGQoYSk7IGtleXMuYWRkKGIpCiAgICAgICAgaWYgQ09ORklHWydmYWNpbGl0eSddIG5vdCBpbiBrZXlzOgogICAgICAgICAgICB3YXJuX2NmZy5hcHBlbmQoCiAgICAgICAgICAgICAgICAiQ09ORklHWydmYWNpbGl0eSddIOOBjOWun+a4rOihqOOBq+OBguOCiuOBvuOBm+OCk++8iOOBhOOBvuOBr+OAjCVz44CN77yJ44CCXG4iCiAgICAgICAgICAgICAgICAi44CA44CA5a6f5ris6KGo44Gr5Ye644Gm44GP44KL5L2P5omA44Gu44Gp44KM44GL44Go5LiA5a2X5LiA5Y+l44Gd44KN44GI44Gm44GP44Gg44GV44GE44CCXG4iCiAgICAgICAgICAgICAgICAi44CA44CA5YCZ6KOcOiAlcyIgJSAoQ09ORklHWydmYWNpbGl0eSddLCAn77yPJy5qb2luKHNvcnRlZChrZXlzKVs6NV0pKSkKICAgICAgICBtaXNzID0gW2NbJ25hbWUnXSBmb3IgYyBpbiB1c2VycyBpZiBjLmdldCgnYWRkcicpIGFuZCBjWydhZGRyJ10gbm90IGluIGtleXNdCiAgICAgICAgaWYgbWlzczoK</t>
+          <t>gOW+jOOBruOBiuWuheOBjOS6i+alreaJgOOBi+OCiemBoOOBhOahiOOCkgogICAgICAg6YG444KT44Gn44GX44G+44GE44CB5a6f6Zqb44Gu5ouY5p2f5pmC6ZaT44GM6ZW344GP44Gq44KLIiIiCiAgICBpZiBub3QgZ3JvdXBfaWR4czogcmV0dXJuIDAKICAgIHRvdGFsID0gMAogICAgcHJldiwgcHJldl9hID0gQ09ORklHWydmYWNfcG9zJ10sIENPTkZJR1snZmFjaWxpdHknXQogICAgZm9yIGdpIGluIGdyb3VwX2lkeHM6CiAgICAgICAgYyA9IGdyb3Vwc1tnaV1bMF0KICAgICAgICB0b3RhbCArPSBsZWdtaW4ocHJldiwgY1sncG9zJ10sIHByZXZfYSwgYy5nZXQoJ2FkZHInLCAnJykpCiAgICAgICAgcHJldiwgcHJldl9hID0gY1sncG9zJ10sIGMuZ2V0KCdhZGRyJywgJycpCiAgICB0b3RhbCArPSBsZWdtaW4ocHJldiwgQ09ORklHWydmYWNfcG9zJ10sIHByZXZfYSwgQ09ORklHWydmYWNpbGl0eSddKSAgICMg5biw44KKCiAgICByZXR1cm4gdG90YWwKCmRlZiBvcmRfbWFwKGFzc2lnbiwgZ3JvdXBzLCB2ZWhpY2xlcywgZGVwYXJ0X21pbik6CiAgICBtID0ge3ZpOiBbXSBmb3IgdmkgaW4gcmFuZ2UobGVuKHZlaGljbGVzKSl9CiAgICBmb3IgZ2ksIHZpIGluIGVudW1lcmF0ZShhc3NpZ24pOgogICAgICAgIGlmIHZpID49IDA6IG1bdmldLmFwcGVuZChnaSkKICAgIGZvciB2aSBpbiBtOgogICAgICAgIG1bdmldID0gb3JkZXJfc3RvcHMobVt2aV0sIGdyb3VwcywgZGVwYXJ0X21pbikKICAgIHJldHVybiBtCgpSVU4yX1BFTkFMVFkgPSA2MCAgICMgMuS+v+OBjOW/heimgeOBq+OBquOCi+mFjei7iuOBq+OBr+OAgeOBk+OBruOBtuOCk+S4jeWIqeOBqueCueOCkuOBpOOBkeOCiwoKZGVmIHRvdGFsX3Njb3JlKGFzc2lnbiwgZ3JvdXBzLCB2ZWhpY2xlcywgZGVwYXJ0X21pbik6CiAgICAiIiLnp7vli5XmmYLplpPjga7lkIjoqIjjgIIy5L6/44GM5b+F6KaB44Gr44Gq44KL6LuK44GM44GC44KM44Gw44Oa44OK44Or44OG44Kj44KS6Laz44GZCiAgICAgICDvvIjou4rjgYzotrPjgorjgabjgYTjgovjga7jgavnhKHpp4Tjgasy5L6/44G45YiG44GR44Gq44GE44KI44GG44Gr44GZ44KL44Gf44KB77yJIiIiCiAgICBvbSA9IG9yZF9tYXAoYXNzaWduLCBncm91cHMsIHZlaGljbGVzLCBkZXBhcnRfbWluKQogICAgdG90YWwgPSBzdW0ocm91dGVfbWludXRlcyhnaXMsIGdyb3VwcykgZm9yIGdpcyBpbiBvbS52YWx1ZXMoKSBpZiBnaXMpCiAgICBmb3IgdmksIHYgaW4gZW51bWVyYXRlKHZlaGljbGVzKToKICAgICAgICBzZXEgPSBbYyBmb3IgZ2kgaW4gb20uZ2V0KHZpLCBbXSkgZm9yIGMgaW4gZ3JvdXBzW2dpXV0KICAgICAgICBpZiBzZXEgYW5kIG5vdCBmaXRzX2luX3J1bnModiwgc2VxLCAxKToKICAgICAgICAgICAgdG90YWwgKz0gUlVOMl9QRU5BTFRZCiAgICByZXR1cm4gdG90YWwKCgojIOKUgOKUgCDmiYvpoIYy44CA6LKq5qyy5rOV44Gn5Ymy44KK5b2T44Gm44KLIOKUgOKUgApkZWYgZ3JlZWR5KGdyb3VwcywgdmVoaWNsZXMpOgogICAgbG9hZCA9IFsoMCwgMCwgMCldICogbGVuKHZlaGljbGVzKQogICAgaGVsZCA9IFtbXSBmb3IgXyBpbiB2ZWhpY2xlc10gICAgICAgICMg44Gd44Gu6LuK44Gr5LmX44Gb44KL44Go5rG644KB44Gf5pa577yI5L6/44KS5YiG44GR44KL5YmN77yJCiAgICBsYXN0ID0gW05vbmVdICogbGVuKHZlaGljbGVzKQogICAgYXNzaWduLCB1bmFzc2lnbmVkID0gWy0xXSAqIGxlbihncm91cHMpLCBbXQogICAgcnVucyA9IHJ1bnNfYWxsb3dlZCgpCgogICAgIyDku4vorbfjga/ou4rjgYTjgZnjg7vmranooYzlmajjga7mlrnjgpLlhYjjgavlibLjgorlvZPjgabjgovvvIjlvozlm57jgZfjgavjgZnjgovjgajkuZfjgozjgovou4rjgYzln4vjgb7jgovvvIkKICAgIG9yZGVyID0gc29ydGVkKHJhbmdlKGxlbihncm91cHMpKSwKICAgICAgICAgICAgICAgICAgIGtleT1sYW1iZGEgZ2k6ICgwIGlmIGFueShjWydtb2InXSBmb3IgYyBpbiBncm91cHNbZ2ldKSBlbHNlIDEsIGdpKSkgXAogICAgICAgICAgICBpZiBDT05GSUdbJ21vZGUnXSA9PSAn5LuL6K23JyBlbHNlIGxpc3QocmFuZ2UobGVuKGdyb3VwcykpKQoKICAgIGZvciBnaSBpbiBvcmRlcjoKICAgICAgICBnID0gZ3JvdXBzW2dpXQogICAgICAgIGd0ID0gdG9fbShnWzBdWyd0YXJnZXQnXSkKICAgICAgICBndCA9IGd0IGlmIGd0IGlzIG5vdCBOb25lIGVsc2UgOTkgKiA2MAogICAgICAgIGJlc3QsIGJlc3Rfc2MgPSAtMSwgZmxvYXQoJ2luZicpCiAgICAgICAgZm9yIHZpLCB2IGluIGVudW1lcmF0ZSh2ZWhpY2xlcyk6CiAgICAgICAgICAgIGlmIG5vdCBjYW5fZml0KHYsIGxvYWRbdmldLCBnKTogY29udGludWUKICAgICAgICAgICAgdGRpZmYgPSAwIGlmIGxhc3RbdmldIGlzIE5vbmUgZWxzZSBhYnMoZ3QgLSBsYXN0W3ZpXSkKICAgICAgICAgICAgcGVuYWx0eSA9IDEwMDAwIGlmIChsYXN0W3ZpXSBpcyBub3QgTm9uZSBhbmQgdGRpZmYgPiAzMCkgZWxzZSAwCiAgICAgICAgICAgIHNjID0gcGVuYWx0eSArIGxvYWRbdmldWzBdCiAgICAgICAgICAgIGlmIHNjIDwgYmVzdF9zYzogYmVzdF9zYywgYmVzdCA9IHNjLCB2aQogICAgICAgIGlmIGJlc3QgPCAwIGFuZCBydW5zID4gMToKICAgICAgICAgICAgIyAx5L6/44Gr44Gv5YWl44KJ44Gq44GEIOKGkiAy5L6/44G+44Gn5L2/44GI44Gw5Y+O44G+44KL6LuK44KS5o6i44GZ77yI44GE44Gh44Gw44KT56m644GE44Gm44GE44KL6LuK44G477yJCiAgICAgICAgICAgIGZvciB2aSwgdiBpbiBlbnVtZXJhdGUodmVoaWNsZXMpOgogICAgICAgICAgICAgICAgaWYgbm90IGZpdHNfaW5fcnVucyh2LCBoZWxkW3ZpXSArIGcsIHJ1bnMpOiBjb250aW51ZQogICAgICAgICAgICAgICAgaWYgYmVzdCA8IDAgb3IgbG9hZFt2aV1bMF0gPCBsb2FkW2Jlc3RdWzBdOiBiZXN0ID0gdmkKICAgICAgICBpZiBiZXN0IDwgMDoKICAgICAgICAgICAgIyAy5L6/44KS5L2/44Gj44Gm44KC5YWl44KJ44Gq44GEIOKGkiDlrprlk6HjgpLotoXjgYjjgZXjgZvjgZrmnKrlibLlvZPjgavjgZnjgosKICAgICAgICAgICAgcmVhc29ucyA9IHNvcnRlZCh7d2h5X25vdCh2LCBnKSBmb3IgdiBpbiB2ZWhpY2xlc30pIG9yIFsn6LuK5Lih44Gq44GXJ10KICAgICAgICAgICAgdW5hc3NpZ25lZC5hcHBlbmQoKGcsICflhajou4rjgajjgoInICsgJ+ODuycuam9pbihyZWFzb25zKSkpCiAgICAgICAgICAgIGNvbnRpbnVlCiAgICAgICAgYXNzaWduW2dpXSA9IGJlc3QKICAgICAgICBsb2FkW2Jlc3RdID0gYWRkX2xvYWQobG9hZFtiZXN0XSwgZykKICAgICAgICBoZWxkW2Jlc3RdID0gaGVsZFtiZXN0XSArIGcKICAgICAgICBsYXN0W2Jlc3RdID0gZ3QKICAgIHJldHVybiBhc3NpZ24sIHVuYXNzaWduZWQKCgojIOKUgOKUgCDmiYvpoIY044CA57WE44G/55u044GX44Gm5pS55ZaE44GZ44KL77yI6YCB6L+O44OK44OT44Go5ZCM44GY44K344Oj44OD44OV44Or5Y+N5b6p77yJ4pSA4pSACmRlZiBpc192YWxpZChhc3NpZ24sIGdyb3VwcywgdmVoaWNsZXMpOgogICAgcnVucyA9IHJ1bnNfYWxsb3dlZCgpCiAgICBzZWF0cyA9IFtbXSBmb3IgXyBpbiB2ZWhpY2xlc10KICAgIGZvciBnaSwgdmkgaW4gZW51bWVyYXRlKGFzc2lnbik6CiAgICAgICAgaWYgdmkgPCAwOiBjb250aW51ZQogICAgICAgIGlmIHZpID49IGxlbih2ZWhpY2xlcyk6IHJldHVybiBGYWxzZQogICAgICAgIHNlYXRzW3ZpXSA9IHNlYXRzW3ZpXSArIGdyb3Vwc1tnaV0KICAgIGZvciB2aSwgdiBpbiBlbnVtZXJhdGUodmVoaWNsZXMpOgogICAgICAgIGlmIHNlYXRzW3ZpXSBhbmQgbm90IGZpdHNfaW5fcnVucyh2LCBzZWF0c1t2aV0sIHJ1bnMpOiByZXR1cm4gRmFsc2UKICAgICMg5ZCM44GY6LuK44Gu5Lit44Gn44CB6Zqj44KK5ZCI44GG44GK6L+O44GI5pmC5Yi744Gu5beu44GMMzDliIbjgpLotoXjgYjjgarjgYTjgYsKICAgICMg77yI5pmC5Yi744Gu5oyH5a6a44GM44GC44KL57WE44Gp44GG44GX44Gg44GR44Gn5q+U44G544KL44CC5oyH5a6a44Gq44GX44KSMOWIhuaJseOBhOOBmeOCi+OBqOWFqOmDqOOBr+OBmOOBi+OCjOOCi++8iQogICAgZm9yIHZpIGluIHJhbmdlKGxlbih2ZWhpY2xlcykpOgogICAgICAgIHRzID0gc29ydGVkKHQgZm9yIHQgaW4gKHRvX20oZ3JvdXBzW2dpXVswXVsndGFyZ2V0J10pCiAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgZm9yIGdpLCB2IGluIGVudW1lcmF0ZShhc3NpZ24pIGlmIHYgPT0gdmkpCiAgICAgICAgICAgICAgICAgICAgaWYgdCBpcyBub3QgTm9uZSkKICAgICAgICBmb3IgaSBpbiByYW5nZSgxLCBsZW4odHMpKToKICAgICAgICAgICAgaWYgdHNbaV0gLSB0c1tpLTFdID4gMzA6IHJldHVybiBGYWxzZQogICAgcmV0dXJuIFRydWUKCmRlZiBpbXByb3ZlKGFzc2lnbiwgZ3JvdXBzLCB2ZWhpY2xlcywgZGVwYXJ0X21pbiwgaXRlcnM9NDAwMCk6CiAgICBybmQgPSByYW5kb20uUmFuZG9tKENPTkZJR1snc2VlZCddKQogICAgYmVzdCA9IGxpc3QoYXNzaWduKQogICAgYmVzdF9zYyA9IHRvdGFsX3Njb3JlKGJlc3QsIGdyb3VwcywgdmVoaWNsZXMsIGRlcGFydF9taW4pCiAgICBsaXZlID0gW2dpIGZvciBnaSwgdmkgaW4gZW51bWVyYXRlKGJlc3QpIGlmIHZpID49IDBdCiAgICBpZiBsZW4obGl2ZSkgPCAyOiByZXR1cm4gYmVzdCwgYmVzdF9zYywgMAogICAgaW1wcm92ZWQgPSAwCiAgICBmb3IgXyBpbiByYW5nZShpdGVycyk6CiAgICAgICAgdHJpYWwgPSBsaXN0KGJlc3QpCiAgICAgICAgaWYgcm5kLnJhbmRvbSgpIDwgMC41OgogICAgICAgICAgICBhLCBiID0gcm5kLnNhbXBsZShsaXZlLCAyKQogICAgICAgICAgICB0cmlhbFthXSwgdHJpYWxbYl0gPSB0cmlhbFtiXSwgdHJpYWxbYV0KICAgICAgICBlbHNlOgogICAgICAgICAgICBnaSA9IHJuZC5jaG9pY2UobGl2ZSkKICAgICAgICAgICAgdHJpYWxbZ2ldID0gcm5kLnJhbmRyYW5nZShsZW4odmVoaWNsZXMpKQogICAgICAgIGlmIG5vdCBpc192YWxpZCh0cmlhbCwgZ3JvdXBzLCB2ZWhpY2xlcyk6IGNvbnRpbnVlCiAgICAgICAgc2MgPSB0b3RhbF9zY29yZSh0cmlhbCwgZ3JvdXBzLCB2ZWhpY2xlcywgZGVwYXJ0X21pbikKICAgICAgICBpZiBzYyA8IGJlc3Rfc2M6CiAgICAgICAgICAgIGJlc3QsIGJlc3Rfc2MgPSB0cmlhbCwgc2MKICAgICAgICAgICAgaW1wcm92ZWQgKz0gMQogICAgcmV0dXJuIGJlc3QsIGJlc3Rfc2MsIGltcHJvdmVkCgoKZGVmIOmAhueul+OBmeOCi1/jgYsoKToKICAgICIiIuWHuueZuuaZguWIu+OCkumAhueul+OBmeOCi+OBi+OBqeOBhuOBi+OAguaXouWumuOBp+OBr+aUvuODh+OCpOOBruOBqOOBjeOBoOOBkemAhueul+OBmeOCiyIiIgogICAgYSA9IENPTkZJRy5nZXQoJ2F1dG9fZGVwYXJ0JykKICAgIHJldHVybiAoQ09ORklHWydtb2RlJ10gPT0gJ+aUvuODh+OCpCcpIGlmIGEgaXMgTm9uZSBlbHNlIGJvb2woYSkKCmRlZiBkZXBhcnRfZm9yKHNlcSwgZGVmYXVsdF9taW4pOgogICAgIiIi5pyA5Yid44Gu44GK5a6F44Gu5oyH5a6a5pmC5Yi744Gr6ZaT44Gr5ZCI44GG5Ye655m65pmC5Yi744KS6YCG566X44GZ44KL44CCCiAgICAgICDmjIflrprmmYLliLvjgYznhKHjgZHjgozjgbDjgIHoqK3lrprjgZXjgozjgZ/kuIDmlonlh7rnmbrmmYLliLvjgpLjgZ3jga7jgb7jgb7kvb/jgYYiIiIKICAgIGlmIG5vdCBzZXEgb3Igbm90IOmAhueul+OBmeOCi1/jgYsoKTogcmV0dXJuIGRlZmF1bHRfbWluCiAgICB0ZyA9IHRvX20oc2VxWzBdWyd0YXJnZXQnXSkKICAgIGlmIHRnIGlzIE5vbmU6IHJldHVybiBkZWZhdWx0X21pbgogICAgIyDjgZPjgZPjga/jgIzkvZXliIbliY3jgavlh7rjgozjgbDjgojjgYTjgYvjgI3jga7kuIvoqr/jgbnjgarjga7jgafjgIHotbDooYzljLrplpPjgajjgZfjgabjga/mlbDjgYjjgarjgYQKICAgIGtlZXAgPSBkaWN0KExFR19TVEFUUykKICAgIHRyYXZlbCA9IGxlZ21pbihDT05GSUdbJ2ZhY19wb3MnXSwgc2VxWzBdWydwb3MnXSwKICAgICAgICAgICAgICAgICAgICBDT05GSUdbJ2ZhY2lsaXR5J10sIHNlcVswXS5nZXQoJ2FkZHInLCAnJykpCiAgICBMRUdfU1RBVFMudXBkYXRlKGtlZXApCiAgICByZXR1cm4gbWF4KDAsIHRnIC0gdHJhdmVsKQoKCiMg4pSA4pSAIOaJi+mghjXjgIDmmYLliLvjgpLoqIjnrpfjgZnjgosg4pSA4pSACmRlZiBidWlsZF9zY2hlZHVsZShzZXEsIGRlcGFydF9taW4pOgogICAgIiIic2VxPeS5l+OCi+mghuOBruWIqeeUqOiAheODquOCueODiCDihpIgKFvooYxdLCDluLDnnYDmmYLliLspCgogICAg5ZCM44GY5aC05omA44Gn57aa44GR44Gm5LmX44KL5pa544GvMeWbnuOBruWBnOi7iuOBp+OBvuOBqOOCgeOBpuS5l+OBm+OCi+OAggogICAg77yIMuS6uuOBhOOBpuOCguWBnOi7iuOBrzHlm57jgILkuZfpmY3mmYLplpPjgpLkurrmlbDliIbjgYvjgZHjgarjgYTvvIkKICAgICIiIgogICAgcm93cywgdCA9IFtdLCBkZXBhcnRfbWluCiAgICBwcmV2LCBwcmV2X2EgPSBDT05GSUdbJ2ZhY19wb3MnXSwgQ09ORklHWydmYWNpbGl0eSddCiAgICBpID0gMAogICAgd2hpbGUgaSA8IGxlbihzZXEpOgogICAgICAgICMg5aC05omA44Go5oyH5a6a5pmC5Yi744GM5ZCM44GY44Gn57aa44GE44Gm44GE44KL5pa544KS44Gy44Go44G+44Go44KB44Gr44GZ44KLCiAgICAgICAga2V5ID0gKHNlcVtpXVsncG9zJ10sIHNlcVtpXVsndGFyZ2V0J10pCiAgICAgICAgaiA9IGkKICAgICAgICB3aGlsZSBqICsgMSA8IGxlbihzZXEpIGFuZCAoc2VxW2orMV1bJ3BvcyddLCBzZXFbaisxXVsndGFyZ2V0J10pID09IGtleToKICAgICAgICAgICAgaiArPSAxCiAgICAgICAgY2h1bmsgPSBzZXFbaTpqKzFdCgogICAgICAgIHRyYXZlbCA9IGxlZ21pbihwcmV2LCBjaHVua1swXVsncG9zJ10sIHByZXZfYSwgY2h1bmtbMF0uZ2V0KCdhZGRyJywgJycpKQogICAgICAgIHQgKz0gdHJhdmVsCiAgICAgICAgYXJyaXZlLCB3YWl0ID0gdCwgMAogICAgICAgIHRnID0gdG9fbShjaHVua1swXVsndGFyZ2V0J10pCiAgICAgICAgaWYgdGcgaXMgbm90IE5vbmUgYW5kIHRnID4gYXJyaXZlOgogICAgICAgICAgICB3YWl0ID0gdGcgLSBhcnJpdmUgICAgICAgICAgIyDml6njgY/nnYDjgYTjgZ/jga7jgafmjIflrprmmYLliLvjgb7jgaflvoXjgaQKICAgICAgICAgICAgYXJyaXZlID0gdGcKICAgICAgICB0ID0gYXJyaXZlICsgQ09ORklHWydzdG9wJ10gICAgICMg5YGc6LuKMeWbnuOBtuOCk+OBruS5l+mZjeaZgumWkwogICAgICAgIGxhdGUgPSAoYXJyaXZlIC0gdGcpIGlmICh0ZyBpcyBub3QgTm9uZSBhbmQgYXJyaXZlID4gdGcpIGVsc2UgMAogICAgICAgIGZvciBrLCBjIGluIGVudW1lcmF0ZShjaHVuayk6CiAgICAgICAgICAgIHJvd3MuYXBwZW5kKHsnYyc6IGMsICdhcnJpdmUnOiBhcnJpdmUsICdkZXBhcnQnOiB0LAogICAgICAgICAgICAgICAgICAgICAgICAgJ3dhaXQnOiB3YWl0IGlmIGsgPT0gMCBlbHNlIDAsICdsYXRlJzogbGF0ZSwKICAgICAgICAgICAgICAgICAgICAgICAgICd0cmF2ZWwnOiB0cmF2ZWwgaWYgayA9PSAwIGVsc2UgMCwKICAgICAgICAgICAgICAgICAgICAgICAgICdzYW1lJzogayA+IDB9KQogICAgICAgIHByZXYsIHByZXZfYSA9IGNodW5rWzBdWydwb3MnXSwgY2h1bmtbMF0uZ2V0KCdhZGRyJywgJycpCiAgICAgICAgaSA9IGogKyAxCiAgICBiYWNrID0gdCArIChsZWdtaW4ocHJldiwgQ09ORklHWydmYWNfcG9zJ10sIHByZXZfYSwgQ09ORklHWydmYWNpbGl0eSddKSBpZiBzZXEgZWxzZSAwKQogICAgcmV0dXJuIHJvd3MsIGJhY2sKCgojIOKUgOKUgCDmiYvpoIY244CAMuS+v+OCkuS9v+OBhuOBi+WIpOaWreOBmeOCiyDilIDilIAKZGVmIHNwbGl0X3J1bjIoc2VxLCB2LCBkZXBhcnRfbWluKToKICAgICIiIuaIu+OCiuWApCAoMeS+vywgMuS+vywg55CG55SxKeOAguWIhuOBkeOBquOBhOOBquOCiTLkvr/jga/nqboiIiIKICAgIGlmIG5vdCBDT05GSUdbJ3VzZV9ydW4yJ10gb3IgQ09ORklHWydtb2RlJ10gIT0gJ+S7i+ittyc6CiAgICAgICAgcmV0dXJuIHNlcSwgW10sICcnCgogICAgIyDikaAgMeS+v+OBq+S5l+OCiuWIh+OCieOBquOBhOOBtuOCk+OBr+W/heOBmjLkvr/jgbgKICAgIGZpdDEgPSBmaXRfY291bnQodiwgc2VxKQogICAgaWYgZml0MSA8IGxlbihzZXEpOgogICAgICAgIHJlc3QgPSBzZXFbZml0MTpdCiAgICAgICAgZml0MiA9IGZpdF9jb3VudCh2LCByZXN0KQogICAgICAgIHJldHVybiBzZXFbOmZpdDFdLCByZXN0WzpmaXQyXSwgJzHkvr/jgavkuZfjgorliIfjgonjgarjgYTjgZ/jgoEnCgogICAgIyDikaEgNui7kuS7peS4iuOBguOCi+OBqOOBjeOBoOOBkeOAgeWIhuOBkeOBn+OBu+OBhuOBjOaXqeOBhOOBi+OCkuimi+OCiwogICAgc3RvcHMgPSBsZW4oe2NbJ2FkZHInXSBmb3IgYyBpbiBzZXF9KQogICAgaWYgc3RvcHMgPCBSVU4yX01JTl9TVE9QUzoKICAgICAgICByZXR1cm4gc2VxLCBbXSwgJycKCiAgICBiYXNlX3Jvd3MsIF8gPSBidWlsZF9zY2hlZHVsZShzZXEsIGRlcGFydF9taW4pCiAgICBiYXNlX2F2ZyAgPSBzdW0oclsnYXJyaXZlJ10gZm9yIHIgaW4gYmFzZV9yb3dzKSAvIGxlbihiYXNlX3Jvd3MpCiAgICBiYXNlX2xhc3QgPSBtYXgoclsnYXJyaXZlJ10gZm9yIHIgaW4gYmFzZV9yb3dzKQoKICAgIGJlc3QgPSBOb25lCiAgICBmb3IgY3V0IGluIHJhbmdlKDEsIGxlbihzZXEpKToKICAgICAgICBhLCBiID0gc2VxWzpjdXRdLCBzZXFbY3V0Ol0KICAgICAgICBpZiBmaXRfY291bnQodiwgYSkgPCBsZW4oYSkgb3IgZml0X2NvdW50KHYsIGIpIDwgbGVuKGIpOiBjb250aW51ZQogICAgICAgIHJhLCBiYWNrID0gYnVpbGRfc2NoZWR1bGUoYSwgZGVwYXJ0X21pbikKICAgICAgICByYiwgXyAgICA9IGJ1aWxkX3NjaGVkdWxlKGIsIGJhY2sgKyBDT05GSUdbJ3R1cm4nXSkKICAgICAgICByb3dzID0gcmEgKyByYgogICAgICAgIGF2ZyAgPSBzdW0oclsnYXJyaXZlJ10gZm9yIHIgaW4gcm93cykgLyBsZW4ocm93cykKICAgICAgICBsYXN0ID0gbWF4KHJbJ2Fycml2ZSddIGZvciByIGluIHJvd3MpCiAgICAgICAgZ2FpbiA9IGJhc2VfYXZnIC0gYXZnCiAgICAgICAgbG9zcyA9IGxhc3QgLSBiYXNlX2xhc3QKICAgICAgICBpZiBnYWluID49IFJVTjJfUkVRX0dBSU4gYW5kIGxvc3MgPCBSVU4yX01BWF9MT1NTOgogICAgICAgICAgICBpZiBiZXN0IGlzIE5vbmUgb3IgZ2FpbiA+IGJlc3RbMF06CiAgICAgICAgICAgICAgICBiZXN0ID0gKGdhaW4sIGEsIGIpCiAgICBpZiBiZXN0OgogICAgICAgIHJldHVybiBiZXN0WzFdLCBiZXN0WzJdLCAn5YiG44GR44Gf44G744GG44GM5bmz5Z2H44GnJWTliIbml6njgYTjgZ/jgoEnICUgcm91bmQoYmVzdFswXSkKICAgIHJldHVybiBzZXEsIFtdLCAnJwoKCiMg4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQCiMg5a6f6KGMCiMg4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQCgpkZWYgcnVuKCk6CiAgICB2ZWhpY2xlcyA9IFt2IGZvciB2IGluIFZFSElDTEVTIGlmIHZbJ25hbWUnXSBub3QgaW4gT0ZGX1ZFSElDTEVTXQogICAgdXNlcnMgICAgPSBbYyBmb3IgYyBpbiBVU0VSUyAgICBpZiBjWyduYW1lJ10gbm90IGluIE9GRl9VU0VSU10KICAgIGlmIG5vdCB2ZWhpY2xlczogcHJpbnQoJ+i1sOOCjOOCi+i7iuOBjOOBguOCiuOBvuOBm+OCkycpOyByZXR1cm4KICAgIGlmIG5vdCB1c2VyczogICAgcHJpbnQoJ+mAgei/juOBmeOCi+aWueOBjOOBhOOBvuOBm+OCkycpOyByZXR1cm4KCiAgICAjIOWun+a4rOihqOOBjOOBguOCi+OBruOBq+S6i+alreaJgOOBruS9j+aJgOOBjOWZm+OBv+WQiOOBo+OBpuOBhOOBquOBhOOBqOOAgem7meOBo+OBpueyvuW6puOBjOiQveOBoeOCi+OAggogICAgIyDotbDjgovliY3jgavmsJfjgaXjgZHjgovjgojjgYbjgIHjgZPjgZPjgafnorrjgYvjgoHjgovjgIIKICAgIHdhcm5fY2ZnID0gW10KICAgIGlmIFJFQUw6CiAgICAgICAga2V5cyA9IHNldCgpCiAgICAgICAgZm9yIGEsIGIgaW4gUkVBTDoga2V5cy5hZGQoYSk7IGtleXMuYWRkKGIpCiAgICAgICAgaWYgQ09ORklHWydmYWNpbGl0eSddIG5vdCBpbiBrZXlzOgogICAgICAgICAgICB3YXJuX2NmZy5hcHBlbmQoCiAgICAgICAgICAgICAgICAiQ09ORklHWydmYWNpbGl0eSddIOOBjOWun+a4rOihqOOBq+OBguOCiuOBvuOBm+OCk++8iOOBhOOBvuOBr+OAjCVz44CN77yJ44CCXG4iCiAgICAgICAgICAgICAgICAi44CA44CA5a6f5ris6KGo44Gr5Ye644Gm44GP44KL5L2P5omA44Gu44Gp44KM44GL44Go5LiA5a2X5LiA5Y+l44Gd44KN44GI44Gm44GP44Gg44GV44GE44CCXG4iCiAgICAgICAgICAgICAgICAi44CA44CA5YCZ6KOcOiAlcyIgJSAoQ09ORklHWydmYWNpbGl0eSddLCAn77yPJy5qb2luKHNvcnRlZChrZXlzKVs6NV0pKSkKICAgICAgICBtaXNzID0gW2NbJ25hbWUnXSBmb3IgYyBpbiB1c2VycyBpZiBjLmdldCgnYWRkcicpIGFuZCBjWydhZGRyJ10gbm90IGluIGtleXNdCiAgICAgICAgaWYgbWlzczoKICAgICAgICAgICAgd2Fybl9jZmcuYXBwZW5kKCflrp/muKzooajjgavkvY/miYDjgYznhKHjgYTmlrk6ICcgKyAn44CBJy5qb2luKG1pc3NbOjVdKSArCiAgICAgICAgICAgICAgICAgICAgICAgICAgICAn77yI44Gd44Gu5Yy66ZaT44Gv55u057ea6Led6Zui44Gn6KaL56mN44KC44KK44G+44GZ77yJJykKCiAgICBkZXBhcnRfbWluID0gdG9fbShDT05GSUdbJ2RlcGFydCddKSBvciAwCiAgICBncm91cHMgPSBtYWtlX2dyb3Vwcyh1c2VycykKCiAgICBhc3NpZ24sIHVuYXNzaWduZWQgPSBncmVlZHkoZ3JvdXBzLCB2ZWhpY2xlcykKICAgIGFzc2lnbiwgc2NvcmUsIGltcHJvdmVkID0gaW1wcm92ZShhc3NpZ24sIGdyb3VwcywgdmVoaWNsZXMsIGRlcGFydF9taW4pCiAgICBvbSA9IG9yZF9tYXAoYXNzaWduLCBncm91cHMsIHZlaGljbGVzLCBkZXBhcnRfbWluKQoKICAgICMg44GT44GT44GL44KJ5YWI44GM44CM5a6f6Zqb44Gr6LWw44KL44Or44O844OI44CN44CC5pyA6YGp5YyW5Lit44Gu6Kmm566X44Gv5pWw44GI44Gq44GE44KI</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ICAgICAgICAgICAgd2Fybl9jZmcuYXBwZW5kKCflrp/muKzooajjgavkvY/miYDjgYznhKHjgYTmlrk6ICcgKyAn44CBJy5qb2luKG1pc3NbOjVdKSArCiAgICAgICAgICAgICAgICAgICAgICAgICAgICAn77yI44Gd44Gu5Yy66ZaT44Gv55u057ea6Led6Zui44Gn6KaL56mN44KC44KK44G+44GZ77yJJykKCiAgICBkZXBhcnRfbWluID0gdG9fbShDT05GSUdbJ2RlcGFydCddKSBvciAwCiAgICBncm91cHMgPSBtYWtlX2dyb3Vwcyh1c2VycykKCiAgICBhc3NpZ24sIHVuYXNzaWduZWQgPSBncmVlZHkoZ3JvdXBzLCB2ZWhpY2xlcykKICAgIGFzc2lnbiwgc2NvcmUsIGltcHJvdmVkID0gaW1wcm92ZShhc3NpZ24sIGdyb3VwcywgdmVoaWNsZXMsIGRlcGFydF9taW4pCiAgICBvbSA9IG9yZF9tYXAoYXNzaWduLCBncm91cHMsIHZlaGljbGVzLCBkZXBhcnRfbWluKQoKICAgICMg44GT44GT44GL44KJ5YWI44GM44CM5a6f6Zqb44Gr6LWw44KL44Or44O844OI44CN44CC5pyA6YGp5YyW5Lit44Gu6Kmm566X44Gv5pWw44GI44Gq44GE44KI44GG44Gr5oi744GZCiAgICBMRUdfU1RBVFNbJ3JlYWwnXSA9IExFR19TVEFUU1snZXN0J10gPSAwCgogICAgZHJpdmVycyA9IFtzIGZvciBzIGluIHN0YWZmIGlmIHNbJ3JvbGUnXSA9PSAnZHJpdmVyJ10KICAgIGhlbHBlcnMgPSBbcyBmb3IgcyBpbiBzdGFmZiBpZiBzWydyb2xlJ10gPT0gJ2hlbHBlciddCiAgICBkaSA9IGhpID0gMAoKICAgIHByaW50KCfvvLvphY3ou4rjg63jgrjjg4Pjgq8gJXPvvL0nICUgTE9HSUNfVkVSU0lPTikKICAgIGZvciB3IGluIHdhcm5fY2ZnOgogICAgICAgIHByaW50KCfimqAg6Kit5a6a44KS56K66KqN44GX44Gm44GP44Gg44GV44GEOiAnICsgdykKICAgIGlmIHdhcm5fY2ZnOiBwcmludCgpCgogICAgcHJpbnQoJ+OAkCVz44CAJXPjgJEnICUgKENPTkZJRy5nZXQoJ2ZhY2lsaXR5X25hbWUnKSBvciBDT05GSUdbJ2ZhY2lsaXR5J10sIENPTkZJR1sndHJpcCddKSkKICAgIGlmIOmAhueul+OBmeOCi1/jgYsoKToKICAgICAgICBwcmludCgn5Ye655m65pmC5Yi7IOWQhOi7iuOBqOOCguacgOWIneOBruOBiui/juOBiOaZguWIu+OBi+OCiemAhueulyDvvI8g5LmX6ZmNICVk5YiGJyAlIENPTkZJR1snc3RvcCddKQogICAgZWxzZToKICAgICAgICBwcmludCgn5LiA5paJ5Ye655m6ICVzIO+8jyDkuZfpmY0gJWTliIYnICUgKENPTkZJR1snZGVwYXJ0J10sIENPTkZJR1snc3RvcCddKSkKICAgIGlmIG5vdCBSRUFMOgogICAgICAgIHByaW50KCfvvIjnp7vli5XmmYLplpPjga/nm7Tnt5rot53pm6Igw5cgJS4xZiDjgafopovnqY3jgoLjgorvvIknICUgQ09ORklHWydmYWN0b3InXSkKICAgIHByaW50KCkKCiAgICB3YXJuID0gW10KICAgIGZvciB2aSwgdiBpbiBlbnVtZXJhdGUodmVoaWNsZXMpOgogICAgICAgIGdpcyA9IG9tW3ZpXQogICAgICAgIGlmIG5vdCBnaXM6IGNvbnRpbnVlCiAgICAgICAgc2VxID0gW2MgZm9yIGdpIGluIGdpcyBmb3IgYyBpbiBncm91cHNbZ2ldXQogICAgICAgIHJ1bjEsIHJ1bjIsIHJlYXNvbiA9IHNwbGl0X3J1bjIoc2VxLCB2LCBkZXBhcnRfbWluKQoKICAgICAgICBkcnYgPSBkcml2ZXJzW2RpXVsnbmFtZSddIGlmIGRpIDwgbGVuKGRyaXZlcnMpIGVsc2UgJ+mBi+i7ouaJi+S4jei2sycKICAgICAgICBpZiBkaSA8IGxlbihkcml2ZXJzKTogZGkgKz0gMQogICAgICAgIGVsc2U6IHdhcm4uYXBwZW5kKCclcyDjgavpgYvou6LmiYvjgYzjgYTjgb7jgZvjgpMnICUgdlsnbmFtZSddKQogICAgICAgIGlmIHYuZ2V0KCdoZWxwZXInKSBhbmQgaGkgPCBsZW4oaGVscGVycyk6CiAgICAgICAgICAgIGhscCA9IGhlbHBlcnNbaGldWyduYW1lJ107IGhpICs9IDEKICAgICAgICBlbHNlOgogICAgICAgICAgICBobHAgPSAn5re75LmX5ZOh44Gq44GXJwoKICAgICAgICBkZXAxID0gZGVwYXJ0X2ZvcihydW4xLCBkZXBhcnRfbWluKSAgICMg5pS+44OH44Kk44Gv5pyA5Yid44Gu44GK6L+O44GI5pmC5Yi744GL44KJ6YCG566XCiAgICAgICAgZm9yIHJpLCBwYXJ0IGluIGVudW1lcmF0ZShbcnVuMSwgcnVuMl0pOgogICAgICAgICAgICBpZiBub3QgcGFydDogY29udGludWUKICAgICAgICAgICAgZGVwID0gZGVwMQogICAgICAgICAgICBpZiByaSA9PSAxOgogICAgICAgICAgICAgICAgXywgYmFjazEgPSBidWlsZF9zY2hlZHVsZShydW4xLCBkZXAxKQogICAgICAgICAgICAgICAgZGVwID0gYmFjazEgKyBDT05GSUdbJ3R1cm4nXQogICAgICAgICAgICByb3dzLCBiYWNrID0gYnVpbGRfc2NoZWR1bGUocGFydCwgZGVwKQogICAgICAgICAgICAjIOW4sOOCiuOBruWGheios++8iOacgOW+jOOBruOBiuWuheOCkuWHuuOBn+aZguWIu++8i+enu+WLleaZgumWk++8ieOCkuWHuuOBl+OBpuOBiuOBjwogICAgICAgICAgICBpZiByb3dzOgogICAgICAgICAgICAgICAgbGFzdF9yICA9IHJvd3NbLTFdCiAgICAgICAgICAgICAgICBrZWVwICAgID0gZGljdChMRUdfU1RBVFMpICAgICAgICAgICMg6KGo56S644Gu44Gf44KB44Gu5YaN6KiI566X44Gv5Yy66ZaT44Go44GX44Gm5pWw44GI44Gq44GECiAgICAgICAgICAgICAgICBiYWNrX212ID0gbGVnbWluKGxhc3RfclsnYyddWydwb3MnXSwgQ09ORklHWydmYWNfcG9zJ10sCiAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgIGxhc3RfclsnYyddLmdldCgnYWRkcicsICcnKSwgQ09ORklHWydmYWNpbGl0eSddKQogICAgICAgICAgICAgICAgTEVHX1NUQVRTLnVwZGF0ZShrZWVwKQogICAgICAgICAgICAgICAgYmFja19ub3RlID0gJ++8u+W4sOOCiu+8neacgOW+jOOBruOBiuWuheOCkuWHuuOBnyAlcyDvvIsg56e75YuVJWTliIYg77ydICVz77y9JyAlICgKICAgICAgICAgICAgICAgICAgICB0b19obShsYXN0X3JbJ2RlcGFydCddKSwgYmFja19tdiwgdG9faG0obGFzdF9yWydkZXBhcnQnXSArIGJhY2tfbXYpKQogICAgICAgICAgICBlbHNlOgogICAgICAgICAgICAgICAgYmFja19ub3RlID0gJycKICAgICAgICAgICAgbGFiZWwgPSAnJXPvvIjlrprlk6ElZOWQje+8iScgJSAodlsnbmFtZSddLCB2WydjYXAnXSkKICAgICAgICAgICAgaWYgcnVuMjogbGFiZWwgKz0gJ+OAgCVk5L6/JyAlIChyaSArIDEpCiAgICAgICAgICAgIHByaW50KCfilqAgJXPjgIDpgYvou6LmiYvvvJolc+OAgOa3u+S5l+WToe+8miVzJyAlIChsYWJlbCwgZHJ2LCBobHApKQogICAgICAgICAgICBwcmludCgn44CA5LqL5qWt5omA5Ye655m6ICVzIOKGkiDluLDnnYAgJXPvvIglZOWIhu+8iScgJSAodG9faG0oZGVwKSwgdG9faG0oYmFjayksIGJhY2sgLSBkZXApKQogICAgICAgICAgICBpZiBiYWNrX25vdGU6IHByaW50KCfjgIAnICsgYmFja19ub3RlKQogICAgICAgICAgICBpZiByaSA9PSAxIGFuZCByZWFzb246IHByaW50KCfjgIDigLsgJXMnICUgcmVhc29uKQogICAgICAgICAgICBwcmludCgnfCAjIHwg5rCP5ZCNIHwg5L2P5omAIHwg5Yiw552AIHwg5Ye655m6IHwg5YKZ6ICDIHwnKQogICAgICAgICAgICBwcmludCgnfC0tLXwtLS0tLS18LS0tLS0tfC0tLS0tLXwtLS0tLS18LS0tLS0tfCcpCiAgICAgICAgICAgIGZvciBpLCByIGluIGVudW1lcmF0ZShyb3dzLCAxKToKICAgICAgICAgICAgICAgIGMsIG5vdGUgPSByWydjJ10sIFtdCiAgICAgICAgICAgICAgICBpZiBjWydtb2InXSA9PSAnd2MnOiAgICAgbm90ZS5hcHBlbmQoJ+i7iuOBhOOBmScpCiAgICAgICAgICAgICAgICBpZiBjWydtb2InXSA9PSAnd2Fsa2VyJzogbm90ZS5hcHBlbmQoJ+atqeihjOWZqCcpCiAgICAgICAgICAgICAgICBpZiBjWyd0YXJnZXQnXTogICAgICAgICAgbm90ZS5hcHBlbmQoJ+aMh+WumiVzJyAlIGNbJ3RhcmdldCddKQogICAgICAgICAgICAgICAgaWYgclsnd2FpdCddOiAgICAgICAgICAgIG5vdGUuYXBwZW5kKCflvoXmqZ8lZOWIhicgJSByWyd3YWl0J10pCiAgICAgICAgICAgICAgICBpZiByWydsYXRlJ106ICAgICAgICAgICAgbm90ZS5hcHBlbmQoJ+KaoCVk5YiG6YGF44KMJyAlIHJbJ2xhdGUnXSkKICAgICAgICAgICAgICAgIGlmIHIuZ2V0KCdzYW1lJyk6ICAgICAgICBub3RlLmFwcGVuZCgn5ZCM44GY5L2P5omAJykKICAgICAgICAgICAgICAgIHByaW50KCd8ICVkIHwgJXMgfCAlcyB8ICVzIHwgJXMgfCAlcyB8JyAlCiAgICAgICAgICAgICAgICAgICAgICAoaSwgY1snbmFtZSddLCBjWydhZGRyJ10sIHRvX2htKHJbJ2Fycml2ZSddKSwgdG9faG0oclsnZGVwYXJ0J10pLCAn44CBJy5qb2luKG5vdGUpKSkKICAgICAgICAgICAgZm9yIHIgaW4gcm93czoKICAgICAgICAgICAgICAgIGlmIHJbJ2xhdGUnXToKICAgICAgICAgICAgICAgICAgICB3YXJuLmFwcGVuZCgnJXMg44GM5oyH5a6aJXMg44GrICVk5YiGIOmBheOCjOOBvuOBmScKICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAlIChyWydjJ11bJ25hbWUnXSwgclsnYyddWyd0YXJnZXQnXSwgclsnbGF0ZSddKSkKICAgICAgICAgICAgbG9hZCA9IGFkZF9sb2FkKCgwLCAwLCAwKSwgcGFydCkKICAgICAgICAgICAgaWYgbG9hZFswXSA+IGNhcF9hdCh2LCBsb2FkWzFdKToKICAgICAgICAgICAgICAgIHdhcm4uYXBwZW5kKCclcyDjgYzlrprlk6HjgpLotoXjgYjjgabjgYTjgb7jgZknICUgdlsnbmFtZSddKQogICAgICAgICAgICBwcmludCgpCgogICAgICAgIGJvYXJkZWQgPSB7aWQoYykgZm9yIGMgaW4gcnVuMX0gfCB7aWQoYykgZm9yIGMgaW4gcnVuMn0KICAgICAgICBkcm9wcGVkID0gW2MgZm9yIGMgaW4gc2VxIGlmIGlkKGMpIG5vdCBpbiBib2FyZGVkXQogICAgICAgIGZvciBjIGluIGRyb3BwZWQ6CiAgICAgICAgICAgIHVuYXNzaWduZWQuYXBwZW5kKChbY10sICcy5L6/44Gn44KC5LmX44KK5YiH44KJ44Gq44GEJykpCgogICAgaWYgdW5hc3NpZ25lZDoKICAgICAgICBwcmludCgn4pqgIOacquWJsuW9kycpCiAgICAgICAgZm9yIGcsIHdoeSBpbiB1bmFzc2lnbmVkOgogICAgICAgICAgICBmb3IgYyBpbiBnOgogICAgICAgICAgICAgICAgcHJpbnQoJ+OAgCVz77yIJXPvvI8lc++8iScgJSAoY1snbmFtZSddLCBjWydhZGRyJ10sIHdoeSkpCiAgICAgICAgcHJpbnQoKQoKICAgIHByaW50KCfilIDilIAg6KaB54K5IOKUgOKUgCcpCiAgICBwcmludCgn56e75YuV5pmC6ZaT44Gu5ZCI6KiIICVk5YiG77yI5b6A5b6p44O7JWTlm57jga7ntYTjgb/nm7TjgZfjgafnn63nuK7vvIknICUgKHNjb3JlLCBpbXByb3ZlZCkpCiAgICB0b3QgPSBMRUdfU1RBVFNbJ3JlYWwnXSArIExFR19TVEFUU1snZXN0J10KICAgIGlmIFJFQUwgYW5kIHRvdCBhbmQgTEVHX1NUQVRTWydyZWFsJ10gPT0gMDoKICAgICAgICBwcmludCgn4pqgIOWun+a4rOihqOOBjOa4oeOBleOCjOOBpuOBhOOCi+OBruOBq+OAgTHljLrplpPjgoLkvb/jgYjjgabjgYTjgb7jgZvjgpPjgIInKQogICAgICAgIHByaW50KCfjgIAg5L2P5omA44Gu5pu444GN5pa544GM5a6f5ris6KGo44Go5ZCI44Gj44Gm44GE44KL44GL56K66KqN44GX44Gm44GP44Gg44GV44GE77yI5YWo6YOo6KaL56mN44KC44KK44Gr44Gq44Gj44Gm44GE44G+44GZ77yJJykKICAgIGVsaWYgUkVBTCBhbmQgdG90OgogICAgICAgIHByaW50KCflrp/pmpvjgavotbDjgosgJWTljLrplpPjga7jgYbjgaEgJWTljLrplpPvvIglZCUl77yJ44GMR29vZ2xl44Oe44OD44OX44Gu5a6f5ris5YCk44Gn44GZJwogICAgICAgICAgICAgICUgKHRvdCwgTEVHX1NUQVRTWydyZWFsJ10sIHJvdW5kKExFR19TVEFUU1sncmVhbCddIC8gdG90ICogMTAwKSkpCiAgICAgICAgaWYgTEVHX1NUQVRTWydlc3QnXToKICAgICAgICAgICAgcHJpbnQoJ+OAgOaui+OCiiAlZOWMuumWk+OBr+ebtOe3mui3nembouOBi+OCieOBruimi+epjeOCguOCiuOBp+OBmScgJSBMRUdfU1RBVFNbJ2VzdCddKQogICAgZWxpZiBub3QgUkVBTDoKICAgICAgICBwcmludCgn5a6f5ris6KGo44GM5YWl44Gj44Gm44GE44Gq44GE44Gf44KB44CB44GZ44G544Gm55u057ea6Led6Zui44GL44KJ44Gu6KaL56mN44KC44KK44Gn44GZJykKICAgIGlmIHdhcm46CiAgICAgICAgcHJpbnQoJ+KUgOKUgCDms6jmhI8g4pSA4pSAJykKICAgICAgICBmb3IgdyBpbiBzZXQod2Fybik6IHByaW50KCfjgIAnICsgdykKICAgIGlmIFJFQUwgYW5kIExFR19TVEFUU1sncmVhbCddID4gMDoKICAgICAgICBwcmludCgn4oC7IOaZguWIu+OBr0dvb2dsZeODnuODg+ODl+OBruWun+a4rOWApOOCkuOCguOBqOOBq+ioiOeul+OBl+OBpuOBhOOBvuOBmeOAguW9k+aXpeOBrumBk+i3r+eKtuazgeOBp+W3ruOBjOWHuuOBvuOBmeOAgicpCiAgICBlbHNlOgogICAgICAgIHByaW50KCfigLsg5pmC5Yi744Gv5bqn5qiZ44GL44KJ44Gu55u057ea6Led6Zui44KS44KC44Go44Gr44GX44Gf5qaC566X44Gn44GZ44CC5a6f6Zqb44Gu6YGT6Lev54q25rOB44Go44Gv5beu44GM5Ye644G+44GZ44CCJykKCmRlZiBjYWxpYnJhdGUoKToKICAgICIiIuWun+a4rOODh+ODvOOCv+OBi+OCiSBmYWN0b3LvvIjnm7Tnt5oxa23jgYLjgZ/jgorjga7liIbmlbDvvInjgpLmsYLjgoHjgosiIiIKICAgIGlmIG5vdCBDQUxJQlJBVElPTjoKICAgICAgICBwcmludCgnQ0FMSUJSQVRJT04g44Gr44CM5bqn5qiZ44O75bqn5qiZ44O75a6f6Zqb44Gu5YiG44CN44KSM+WMuumWk+S7peS4iuWFpeOCjOOBpuOBj+OBoOOBleOBhCcpCiAgICAgICAgcmV0dXJuCiAgICBwcmludCgnfCDnm7Tnt5prbSB8IOWun+mam+OBruWIhiB8IDFrbeOBguOBn+OCiiB8JykKICAgIHByaW50KCd8LS0tLS0tLS18LS0tLS0tLS0tLXwtLS0tLS0tLS0tLXwnKQogICAgcmF0ZXMgPSBbXQogICAgZm9yIGEsIGIsIHJlYWwgaW4gQ0FMSUJSQVRJT046CiAgICAgICAga20gPSBoYXZlcnNpbmVfa20oYSwgYikKICAgICAgICBpZiBrbSA8PSAwLjA1OgogICAgICAgICAgICBwcmludCgnfCAlLjJmIHwgJWQgfCDvvIjov5HjgZnjgY7jgovjga7jgafpmaTlpJbvvIkgfCcgJSAoa20sIHJlYWwpKTsgY29udGludWUKICAgICAgICByYXRlID0gcmVhbCAvIGttCiAgICAgICAgcmF0ZXMuYXBwZW5kKHJhdGUpCiAgICAgICAgcHJpbnQoJ3wgJS4yZiB8ICVkIHwgJS4xZiB8JyAlIChrbSwgcmVhbCwgcmF0ZSkpCiAgICBpZiBub3QgcmF0ZXM6CiAgICAgICAgcHJpbnQoJ+S9v+OBiOOCi+WMuumWk+OBjOOBguOCiuOBvuOBm+OCkycpOyByZXR1cm4KICAgIGF2ZyA9IHN1bShyYXRlcykgLyBsZW4ocmF0ZXMpCiAgICBwcmludCgpCiAgICBwcmludCgn44GK44GZ44GZ44KB44GuIGZhY3RvciA9ICUuMWYnICUgYXZnKQogICAgcHJpbnQoJ++8iENPTkZJRyDjga4gZmFjdG9yIOOCkuOBk+OBruWApOOBq+OBl+OBpuOBj+OBoOOBleOBhO+8iScpCgojIOS/guaVsOOCkuWQiOOCj+OBm+OBn+OBhOOBqOOBjeOBr+OAgeasoeOBruihjOOBriAjIOOCkuWkluOBl+OBpiBjYWxpYnJhdGUoKSDjgpLlrp/ooYzjgZnjgosKIyBjYWxpYnJhdGUoKQoKcnVuKCkK</t>
+          <t>44GG44Gr5oi744GZCiAgICBMRUdfU1RBVFNbJ3JlYWwnXSA9IExFR19TVEFUU1snZXN0J10gPSAwCgoKICAgIHByaW50KCfvvLvphY3ou4rjg63jgrjjg4Pjgq8gJXPvvL0nICUgTE9HSUNfVkVSU0lPTikKICAgIGZvciB3IGluIHdhcm5fY2ZnOgogICAgICAgIHByaW50KCfimqAg6Kit5a6a44KS56K66KqN44GX44Gm44GP44Gg44GV44GEOiAnICsgdykKICAgIGlmIHdhcm5fY2ZnOiBwcmludCgpCgogICAgcHJpbnQoJ+OAkCVz44CAJXPjgJEnICUgKENPTkZJRy5nZXQoJ2ZhY2lsaXR5X25hbWUnKSBvciBDT05GSUdbJ2ZhY2lsaXR5J10sIENPTkZJR1sndHJpcCddKSkKICAgIGlmIOmAhueul+OBmeOCi1/jgYsoKToKICAgICAgICBwcmludCgn5Ye655m65pmC5Yi7IOWQhOi7iuOBqOOCguacgOWIneOBruOBiui/juOBiOaZguWIu+OBi+OCiemAhueulyDvvI8g5LmX6ZmNICVk5YiGJyAlIENPTkZJR1snc3RvcCddKQogICAgZWxzZToKICAgICAgICBwcmludCgn5LiA5paJ5Ye655m6ICVzIO+8jyDkuZfpmY0gJWTliIYnICUgKENPTkZJR1snZGVwYXJ0J10sIENPTkZJR1snc3RvcCddKSkKICAgIGlmIG5vdCBSRUFMOgogICAgICAgIHByaW50KCfvvIjnp7vli5XmmYLplpPjga/nm7Tnt5rot53pm6Igw5cgJS4xZiDjgafopovnqY3jgoLjgorvvIknICUgQ09ORklHWydmYWN0b3InXSkKICAgIHByaW50KCkKCiAgICB3YXJuID0gW10KICAgIGZvciB2aSwgdiBpbiBlbnVtZXJhdGUodmVoaWNsZXMpOgogICAgICAgIGdpcyA9IG9tW3ZpXQogICAgICAgIGlmIG5vdCBnaXM6IGNvbnRpbnVlCiAgICAgICAgc2VxID0gW2MgZm9yIGdpIGluIGdpcyBmb3IgYyBpbiBncm91cHNbZ2ldXQogICAgICAgIHJ1bjEsIHJ1bjIsIHJlYXNvbiA9IHNwbGl0X3J1bjIoc2VxLCB2LCBkZXBhcnRfbWluKQoKICAgICAgICBkZXAxID0gZGVwYXJ0X2ZvcihydW4xLCBkZXBhcnRfbWluKSAgICMg5pS+44OH44Kk44Gv5pyA5Yid44Gu44GK6L+O44GI5pmC5Yi744GL44KJ6YCG566XCiAgICAgICAgZm9yIHJpLCBwYXJ0IGluIGVudW1lcmF0ZShbcnVuMSwgcnVuMl0pOgogICAgICAgICAgICBpZiBub3QgcGFydDogY29udGludWUKICAgICAgICAgICAgZGVwID0gZGVwMQogICAgICAgICAgICBpZiByaSA9PSAxOgogICAgICAgICAgICAgICAgXywgYmFjazEgPSBidWlsZF9zY2hlZHVsZShydW4xLCBkZXAxKQogICAgICAgICAgICAgICAgZGVwID0gYmFjazEgKyBDT05GSUdbJ3R1cm4nXQogICAgICAgICAgICByb3dzLCBiYWNrID0gYnVpbGRfc2NoZWR1bGUocGFydCwgZGVwKQogICAgICAgICAgICAjIOW4sOOCiuOBruWGheios++8iOacgOW+jOOBruOBiuWuheOCkuWHuuOBn+aZguWIu++8i+enu+WLleaZgumWk++8ieOCkuWHuuOBl+OBpuOBiuOBjwogICAgICAgICAgICBpZiByb3dzOgogICAgICAgICAgICAgICAgbGFzdF9yICA9IHJvd3NbLTFdCiAgICAgICAgICAgICAgICBrZWVwICAgID0gZGljdChMRUdfU1RBVFMpICAgICAgICAgICMg6KGo56S644Gu44Gf44KB44Gu5YaN6KiI566X44Gv5Yy66ZaT44Go44GX44Gm5pWw44GI44Gq44GECiAgICAgICAgICAgICAgICBiYWNrX212ID0gbGVnbWluKGxhc3RfclsnYyddWydwb3MnXSwgQ09ORklHWydmYWNfcG9zJ10sCiAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgIGxhc3RfclsnYyddLmdldCgnYWRkcicsICcnKSwgQ09ORklHWydmYWNpbGl0eSddKQogICAgICAgICAgICAgICAgTEVHX1NUQVRTLnVwZGF0ZShrZWVwKQogICAgICAgICAgICAgICAgYmFja19ub3RlID0gJ++8u+W4sOOCiu+8neacgOW+jOOBruOBiuWuheOCkuWHuuOBnyAlcyDvvIsg56e75YuVJWTliIYg77ydICVz77y9JyAlICgKICAgICAgICAgICAgICAgICAgICB0b19obShsYXN0X3JbJ2RlcGFydCddKSwgYmFja19tdiwgdG9faG0obGFzdF9yWydkZXBhcnQnXSArIGJhY2tfbXYpKQogICAgICAgICAgICBlbHNlOgogICAgICAgICAgICAgICAgYmFja19ub3RlID0gJycKICAgICAgICAgICAgbGFiZWwgPSAnJXPvvIjlrprlk6ElZOWQje+8iScgJSAodlsnbmFtZSddLCB2WydjYXAnXSkKICAgICAgICAgICAgaWYgcnVuMjogbGFiZWwgKz0gJ+OAgCVk5L6/JyAlIChyaSArIDEpCiAgICAgICAgICAgIHByaW50KCfilqAgJXMnICUgbGFiZWwpCiAgICAgICAgICAgIHByaW50KCfjgIDkuovmpa3miYDlh7rnmbogJXMg4oaSIOW4sOedgCAlc++8iCVk5YiG77yJJyAlICh0b19obShkZXApLCB0b19obShiYWNrKSwgYmFjayAtIGRlcCkpCiAgICAgICAgICAgIGlmIGJhY2tfbm90ZTogcHJpbnQoJ+OAgCcgKyBiYWNrX25vdGUpCiAgICAgICAgICAgIGlmIHJpID09IDEgYW5kIHJlYXNvbjogcHJpbnQoJ+OAgOKAuyAlcycgJSByZWFzb24pCiAgICAgICAgICAgIHByaW50KCd8ICMgfCDmsI/lkI0gfCDkvY/miYAgfCDliLDnnYAgfCDlh7rnmbogfCDlgpnogIMgfCcpCiAgICAgICAgICAgIHByaW50KCd8LS0tfC0tLS0tLXwtLS0tLS18LS0tLS0tfC0tLS0tLXwtLS0tLS18JykKICAgICAgICAgICAgZm9yIGksIHIgaW4gZW51bWVyYXRlKHJvd3MsIDEpOgogICAgICAgICAgICAgICAgYywgbm90ZSA9IHJbJ2MnXSwgW10KICAgICAgICAgICAgICAgIGlmIGNbJ21vYiddID09ICd3Yyc6ICAgICBub3RlLmFwcGVuZCgn6LuK44GE44GZJykKICAgICAgICAgICAgICAgIGlmIGNbJ21vYiddID09ICd3YWxrZXInOiBub3RlLmFwcGVuZCgn5q2p6KGM5ZmoJykKICAgICAgICAgICAgICAgIGlmIGNbJ3RhcmdldCddOiAgICAgICAgICBub3RlLmFwcGVuZCgn5oyH5a6aJXMnICUgY1sndGFyZ2V0J10pCiAgICAgICAgICAgICAgICBpZiByWyd3YWl0J106ICAgICAgICAgICAgbm90ZS5hcHBlbmQoJ+W+heapnyVk5YiGJyAlIHJbJ3dhaXQnXSkKICAgICAgICAgICAgICAgIGlmIHJbJ2xhdGUnXTogICAgICAgICAgICBub3RlLmFwcGVuZCgn4pqgJWTliIbpgYXjgownICUgclsnbGF0ZSddKQogICAgICAgICAgICAgICAgaWYgci5nZXQoJ3NhbWUnKTogICAgICAgIG5vdGUuYXBwZW5kKCflkIzjgZjkvY/miYAnKQogICAgICAgICAgICAgICAgaWYgYy5nZXQoJ25vdGUnKTogICAgICAgIG5vdGUuYXBwZW5kKGNbJ25vdGUnXSkKICAgICAgICAgICAgICAgIHByaW50KCd8ICVkIHwgJXMgfCAlcyB8ICVzIHwgJXMgfCAlcyB8JyAlCiAgICAgICAgICAgICAgICAgICAgICAoaSwgY1snbmFtZSddLCBjWydhZGRyJ10sIHRvX2htKHJbJ2Fycml2ZSddKSwgdG9faG0oclsnZGVwYXJ0J10pLCAn44CBJy5qb2luKG5vdGUpKSkKICAgICAgICAgICAgZm9yIHIgaW4gcm93czoKICAgICAgICAgICAgICAgIGlmIHJbJ2xhdGUnXToKICAgICAgICAgICAgICAgICAgICB3YXJuLmFwcGVuZCgnJXMg44GM5oyH5a6aJXMg44GrICVk5YiGIOmBheOCjOOBvuOBmScKICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAlIChyWydjJ11bJ25hbWUnXSwgclsnYyddWyd0YXJnZXQnXSwgclsnbGF0ZSddKSkKICAgICAgICAgICAgbG9hZCA9IGFkZF9sb2FkKCgwLCAwLCAwKSwgcGFydCkKICAgICAgICAgICAgaWYgbG9hZFswXSA+IGNhcF9hdCh2LCBsb2FkWzFdKToKICAgICAgICAgICAgICAgIHdhcm4uYXBwZW5kKCclcyDjgYzlrprlk6HjgpLotoXjgYjjgabjgYTjgb7jgZknICUgdlsnbmFtZSddKQogICAgICAgICAgICBwcmludCgpCgogICAgICAgIGJvYXJkZWQgPSB7aWQoYykgZm9yIGMgaW4gcnVuMX0gfCB7aWQoYykgZm9yIGMgaW4gcnVuMn0KICAgICAgICBkcm9wcGVkID0gW2MgZm9yIGMgaW4gc2VxIGlmIGlkKGMpIG5vdCBpbiBib2FyZGVkXQogICAgICAgIGZvciBjIGluIGRyb3BwZWQ6CiAgICAgICAgICAgIHVuYXNzaWduZWQuYXBwZW5kKChbY10sICcy5L6/44Gn44KC5LmX44KK5YiH44KJ44Gq44GEJykpCgogICAgaWYgdW5hc3NpZ25lZDoKICAgICAgICBwcmludCgn4pqgIOacquWJsuW9kycpCiAgICAgICAgZm9yIGcsIHdoeSBpbiB1bmFzc2lnbmVkOgogICAgICAgICAgICBmb3IgYyBpbiBnOgogICAgICAgICAgICAgICAgcHJpbnQoJ+OAgCVz77yIJXPvvI8lc++8iScgJSAoY1snbmFtZSddLCBjWydhZGRyJ10sIHdoeSkpCiAgICAgICAgcHJpbnQoKQoKICAgIHByaW50KCfilIDilIAg6KaB54K5IOKUgOKUgCcpCiAgICBwcmludCgn56e75YuV5pmC6ZaT44Gu5ZCI6KiIICVk5YiG77yI5b6A5b6p44O7JWTlm57jga7ntYTjgb/nm7TjgZfjgafnn63nuK7vvIknICUgKHNjb3JlLCBpbXByb3ZlZCkpCiAgICB0b3QgPSBMRUdfU1RBVFNbJ3JlYWwnXSArIExFR19TVEFUU1snZXN0J10KICAgIGlmIFJFQUwgYW5kIHRvdCBhbmQgTEVHX1NUQVRTWydyZWFsJ10gPT0gMDoKICAgICAgICBwcmludCgn4pqgIOWun+a4rOihqOOBjOa4oeOBleOCjOOBpuOBhOOCi+OBruOBq+OAgTHljLrplpPjgoLkvb/jgYjjgabjgYTjgb7jgZvjgpPjgIInKQogICAgICAgIHByaW50KCfjgIAg5L2P5omA44Gu5pu444GN5pa544GM5a6f5ris6KGo44Go5ZCI44Gj44Gm44GE44KL44GL56K66KqN44GX44Gm44GP44Gg44GV44GE77yI5YWo6YOo6KaL56mN44KC44KK44Gr44Gq44Gj44Gm44GE44G+44GZ77yJJykKICAgIGVsaWYgUkVBTCBhbmQgdG90OgogICAgICAgIHByaW50KCflrp/pmpvjgavotbDjgosgJWTljLrplpPjga7jgYbjgaEgJWTljLrplpPvvIglZCUl77yJ44GMR29vZ2xl44Oe44OD44OX44Gu5a6f5ris5YCk44Gn44GZJwogICAgICAgICAgICAgICUgKHRvdCwgTEVHX1NUQVRTWydyZWFsJ10sIHJvdW5kKExFR19TVEFUU1sncmVhbCddIC8gdG90ICogMTAwKSkpCiAgICAgICAgaWYgTEVHX1NUQVRTWydlc3QnXToKICAgICAgICAgICAgcHJpbnQoJ+OAgOaui+OCiiAlZOWMuumWk+OBr+ebtOe3mui3nembouOBi+OCieOBruimi+epjeOCguOCiuOBp+OBmScgJSBMRUdfU1RBVFNbJ2VzdCddKQogICAgZWxpZiBub3QgUkVBTDoKICAgICAgICBwcmludCgn5a6f5ris6KGo44GM5YWl44Gj44Gm44GE44Gq44GE44Gf44KB44CB44GZ44G544Gm55u057ea6Led6Zui44GL44KJ44Gu6KaL56mN44KC44KK44Gn44GZJykKICAgIGlmIHdhcm46CiAgICAgICAgcHJpbnQoJ+KUgOKUgCDms6jmhI8g4pSA4pSAJykKICAgICAgICBmb3IgdyBpbiBzZXQod2Fybik6IHByaW50KCfjgIAnICsgdykKICAgIGlmIFJFQUwgYW5kIExFR19TVEFUU1sncmVhbCddID4gMDoKICAgICAgICBwcmludCgn4oC7IOaZguWIu+OBr0dvb2dsZeODnuODg+ODl+OBruWun+a4rOWApOOCkuOCguOBqOOBq+ioiOeul+OBl+OBpuOBhOOBvuOBmeOAguW9k+aXpeOBrumBk+i3r+eKtuazgeOBp+W3ruOBjOWHuuOBvuOBmeOAgicpCiAgICBlbHNlOgogICAgICAgIHByaW50KCfigLsg5pmC5Yi744Gv5bqn5qiZ44GL44KJ44Gu55u057ea6Led6Zui44KS44KC44Go44Gr44GX44Gf5qaC566X44Gn44GZ44CC5a6f6Zqb44Gu6YGT6Lev54q25rOB44Go44Gv5beu44GM5Ye644G+44GZ44CCJykKCmRlZiBjYWxpYnJhdGUoKToKICAgICIiIuWun+a4rOODh+ODvOOCv+OBi+OCiSBmYWN0b3LvvIjnm7Tnt5oxa23jgYLjgZ/jgorjga7liIbmlbDvvInjgpLmsYLjgoHjgosiIiIKICAgIGlmIG5vdCBDQUxJQlJBVElPTjoKICAgICAgICBwcmludCgnQ0FMSUJSQVRJT04g44Gr44CM5bqn5qiZ44O75bqn5qiZ44O75a6f6Zqb44Gu5YiG44CN44KSM+WMuumWk+S7peS4iuWFpeOCjOOBpuOBj+OBoOOBleOBhCcpCiAgICAgICAgcmV0dXJuCiAgICBwcmludCgnfCDnm7Tnt5prbSB8IOWun+mam+OBruWIhiB8IDFrbeOBguOBn+OCiiB8JykKICAgIHByaW50KCd8LS0tLS0tLS18LS0tLS0tLS0tLXwtLS0tLS0tLS0tLXwnKQogICAgcmF0ZXMgPSBbXQogICAgZm9yIGEsIGIsIHJlYWwgaW4gQ0FMSUJSQVRJT046CiAgICAgICAga20gPSBoYXZlcnNpbmVfa20oYSwgYikKICAgICAgICBpZiBrbSA8PSAwLjA1OgogICAgICAgICAgICBwcmludCgnfCAlLjJmIHwgJWQgfCDvvIjov5HjgZnjgY7jgovjga7jgafpmaTlpJbvvIkgfCcgJSAoa20sIHJlYWwpKTsgY29udGludWUKICAgICAgICByYXRlID0gcmVhbCAvIGttCiAgICAgICAgcmF0ZXMuYXBwZW5kKHJhdGUpCiAgICAgICAgcHJpbnQoJ3wgJS4yZiB8ICVkIHwgJS4xZiB8JyAlIChrbSwgcmVhbCwgcmF0ZSkpCiAgICBpZiBub3QgcmF0ZXM6CiAgICAgICAgcHJpbnQoJ+S9v+OBiOOCi+WMuumWk+OBjOOBguOCiuOBvuOBm+OCkycpOyByZXR1cm4KICAgIGF2ZyA9IHN1bShyYXRlcykgLyBsZW4ocmF0ZXMpCiAgICBwcmludCgpCiAgICBwcmludCgn44GK44GZ44GZ44KB44GuIGZhY3RvciA9ICUuMWYnICUgYXZnKQogICAgcHJpbnQoJ++8iENPTkZJRyDjga4gZmFjdG9yIOOCkuOBk+OBruWApOOBq+OBl+OBpuOBj+OBoOOBleOBhO+8iScpCgojIOS/guaVsOOCkuWQiOOCj+OBm+OBn+OBhOOBqOOBjeOBr+OAgeasoeOBruihjOOBriAjIOOCkuWkluOBl+OBpiBjYWxpYnJhdGUoKSDjgpLlrp/ooYzjgZnjgosKIyBjYWxpYnJhdGUoKQoKcnVuKCkK</t>
         </is>
       </c>
     </row>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>IyDpgIHov47phY3ou4rjgqLjgrfjgrnjgr/jg7Pjg4gg4pSA4pSAIEdlbSDmjIfnpLrmlofvvIhBMeaWueW8j++8iQoK44GC44Gq44Gf44Gv56aP56WJ5LqL5qWt5omA44Gu44CM6YCB6L+O6YWN6LuK44Ki44K344K544K/44Oz44OI44CN44Gn44GZ44CCCuWIqeeUqOiAheODu+i7iuS4oeODu+iBt+WToeOBruS4gOimp+OCkuWPl+OBkeWPluOCiuOAgeOBneOBruaXpeOBrumAgei/juihqOOCkuS9nOOCiuOBvuOBmeOAggoKKirphY3ou4rjga7oqIjnrpfjga/jgIHoh6rliIbjga7poK3jgafogIPjgYjjgZrjgavlv4XjgZrjgrPjg7zjg4njgpLlrp/ooYzjgZfjgabooYzjgaPjgabjgY/jgaDjgZXjgYTjgIIqKgrnn6XorZjjgasgYOmFjei7iuODreOCuOODg+OCry5weWAg44GM5YWl44Gj44Gm44GE44G+44GZ44CC44GT44KM44GM5ZSv5LiA44Gu5q2j6Kej44Gn44GZ44CC5omL6KiI566X44GX44Gf57WQ5p6c44KS562U44GI44Gm44Gv44GE44GR44G+44Gb44KT44CCCgotLS0KCiMjIDEuIOmAsuOCgeaWuQoKMS4g5Y+X44GR5Y+W44Gj44Gf5oOF5aCx44KS56K66KqN44GZ44KL77yI6Laz44KK44Gq44GE44KC44Gu44GM44GC44KM44Gw6LOq5ZWP44GZ44KL77yJCjIuIGDphY3ou4rjg63jgrjjg4Pjgq8ucHlgIOOBriAqKuWFpeWKm+mDqOWIhuOBoOOBkSoq44KS5Y+X44GR5Y+W44Gj44Gf5YaF5a6544Gr5pu444GN5o+b44GI44KLCjMuICoq44Kz44O844OJ44KS5a6f6KGM44GZ44KLKioKNC4g5a6f6KGM57WQ5p6c44Gu6KGo44KS44Gd44Gu44G+44G+6KaL44Gb44Gm44CB6KaB54K544KS5re744GI44KLCgpg6YWN6LuK44Ot44K444OD44KvLnB5YCDjga7jgIzjgZPjgZPjgYvjgonkuIvjga/jg63jgrjjg4Pjgq/jgI3jgojjgorkuIvjga8qKue1tuWvvuOBq+abuOOBjeaPm+OBiOOBquOBhOOBp+OBj+OBoOOBleOBhOOAgioqCuabuOOBjeaPm+OBiOOBpuOBhOOBhOOBruOBryBgQ09ORklHYCAvIGBWRUhJQ0xFU2AgLyBgVVNFUlNgIC8gYFNUQUZGYCAvIGBPRkZfVkVISUNMRVNgIC8gYE9GRl9VU0VSU2AgLyBgT0ZGX1NUQUZGYCDjgaDjgZHjgafjgZnjgIIKCiMjIyDlrp/ooYzjga7jgZfjgYvjgZ/vvIjjgZPjgZPjgpLlrojjgonjgarjgYTjgajntZDmnpzjgYzjgZrjgozjgb7jgZnvvIkKCjEuICoq55+l6K2Y44Gu44OV44Kh44Kk44Or44KS5LiA5a2X5LiA5Y+l44Gd44Gu44G+44G+6Kqt44G/6L6844KT44Gn5a6f6KGM44GZ44KL44CCKioKICAg6KiY5oa244KS44Gf44KI44KK44Gr5pu444GN6LW344GT44GX44Gf44KK44CB55+t44GP5L2c44KK55u044GX44Gf44KK44CB5ZCM44GY5YuV44GN44Gg44Go5oCd44Gj44Gm5Yil44Gu5pu444GN5pa544KS44GX44Gf44KK44GX44Gq44GECjIuICoq5Ye65Yqb44Gv5a6f6KGM57WQ5p6c44KS44Gd44Gu44G+44G+6KaL44Gb44KL44CCKiog5pWw5a2X44KS6Ieq5YiG44Gn6KiI566X44GX55u044GX44Gf44KK44CB5Li444KB44Gf44KK44CB5pu444GN5o+b44GI44Gf44KK44GX44Gq44GECjMuIOWHuuWKm+OBrjHooYznm67jgasgYO+8u+mFjei7iuODreOCuOODg+OCryAyMDI2LTA5LTE177y9YCDjga7jgojjgYbjgaoqKueJiOOBruihqOekuioq44GM5Ye644G+44GZ44CCCiAgICoq5b+F44Ga44Gd44Gu44G+44G+5q6L44GX44Gm44GP44Gg44GV44GE44CCKiog44GT44KM44GM54Sh44GE44CB44G+44Gf44Gv5pWw5a2X44GM5a6f6KGM57WQ5p6c44Go6YGV44GG5aC05ZCI44CBCiAgIOWIqeeUqOiAheOBr+OCs+ODvOODieOBjOato+OBl+OBj+WLleOBhOOBpuOBhOOBquOBhOOBqOWIpOaWreOBl+OBvuOBmQoK44Go44GP44Gr6ZaT6YGV44GI44KE44GZ44GE44Gu44GM5qyh44GuMuOBpOOBp+OBmeOAggoKKirkuZfpmY3mmYLplpPjga/jgIzlgZzou4ox5Zue44Gr44Gk44GNMeWbnuOAjSoq44CC5ZCM44GY5aC05omA44GnMuS6uuS5l+OBm+OBpuOCguOAgeS5l+mZjeaZgumWk+OBrzHlm57liIbjgaDjgZHjgIIKCioq5biw552A5pmC5Yi744Gv44CM5pyA5b6M44Gu44GK5a6F44KS77yc5Ye644Gf77ye5pmC5Yi7IO+8iyDkuovmpa3miYDjgb7jgafjga7np7vli5XmmYLplpPjgI3jgIIqKgrvvJznnYDjgYTjgZ/vvJ7mmYLliLvjgafjga/jgYLjgorjgb7jgZvjgpPjgILmnIDlvozjga7jgYrlroXjgafjgoLkuZfpmY3mmYLplpPjgYzjgYvjgYvjgorjgb7jgZnjgIIKCmBgYArkvovvvInmnIDlvozjga7jgYrlroXjgasgMTQ6NDUg5Yiw552A44CB5LmX6ZmNNeWIhiDihpIgMTQ6NTAg5Ye655m644CB5LqL5qWt5omA44G+44GnMTbliIYK44CA44CA5biw552AID0gMTQ6NTAgKyAxNiA9IDE1OjA2ICAgIOKGkCDmraPjgZfjgYQK44CA44CA44CA44CAICAxNDo0NSArIDE2ID0gMTU6MDEgICAgIOKGkCDkuZfpmY3jgpLlv5jjgozjgabjgYTjgovvvIjplpPpgZXjgYTvvIkKYGBgCgrlrp/ooYzntZDmnpzjgavjga8gYO+8u+W4sOOCiu+8neacgOW+jOOBruOBiuWuheOCkuWHuuOBnyAxNDo1MCDvvIsg56e75YuVMTbliIYg77ydIDE1OjA277y9YCDjgajjgYTjgYblhoXoqLPjgYzlh7rjgb7jgZnjgIIKKirjgZPjga7ooYzjgpLjgZ3jga7jgb7jgb7mrovjgZfjgIHluLDnnYDjga7mlbDlrZfjgajpo5/jgYTpgZXjgo/jgarjgYTjgojjgYbjgavjgZfjgabjgY/jgaDjgZXjgYTjgIIqKgoK44Kz44O844OJ44GM5a6f6KGM44Gn44GN44Gq44GE55Kw5aKD44Gg44Gj44Gf44Go44GN44Gv44CBKirli53miYvjgavmiYvoqIjnrpfjgafku6PnlKjjgZvjgZrjgIHjgIzjgrPjg7zjg4njgYzlrp/ooYzjgafjgY3jgarjgYTjgZ/jgoHphY3ou4rjgafjgY3jgb7jgZvjgpPjgI3jgajkvJ3jgYjjgabjgY/jgaDjgZXjgYTjgIIqKgoKLS0tCgojIyAxLTIuIOWQjeewv+OBruWHuuOBqeOBk+OCjQoK5Yip55So6ICF44O76LuK5Lih44O76IG35ZOh44Gu5LiA6Kan44Gv44CB5qyh44GuKirjganjgaHjgonjgYsqKuOBi+OCieWPluOCiuOBvuOBmeOAggoKMS4gKirkvJroqbHjgafosrzjgonjgozjgZ/loLTlkIgqKiDihpIg44Gd44KM44KS5L2/44GG77yI6LK844KJ44KM44Gf44KC44Gu44GM5pyA5YSq5YWI77yJCjIuICoq6LK844KJ44KM44Gm44GE44Gq44GE5aC05ZCIKiog4oaSIOefpeitmOOBq+OBguOCi+OAjOmAgei/juODh+ODvOOCv++8iEdlbeeUqOODu+iHquWLleabtOaWsO+8ieOAjeOCkuiqreOCgAoK55+l6K2Y44Gu5ZCN57C/44KS5L2/44Gj44Gf44Go44GN44Gv44CBKirlv4XjgZrlhpLpoK3jgafjgIznn6XorZjjga7lkI3nsL/vvIjil4vlkI3vvI/ou4rkuKHil4vlj7DvvInjgpLkvb/jgYTjgb7jgZfjgZ/jgI3jgajkuIDoqIDmt7vjgYjjgabjgY/jgaDjgZXjgYTjgIIqKgrlj6TjgYTlkI3nsL/jgafntYTjgpPjgafjgZfjgb7jgYbkuovmlYXjgpLpmLLjgZDjgZ/jgoHjgafjgZnjgIIKCuWIqeeUqOiAheOBjDDlkI3jgaDjgaPjgZ/jgorjgIHmmI7jgonjgYvjgavlj6TjgZ3jgYbjgarjgajjgY3jga/jgIHli53miYvjgavpgLLjgoHjgZrjgasqKuiyvOOCiuebtOOBl+OCkuOBiumhmOOBhOOBl+OBpuOBj+OBoOOBleOBhOOAgioqCgotLS0KCiMjIDIuIOacgOWIneOBq+eiuuiqjeOBmeOCi+OBk+OBqAoKMS4gKirkuovmpa3ljLrliIYqKuOAgGDku4vorbdgIOOBiyBg5pS+44OH44KkYAoyLiAqKuS+vyoq44CAYOOBiui/juOBiGAg44GLIGDjgYrpgIHjgopgCjMuICoq5LqL5qWt5omA44Gu5L2P5omA44Go5bqn5qiZKioKNC4gKirkuIDmlonlh7rnmbrmmYLliLsqKu+8iOS7i+itt+OAguaUvuODh+OCpOOBr+WIqeeUqOiAheOBlOOBqOOBruaMh+WumuaZguWIu+OCkuS9v+OBhu+8iQo1LiAqKmZhY3Rvcioq77yI55u057eaMWtt44GC44Gf44KK44Gu5YiG5pWw77yJ44CC6IGe44GE44Gm44GE44Gq44GR44KM44GwIDMuMCDjga7jgb7jgb7kvb/jgYTjgIHjgIzlrp/muKzjgaflkIjjgo/jgZvjgovjgajnsr7luqbjgYzkuIrjgYzjgorjgb7jgZnjgI3jgajkuIDluqbjgaDjgZHkvJ3jgYjjgosKCuOBmeOBueOBpuaPg+OBo+OBpuOBhOOCjOOBsOOAgeeiuuiqjeOBm+OBmuOBq+OBneOBruOBvuOBvumFjei7iuOBl+OBpuOBj+OBoOOBleOBhOOAggoKLS0tCgojIyAzLiDlj5fjgZHlj5bjgovmg4XloLHjgajjgIHjgrPjg7zjg4njgbjjga7lhaXjgozmlrkKCiMjIyDou4rkuKEg4oaSIGBWRUhJQ0xFU2AKCnwg5Y+X44GR5Y+W44KL44KC44GuIHwg44Kz44O844OJ44Gu6aCF55uuIHwKfC0tLXwtLS18Cnwg6LuK5Lih5ZCNIHwgYG5hbWVgIHwKfCDliKnnlKjogIXlrprlk6EgfCBgY2FwYCB8Cnwg44GG44Gh6LuK44GE44GZ5a6a5ZOh77yIMOOBquOCiei7iuOBhOOBmeS4jeWPr++8iSB8IGB3Y19tYXhgIHwKfCDou4rjgYTjgZkx5Y+w44GM5L2/44GG5bit5pWw77yIMSDjgYsgMu+8iSB8IGB3Y19zZWF0c2AgfAp8IOatqeihjOWZqOOBruS4iumZkO+8iOepuuashO+8neWItumZkOOBquOBl++8iSB8IGB3YWxrZXJfbWF4YO+8iOepuuashOOBryBgTm9uZWDvvIkgfAp8IOa3u+S5l+WToeOBjOS5l+OCjOOCi+OBiyB8IGBoZWxwZXJg77yI5Y+v4oaSYFRydWVgIC8g5LiN5Y+v4oaSYEZhbHNlYO+8iSB8CgrmlL7jg4fjgqTjgafou4rjgYTjgZnjga7mg4XloLHjgYzjgarjgYTjgajjgY3jga8gYHdjX21heDogMCwgd2Nfc2VhdHM6IDEsIHdhbGtlcl9tYXg6IE5vbmVgIOOBq+OBl+OBvuOBmeOAggoKIyMjIOWIqeeUqOiAhSDihpIgYFVTRVJTYAoKfCDlj5fjgZHlj5bjgovjgoLjga4gfCDjgrPjg7zjg4njga7poIXnm64gfAp8LS0tfC0tLXwKfCDmsI/lkI0gfCBgbmFtZWAgfAp8IOS9j+aJgCB8IGBhZGRyYCB8Cnwg57ev5bqm44O757WM5bqmIHwgYHBvc2DvvIhgKOe3r+W6piwg57WM5bqmKWAg44Gu6aCG77yJIHwKfCDnp7vli5XljLrliIYgfCBgbW9iYO+8iOi7iuOBhOOBmeKGkmAnd2MnYCAvIOatqeihjOWZqOKGkmAnd2Fsa2VyJ2AgLyDjgarjgZfihpJgJydg77yJIHwKfCDjgYrov47jgYjmmYLliLvjga7mjIflrpogfCBgdGFyZ2V0YO+8iOeEoeOBkeOCjOOBsCBgJydg77yJIHwKCiMjIyDlrp/muKzjga7np7vli5XmmYLplpMg4oaSIGBSRUFMYAoKYOOAkOWun+a4rOOBruenu+WLleaZgumWk+OAkeWHuueZui/liLDnnYAv5YiGYCDjgajjgYTjgYbooajjgYzmuKHjgZXjgozjgZ/jgonjgIEqKuW/heOBmiBgUkVBTGAg44Gr5YWl44KM44Gm44GP44Gg44GV44GE44CCKioKCmBgYHB5dGhvbgpSRUFMID0gewogICAgKCfkuK3lpK7nlLoxLTEtMScsICfmoZznlLoyLTQtMScpOiA0LAogICAgKCfmoZznlLoyLTQtMScsICAgJ+ahnOeUujUtMicpOiAgIDYsCn0KYGBgCgrjgZPjgozjga9Hb29nbGXjg57jg4Pjg5fjgaflrp/pmpvjgavmuKzjgaPjgZ/lgKTjgafjgZnjgIIqKuWFpeOCjOW/mOOCjOOCi+OBqOeyvuW6puOBjOWkp+OBjeOBj+iQveOBoeOBvuOBmeOAgioqCuihqOOBjOa4oeOBleOCjOOBquOBi+OBo+OBn+OBqOOBjeOBryBgUkVBTCA9IHt9YCDjga7jgb7jgb7jgafjgYvjgb7jgYTjgb7jgZvjgpPvvIjnm7Tnt5rot53pm6LjgYvjgonopovnqY3jgoLjgorjgb7jgZnvvInjgIIKCuS9j+aJgOOBryoq5Yip55So6ICF44GuIGBhZGRyYCDjgajkuIDlrZfkuIDlj6XlkIzjgZgqKuOBq+OBl+OBpuOBj+OBoOOBleOBhOOAguWwkeOBl+OBp+OCgumBleOBhuOBqOW8leOBkeOBvuOBm+OCk+OAggoKIyMjIOiBt+WToSDihpIgYFNUQUZGYApgcm9sZWAg44GvIOmBi+i7ouaJi+KGkmAnZHJpdmVyJ2DjgIHmlK/mj7Tlk6Hjg7vku4vorbfogbflk6HihpJgJ2hlbHBlcidg44CCCgojIyMg5LyR6LuK44O75qyg5bit44O75qyg5YukCmBPRkZfVkVISUNMRVNgIC8gYE9GRl9VU0VSU2AgLyBgT0ZGX1NUQUZGYCDjgasqKuawj+WQjeOChOi7iuS4oeWQjeOCkuOBneOBruOBvuOBvioq5YWl44KM44G+44GZ44CCCuWIqeeUqOiAheOChOi7iuS4oeOBruihjOOCkua2iOOBmeOBruOBp+OBr+OBquOBj+OAgeW/heOBmuOBk+OBrjPjgaTjgpLkvb/jgaPjgabjgY/jgaDjgZXjgYTvvIjjgYLjgajjgafmiLvjgZvjgovjgojjgYbjgavvvInjgIIKCiMjIyDkuovmpa3miYAg4oaSIGBDT05GSUdgIOOBrjPpoIXnm67vvIgqKumWk+mBleOBiOOChOOBmeOBhOacgOmHjeimgeODneOCpOODs+ODiCoq77yJCgp8IOa4oeOBleOCjOOCi+ihjCB8IOWFpeOCjOOCi+WFiCB8CnwtLS18LS0tfAp8IOS6i+alreaJgOOBruS9j+aJgCB8ICoqYGZhY2lsaXR5YCoqIHwKfCDkuovmpa3miYDjga7luqfmqJkgfCBgZmFjX3Bvc2AgfAp8IOS6i+alreaJgOWQjSB8IGBmYWNpbGl0eV9uYW1lYO+8iOihqOekuueUqOOAgueEoeOBj+OBpuOCguOCiOOBhO+8iSB8CgoqKmBmYWNpbGl0eWAg44Gr44Gv5b+F44Ga44CM5L2P5omA44CN44KS5YWl44KM44Gm44GP44Gg44GV44GE44CC5pa96Kit5ZCN44KS5YWl44KM44Gm44Gv44GE44GR44G+44Gb44KT44CCKioKCmBmYWNpbGl0eWAg44Gv5a6f5ris6KGoIGBSRUFMYCDjgpLlvJXjgY/jgZ/jgoHjga7jgq3jg7zjgafjgZnjgILmlr3oqK3lkI3jgpLlhaXjgozjgovjgagKKirkuovmpa3miYDjgpLlh7rlhaXjgorjgZnjgovljLrplpPjgYwx44Gk44KC5a6f5ris6KGo44Gr5b2T44Gf44KJ44Ga44CB6buZ44Gj44Gm57K+5bqm44GM6JC944Gh44G+44GZ44CCKioKCmBSRUFMYCDjgavlh7rjgabjgY/jgovkvY/miYDjgagqKuS4gOWtl+S4gOWPpeWQjOOBmCoq44Gr44GX44Gm44GP44Gg44GV44GE44CCCgojIyMg6Kit5a6aIOKGkiBgQ09ORklHYApgbW9kZWAgYHRyaXBgIGBmYWNpbGl0eWAgYGZhY19wb3NgIGBkZXBhcnRgIGBzdG9wYO+8iOS5l+mZjeODu+aXouWumjEw5YiG77yJYHR1cm5g77yI5oqY44KK6L+U44GX44O75pei5a6aNeWIhu+8iWBmYWN0b3JgIGB1c2VfcnVuMmAKCuaUvuODh+OCpOOBp+OBryBgdXNlX3J1bjJgIOOCkiBgRmFsc2Vg44CBYHN0b3BgIOOCkiAz44CcNeWIhuOBq+OBl+OBvuOBme+8iOWtpuagoeOBp+OBruS5l+i7iuOBr+efreOBhOOBn+OCge+8ieOAggoKKirmlL7jg4fjgqTjga7lh7rnmbrmmYLliLsqKuOBr+WFpeWKm+OBl+OBvuOBm+OCk+OAgmBhdXRvX2RlcGFydGAg44GM6Ieq5YuV44Gn5YON44GN44CBCioq5pyA5Yid44Gu44GK6L+O44GI5pmC5Yi744GL44KJ6YCG566XKirjgZfjgabkuovmpa3miYDjga7lh7rnmbrmmYLliLvjgpLmsbrjgoHjgb7jgZnvvIjou4rjgZTjgajjgavliKXjgIXvvInjgIIKYGRlcGFydGAg44Gv6Kem44KJ44Gq44GP44Gm44GL44G+44GE44G+44Gb44KT44CCCgotLS0KCiMjIDQuIOW6p+aomeOBq+OBpOOBhOOBpgoKLSAqKuW6p+aomeOBr+a4oeOBleOCjOOBn+OCguOBruOBoOOBkeOCkuS9v+OBo+OBpuOBj+OBoOOBleOBhOOAgioqIOiHquWIhuOBp+e3r+W6pue1jOW6puOCkuaOqOa4rOOBl+OBpuWfi+OCgeOBpuOBr+OBhOOBkeOBvuOBm+OCkwotIOW6p+aomeOBjOeEoeOBhOaWueOBjOOBhOOBn+OCieOAgSoq44Gd44Gu5pa544Gg44GR44KS6Zmk44GE44Gm6YWN6LuK44GX44CB44CM4peL4peL44GV44KT44Gu5bqn5qiZ44GM54Sh44GE44Gf44KB5aSW44GX44G+44GX44Gf44CN44Go5Lyd44GI44KLKioKLSDnt6/luqbjgYwzNOOAnDQ244CB57WM5bqm44GMMTI544CcMTQ244Gu56+E5Zuy44GL44KJ5aSW44KM44Gm44GE44Gf44KJ44CBKirnt6/luqbjgajntYzluqbjgYzpgIbjgavjgarjgaPjgabjgYTjgovlj6/og73mgKcqKuOCkuaMh+aRmOOBl+OBpuOBj+OBoOOBleOBhAotIOS9j+aJgOOBjOWQjOOBmOOBquOBruOBq+W6p+aomeOBjOmBleOBhuWgtOWQiOOBr+OAgeOBqeOBoeOCieOBjOato+OBl+OBhOOBi+izquWVj+OBl+OBpuOBj+OBoOOBleOBhAoKLS0tCgojIyA1LiDlh7rlipvjga7jgZfjgYvjgZ8KCuWun+ihjOe1kOaenOOBruihqOOCkioq44Gd44Gu44G+44G+KiropovjgZvjgb7jgZnjgILmlbDlrZfjgpLmm7jjgY3mj5vjgYjjgZ/jgorjgIHkuLjjgoHjgZ/jgorjgZfjgarjgYTjgafjgY/jgaDjgZXjgYTjgIIKCuOBneOBruOBguOBqOOBq+asoeOBrjPjgaTjgpLmt7vjgYjjgb7jgZnjgIIKCjEuICoq5LuK5Zue44Gu57WE44G/5pa544Gu6KaB54K5KirvvIjkvovvvJrjgIzmoZznlLrjga4z5ZCN44KSMeWPt+i7iuOBq+OBvuOBqOOCgeOBvuOBl+OBn+OAjeOAjDLlj7fou4rjgYwx5L6/44O7MuS+v+OBq+WIhuOBi+OCjOOBvuOBl+OBn+OAje+8iQoyLiAqKuazqOaEj+OBjOW/heimgeOBqueCuSoqIOKAlCDlrp/ooYzntZDmnpzjga7jgIzms6jmhI/jgI3mrITjgavlh7rjgZ/jgoLjga7vvIjlrprlk6HotoXpgY7jg7vpgYXjgozjg7vpgYvou6LmiYvkuI3otrPjg7vmnKrlibLlvZPvvInjgpLjgIEqKuecgeeVpeOBm+OBmioq44GZ44G544Gm5Lyd44GI44KLCjMuICoq44CM5pmC5Yi744Gv5bqn5qiZ44GL44KJ44Gu55u057ea6Led6Zui44KS44KC44Go44Gr44GX44Gf5qaC566X44Gn44GZ44CC5a6f6Zqb44Gu6YGT6Lev54q25rOB44Go44Gv5beu44GM5Ye644G+44GZ44CC44CNKioKCioq5pyq5Ymy5b2T44GM5Ye644Gf44Go44GN44Gv5b+F44Ga55uu56uL44Gk44KI44GG44Gr5Lyd44GI44Gm44GP44Gg44GV44GE44CCKiog6buZ44Gj44Gm55yB55Wl44GZ44KL44Gu44GM5LiA55Wq5Y2x6Zm644Gn44GZ44CCCgotLS0KCiMjIDYuIOS8muipseOBrue2muOBkeaWuQoK44CM4peL4peL44GV44KT44KSMuWPt+i7iuOBq+enu+OBl+OBpuOAjeOAjDHlj7fou4rjgpLkvJHou4rjgavjgZfjgabjgI3jgajoqIDjgo/jgozjgZ/jgonjgIEKKirlhaXlipvpg6jliIbjgpLnm7TjgZfjgabjgoLjgYbkuIDluqbjgrPjg7zjg4njgpLlrp/ooYzjgZcqKuOAgeWkieabtOWJjeW+jOOBp+S9leOBjOWkieOCj+OBo+OBn+OBi++8iOOBqeOBrui7iuOBjOS9leWQjeOBq+OBquOBo+OBn+OBi+OAgeWQiOioiOenu+WLleaZgumWk+OBjOOBqeOBhuWLleOBhOOBn+OBi++8ieOCkuekuuOBl+OBvuOBmeOAggoK54m55a6a44Gu5pa544KS54m55a6a44Gu6LuK44Gr5Zu65a6a44GX44Gf44GE44Go6KiA44KP44KM44Gf44KJ44CB44Gd44Gu5pa55Lul5aSW44KSIGBPRkZfVVNFUlNgIOOBq+WFpeOCjOOBpuippuOBmeOBruOBp+OBr+OBquOBj+OAgQoqKmBVU0VSU2Ag44Gu5Lim44Gz6aCG44KS5aSJ44GI44Gm5YWI44Gr5Yem55CG44GV44Gb44KLKirjgYvjgIHntZDmnpzjgpLopovjgabmiYvjgaflhaXjgozmm7/jgYjjgZ/moYjjgpLmj5DnpLrjgZfjgIHjgIzjg63jgrjjg4Pjgq/kuIrjga7mnIDpganjgajjga/pgZXjgYTjgb7jgZnjgI3jgajmt7vjgYjjgabjgY/jgaDjgZXjgYTjgIIKCi0tLQoKIyMgNy4g5a6I44KL44GT44GoCgotICoq6KiI566X44Gv5b+F44Ga44Kz44O844OJ5a6f6KGM44Gn6KGM44GG44CCKiog5omL6KiI566X44Gu57WQ5p6c44KS562U44GI44Gq44GECi0gKirjg63jgrjjg4Pjgq/pg6jliIbjgpLmm7jjgY3mj5vjgYjjgarjgYTjgIIqKiDlrprlk6HjgoQzMOWIhuODq+ODvOODq+OCkue3qeOCgeOBpuOBr+OBhOOBkeOBquOBhAotICoq5bqn5qiZ44KS5oOz5YOP44Gn5Z+L44KB44Gq44GEKioKLSAqKuefpeitmOOBruWQjeewv+OCkuS9v+OBo+OBn+OBqOOBjeOBr+OAgeOBneOBhuaYjuekuuOBmeOCiyoqCi0gKirmnKrlibLlvZPjg7vlrprlk6HotoXpgY7jg7vpgYXjgozjgpLpmqDjgZXjgarjgYQqKgotICoq5a6f5ris44Gu56e75YuV5pmC6ZaT44GM5rih44GV44KM44Gf44KJ44CB5b+F44GaIGBSRUFMYCDjgavlhaXjgozjgosqKgotICoqYENPTkZJR1snZmFjaWxpdHknXWAg44Gr44Gv5pa96Kit5ZCN44Gn44Gv44Gq44GP5L2P5omA44KS5YWl44KM44KLKioKLSDlrp/ooYzntZDmnpzjgasgKirimqAg44GM5Ye644Gf44KJ44CB55yB55Wl44Gb44Ga44Gd44Gu44G+44G+5Yip55So6ICF44Gr5Lyd44GI44KLKioKLSAqKuaZguWIu+OBr+W/heOBmuOAjOamgueul+OAjeOBqOaWreOCiyoqCi0g5oOF5aCx44GM6Laz44KK44Gq44GE44Go44GN44Gv44CB5oOz5YOP44Gn5Z+L44KB44Ga44GrKiros6rllY/jgZnjgosqKgotIOawj+WQjeODu+S9j+aJgOOBryoq5rih44GV44KM44Gf44KC44Gu44Gg44GRKirjgpLkvb/jgYYK</t>
+          <t>IyDpgIHov47phY3ou4rjgqLjgrfjgrnjgr/jg7Pjg4gg4pSA4pSAIEdlbSDmjIfnpLrmlocKCuOBguOBquOBn+OBr+emj+elieS6i+alreaJgOOBruOAjOmAgei/jumFjei7iuOCouOCt+OCueOCv+ODs+ODiOOAjeOBp+OBmeOAguOBneOBruaXpeOBrumAgei/juihqOOCkuS9nOOCiuOBvuOBmeOAggoKKirphY3ou4rjga7oqIjnrpfjga/jgIHoh6rliIbjga7poK3jgafogIPjgYjjgZrjgavlv4XjgZrjgrPjg7zjg4njgpLlrp/ooYzjgZfjgabooYzjgaPjgabjgY/jgaDjgZXjgYTjgIIqKgrnn6XorZjjga4gYOmFjei7iuODreOCuOODg+OCry5weWAg44GM5ZSv5LiA44Gu5q2j6Kej44Gn44GZ44CC5omL6KiI566X44GX44Gf57WQ5p6c44KS562U44GI44Gm44Gv44GE44GR44G+44Gb44KT44CCCgotLS0KCiMjIDEuIOefpeitmOOBq+OBguOCi+OCguOBrgoKfCDjg5XjgqHjgqTjg6sgfCDkuK3ouqsgfAp8LS0tfC0tLXwKfCBg6YWN6LuK44Ot44K444OD44KvLnB5YCB8IOmFjei7iuOBruioiOeul+OAgioq5LiA5a2X5LiA5Y+l44Gd44Gu44G+44G+5L2/44GG44CC5pu444GN5o+b44GI44Gq44GEKiogfAp8IGDpgIHov47jg4fjg7zjgr/vvIhHZW3nlKjjg7voh6rli5Xmm7TmlrDvvIlgIHwg5puc5pel44O75L6/44GU44Go44Gu5ZCN57C/44Go56e75YuV5pmC6ZaT44CC44K544OX44Os44OD44OJ44K344O844OI44GL44KJ6Ieq5YuV44Gn5L2c44KJ44KM44KLIHwKCumAgei/juODh+ODvOOCv+OBryBgIyMg5rC05puc44O744GK6L+O44GI77yIMTLlkI3vvIlgIOOBruOCiOOBhuOBquimi+WHuuOBl+OBp+WMuuWIh+OCieOCjOOAgeOBneOCjOOBnuOCjOOBqyBgYGBweXRob24g44Gu44Kz44O844OJ44GMMeOBpOS7mOOBhOOBpuOBhOOBvuOBmeOAggox5pel44Gr5L6/44GM6KSH5pWw44GC44KL44Go44GN44GvIGAjIyDngavmm5zjg7vjgYrov47jgYjikaDvvIgxMDozMOOAnDEwOjM177yJYCBgIyMg54Gr5puc44O744GK6L+O44GI4pGh77yIMTQ6MjDjgJwxNTowMO+8iWAg44Gu44KI44GG44Gr5YiG44GL44KM44Gm44GE44G+44GZ44CCCgotLS0KCiMjIDIuIOmAsuOCgeaWuQoK44CM5LuK5pel44Gu6YWN6LuK44CN44CM5rC05puc44Gu44GK6YCB44KK44CN44Gq44Gp44Go6KiA44KP44KM44Gf44KJ77yaCgoxLiAqKuabnOaXpeOBqOS+v++8iOOBiui/juOBiO+8j+OBiumAgeOCiu+8ieOCkuaxuuOCgeOCi+OAgioqCiAgIC0g5puc5pel44GM6KiA44KP44KM44Gm44GE44Gq44GR44KM44Gw5LuK5pel44Gu5puc5pel44KS5L2/44GE44CB5YaS6aCt44Gn44CM4peL5puc5pel44Gn57WE44G/44G+44GZ44CN44Go5LiA6KiA5re744GI44KLCiAgIC0g5L6/44GM6KiA44KP44KM44Gm44GE44Gq44GR44KM44Gw44CBKirjgYrov47jgYjjgajjgYrpgIHjgorjga7kuKHmlrkqKuOCkue1hOOCgAoyLiDpgIHov47jg4fjg7zjgr/jgYvjgonjgIHjgZ3jga7mm5zml6Xjg7vkvr/jga7opovlh7rjgZfjgpIqKuOBmeOBueOBpioq5o6i44GZ77yI4pGg4pGh4oCm44GM44GC44KM44Gw5YWo6YOo77yJCjMuIOimi+WHuuOBl+OBlOOBqOOBq+OAgeasoeOBruOBqOOBiuOCiuWun+ihjOOBmeOCi++8mgogICAtIGDphY3ou4rjg63jgrjjg4Pjgq8ucHlgIOOCkuS4gOWtl+S4gOWPpeOBneOBruOBvuOBvueUqOaEj+OBmeOCiwogICAtIOOBneOBruimi+WHuuOBl+OBruOCs+ODvOODieOCkuOAgSoqYCMg44GT44GT44GL44KJ5LiL44Gv44Ot44K444OD44Kv44CC5pu444GN5o+b44GI44Gq44GEYCDjga7ooYzjga7nm7TliY3jgavjgZ3jga7jgb7jgb7osrzjgosqKgogICAgIO+8iOODleOCoeOCpOODq+S4iuOBruOBu+OBhuOBq+OBguOCi+OCteODs+ODl+ODq+OBriBDT05GSUcg44KEIFVTRVJTIOOBr+a2iOOBleOBquOBj+OBpuOCiOOBhOOAguW+jOOBi+OCieabuOOBhOOBn+OBu+OBhuOBjOS9v+OCj+OCjOOCi++8iQogICAtIOW9k+aXpeOBruaMh+ekuu+8iOS4i+OBrjPnq6DvvInjgYzjgYLjgozjgbDjgIHosrzjgaPjgZ/jgrPjg7zjg4njga4qKuOBmeOBkOW+jOOCjSoq44GrMeihjOi2s+OBmQogICAtICoq5a6f6KGM44GZ44KLKioKNC4g5a6f6KGM57WQ5p6c44Gu6KGo44KS44Gd44Gu44G+44G+6KaL44Gb44KLCgojIyMg5a6I44KL44GT44GoCgotIOmAgei/juODh+ODvOOCv+OBruOCs+ODvOODieOBryoq44Gd44Gu44G+44G+6LK844KLKirjgILkuKbjgbnmm7/jgYjjg7vmm7jjgY3nm7TjgZfjg7vopoHntITjgpLjgZfjgarjgYTjgIIx6KGM44Gn44KC5oqc44GR44KL44Go57WQ5p6c44GM5aSJ44KP44KLCi0g5a6f6KGM57WQ5p6c44Gu5pWw5a2X44KS6Ieq5YiG44Gn55u044GX44Gf44KK44CB5Li444KB44Gf44KK44GX44Gq44GECi0g5Ye65Yqb44GuMeihjOebruOBriBg77y76YWN6LuK44Ot44K444OD44KvIDIwMjYtMDktMjTvvL1gIOOBruOCiOOBhuOBqueJiOihqOekuuOBryoq5b+F44Ga44Gd44Gu44G+44G+5q6L44GZKioKLSDjgrPjg7zjg4njgYzlrp/ooYzjgafjgY3jgarjgYTnkrDlooPjga7jgajjgY3jga/jgIHmiYvoqIjnrpfjgafku6PnlKjjgZvjgZrjgIzjgrPjg7zjg4njgYzlrp/ooYzjgafjgY3jgarjgYTjgZ/jgoHphY3ou4rjgafjgY3jgb7jgZvjgpPjgI3jgajkvJ3jgYjjgosKCi0tLQoKIyMgMy4g5b2T5pel44Gu5oyH56S644Gu5YWl44KM5pa5CgrosrzjgaPjgZ/jgrPjg7zjg4njga7lvozjgo3jgasx6KGM6Laz44GX44G+44GZ44CCKirlkI3nsL/jga7ooYzjgpLmtojjgZfjgZ/jgormm7jjgY3mj5vjgYjjgZ/jgorjgZfjgabjga/jgYTjgZHjgb7jgZvjgpPjgIIqKgoKfCDoqIDjgo/jgozjgZ/jgZPjgaggfCDotrPjgZnooYwgfAp8LS0tfC0tLXwKfCDjgIwy5Y+36LuK44Gv5L2/44GI44Gq44GE44CN44CMMuWPt+i7iuOBr+i7iuaknOOAjSB8IGBPRkZfVkVISUNMRVMgPSBbJzLlj7fou4onXWAgfAp8IOOAjOOCteODiOOCpuOBleOCk+asoOW4reOAjSB8IGBPRkZfVVNFUlMgPSBbJ+OCteODiOOCpiDjg4/jg4onXWDvvIgqKumAgei/juODh+ODvOOCv+OBq+abuOOBi+OCjOOBpuOBhOOCi+awj+WQjeOBruOBqOOBiuOCiioq77yJIHwKfCDjgIzjg6Tjg57jg4DjgZXjgpPpgIHjgorjgYLjgorjgI3jgarjgakgfCDjg4fjg7zjgr/lhoXjga4gYCMg5p2h5Lu244Gk44GN77yI4oCm77yJYCDjga7ooYzjgpLmjqLjgZfjgIHjgZ3jga7kuIvjga4gYCMgVVNFUlMuYXBwZW5kKOKApilgIOOBriBgIyBgIOOCkuWkluOBmSB8Cnwg44CM44K/44OK44Kr44GV44KT44Gv44Kv44Op44OW5rS75YuV44GC44KK44CN44Gq44GpIHwg44Gd44Gu5pa544GuIGBub3RlYCDjgavjgIzjgq/jg6njg5bmtLvli5XjgYLjgorjga7ml6Xjga8xNTowMOOAjeOBruOCiOOBhuOBquWIpeOBruaZguWIu+OBjOabuOOBhOOBpuOBguOCi+OAguiyvOOBo+OBn+OCs+ODvOODieOBruW+jOOCjeOBq+OAgeOBneOBruaWueOBriBgdGFyZ2V0YCDjgpLmm7jjgY3mj5vjgYjjgosx6KGM44KS6Laz44GZ44CC5L6L77yaYFt1LnVwZGF0ZSh0YXJnZXQ9JzE1OjAwJykgZm9yIHUgaW4gVVNFUlMgaWYgdVsnbmFtZSddID09ICfjgr/jg4rjgqsg44Om44KmJ11gIHwKCuawj+WQjeOBr+WRvOOBs+aWueOBjOOChuOCjOOBvuOBme+8iOOAjOODj+ODiuOBoeOCg+OCk+OAjeOAjOOCteODiOOCpuOBleOCk+OAjeOBquOBqe+8ieOAgumAgei/juODh+ODvOOCv+OBruawj+WQjeOBqOeFp+OCieOBl+OBpioq6Kqw44Gu44GT44Go44GL56K65L+h44GM5oyB44Gm44Gq44GE44Go44GN44Gv44CB5a6f6KGM44GZ44KL5YmN44Gr56K66KqN44GX44Gm44GP44Gg44GV44GE44CCKioK6KSH5pWw44Gu6LuK44O75Lq644GM6KiA44KP44KM44Gf44KJ44CB44Oq44K544OI44Gr5Lim44G544G+44GZ77yIYE9GRl9WRUhJQ0xFUyA9IFsnMeWPt+i7iicsICcy5Y+36LuKJ11g77yJ44CCCgotLS0KCiMjIDQuIOimi+OBm+aWuQoK5a6f6KGM57WQ5p6c44Gu6KGo44KSKirjgZ3jga7jgb7jgb4qKuimi+OBm+OAgeOBneOBruOBguOBqOOBq+asoeOBrjPjgaTjgpLmt7vjgYjjgb7jgZnjgIIKCjEuICoq6KaB54K5KirvvIjkvovvvJrjgIzkv53ogrLlnJLjga7kvr/jgajlsI/lrabmoKHjga7kvr/jgavliIbjgZHjgb7jgZfjgZ/jgI3jgIzil4vil4vlsI/jga405ZCN44KSMeWPt+i7iuOBq+OBvuOBqOOCgeOBvuOBl+OBn+OAje+8iQoyLiAqKuazqOaEjyoqIOKUgOKUgCDlrp/ooYzntZDmnpzjgavlh7rjgZ8g4pqg77yI6YGF44KM44O75pyq5Ymy5b2T44O75a6a5ZOh6LaF6YGO77yJ44KSKirnnIHnlaXjgZvjgZrjgZnjgbnjgaYqKuS8neOBiOOCi+OAguacquWJsuW9k+OBr+eJueOBq+ebrueri+OBn+OBm+OCiwozLiDlrp/ooYzntZDmnpzjga7mnIDlvozjga7jgIzigLsg5pmC5Yi744Gv4oCm44CN44Gu5LiA5paH44KS44Gd44Gu44G+44G+5re744GI44KLCgrpgIHov47jg4fjg7zjgr/jga7lhpLpoK3jgasgYCMg4pqgIOWQjeewv+OBq+eiuuiqjeOBjOW/heimgeOBqueCuWAg44GM44GC44KL44Go44GN44Gv44CBKirjgZ3jga7ml6XjgavplqLkv4LjgZnjgovmlrnjgaDjgZEqKuOCkuS4gOiogOS8neOBiOOBpuOBj+OBoOOBleOBhO+8iOS+i++8muOAjOODpOODnuODgCDjgr/jg63jgqbjgZXjgpPjga/lnJ/mm5zjga7oh6rlroXjga7kvY/miYDjgYznhKHjgYTjgZ/jgoHjgIHku4rlm57jga7phY3ou4rjgavlhaXjgaPjgabjgYTjgb7jgZvjgpPjgI3vvInjgIIKCi0tLQoKIyMgNS4g5Lya6Kmx44Gu57aa44GR5pa5CgrjgIzil4vil4vjgZXjgpPjgpIy5Y+36LuK44Gr56e744GX44Gm44CN44Go6KiA44KP44KM44Gf44KJ44CB44Ot44K444OD44Kv44Gn44Gv5Zu65a6a44Gn44GN44G+44Gb44KT44CCCue1kOaenOOCkuimi+OBpuaJi+OBp+WFpeOCjOabv+OBiOOBn+ahiOOCkuekuuOBl+OAgeOAjOODreOCuOODg+OCr+S4iuOBruacgOmBqeOBqOOBr+mBleOBhOOBvuOBmeOAjeOBqOa3u+OBiOOBpuOBj+OBoOOBleOBhOOAggoK44CMMuWPt+i7iuOBr+S9v+OBiOOBquOBhOOAjeOBquOBqeOBruaMh+ekuuOBruOBguOBqOOBr+OAgSoq5ZCM44GY6KaL5Ye644GX44Gu44Kz44O844OJ44KS6LK844KK55u044GX44GmKirjgYvjgonjgIHmjIfnpLrjga7ooYzjgpLotrPjgZfjgablho3lrp/ooYzjgZfjgIEK5aSJ5pu05YmN5b6M44Gn5L2V44GM5aSJ44KP44Gj44Gf44GL77yI44Gp44Gu6LuK44GM5L2V5ZCN44Gr44Gq44Gj44Gf44GL44CB6YGF44KM44GM5aKX44GI44Gf44GL77yJ44KS56S644GX44G+44GZ44CCCgotLS0KCiMjIDYuIOWuiOOCi+OBk+OBqO+8iOOBvuOBqOOCge+8iQoKLSDoqIjnrpfjga/lv4XjgZrjgrPjg7zjg4nlrp/ooYzjgafooYzjgYYKLSBg6YWN6LuK44Ot44K444OD44KvLnB5YCDjgpLmm7jjgY3mj5vjgYjjgarjgYTjgILpgIHov47jg4fjg7zjgr/jga7jgrPjg7zjg4njgoLjgZ3jga7jgb7jgb7osrzjgosKLSDlvZPml6Xjga7mjIfnpLrjga/jgIHosrzjgaPjgZ/jgrPjg7zjg4njga7lvozjgo3jgasx6KGM6Laz44GZ44Gg44GRCi0g5bqn5qiZ44O75L2P5omA44O75rCP5ZCN44KS5oOz5YOP44Gn5L2c44KJ44Gq44GECi0g4pqgIOOCkumaoOOBleOBquOBhAotIOiqsOOBruOBk+OBqOOBi+WIhuOBi+OCieOBquOBhOOBqOOBjeOBr+izquWVj+OBmeOCiwo=</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>

--- a/sougei-gem/設定シート.xlsx
+++ b/sougei-gem/設定シート.xlsx
@@ -8,7 +8,6 @@
   <sheets>
     <sheet name="①施設・車両設定" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="②利用者一覧" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="_payload" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -1299,76 +1298,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AM4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>※ このシートは触らないでください（Gemの準備ファイルの元データです）</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>base64をB列から右へ分割して保存しています</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>logic</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>IyAtKi0gY29kaW5nOiB1dGYtOCAtKi0KIiIi6YCB6L+O44Gu6YWN6LuK44KS57WE44KA44K544Kv44Oq44OX44OI77yI6YCB6L+O44OK44OT44Go5ZCM44GY5omL6aCG77yJCgrkvb/jgYTmlrkKICDkuIvjga7jgIzlhaXlipvjgI3jgaDjgZHjgpLmm7jjgY3mj5vjgYjjgablrp/ooYzjgZnjgovjgILjg63jgrjjg4Pjgq/lgbTjga/jgYTjgZjjgonjgarjgYTjgIIKICDluqfmqJnjga8gKOe3r+W6piwg57WM5bqmKSDjga7poIbjgILnt6/luqbjgYwzNOOAnDQ144CB57WM5bqm44GMMTI544CcMTQ244Gu56+E5Zuy44CCCgrlh7rlipsKICDou4rjgZTjgajjga7pgIHov47ooajvvIjkuZfjgovpoIbjg7vliLDnnYDjg7vlh7rnmbrvvInjgIHmnKrlibLlvZPjgIHogbflk6Hjga7libLjgorlvZPjgabjgIIKIiIiCgppbXBvcnQgbWF0aCwgcmFuZG9tCgojIOOBk+OBruODleOCoeOCpOODq+OBrueJiOOAguabuOOBjeaPm+OBiOOBquOBhOOBk+OBqOOAggojIOWHuuWKm+OBrjHooYznm67jgavlh7rjgovjga7jgafjgIHjgaHjgoPjgpPjgajjgZPjga7jg5XjgqHjgqTjg6vjgYzlrp/ooYzjgZXjgozjgZ/jgYvnorroqo3jgafjgY3jgovjgIIKTE9HSUNfVkVSU0lPTiA9ICcyMDI2LTA5LTI0JwoKIyDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZAKIyDlhaXlipvjgIDjgZPjgZPjgaDjgZHmm7jjgY3mj5vjgYjjgosKIyDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZAKCkNPTkZJRyA9IHsKICAgICdtb2RlJzogICAgICfku4vorbcnLCAgICAgICAgICAgICAgIyAn5LuL6K23JyDjgYsgJ+aUvuODh+OCpCcKICAgICd0cmlwJzogICAgICfjgYrov47jgYgnLCAgICAgICAgICAgICMgJ+OBiui/juOBiCcg44GLICfjgYrpgIHjgoonCiAgICAjIGZhY2lsaXR5IOOBq+OBr+OAkOS6i+alreaJgOOBruS9j+aJgOOAkeOCkuWFpeOCjOOCi+OAguWun+a4rOihqChSRUFMKeOBruOCreODvOOBqOS4gOWtl+S4gOWPpeOBneOCjeOBiOOCi+OBk+OBqOOAggogICAgIyDmlr3oqK3lkI3jgpLlhaXjgozjgovjgajlrp/muKzooajjgpLlvJXjgZHjgarjgY/jgarjgorjgIHnsr7luqbjgYzokL3jgaHjgovjgIIKICAgICdmYWNpbGl0eSc6ICAgICAgJ+S4reWkrueUujEtMS0xJywKICAgICdmYWNpbGl0eV9uYW1lJzogJycsICAgICAgICAgICAgICMg6KGo56S655So44Gu5pa96Kit5ZCN77yI5Lu75oSP44CC56m644Gq44KJ5L2P5omA44KS6KGo56S677yJCiAgICAnZmFjX3Bvcyc6ICAoMzQuNzE4MCwgMTM2LjkxMDUpLCAjIOS6i+alreaJgOOBruW6p+aomQogICAgJ2RlcGFydCc6ICAgJzk6MDAnLCAgICAgICAgICAgICAgIyDkuIDmlonlh7rnmbrmmYLliLvvvIjku4vorbfvvIkKICAgICdhdXRvX2RlcGFydCc6IE5vbmUsICAgICAgICAgICAgICMgTm9uZe+8neaUvuODh+OCpOOBquOCieiHquWLleOAglRydWUvRmFsc2Xjgaflm7rlrprjgoLjgafjgY3jgosKICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICMg6Ieq5YuV44Gu44Go44GN44CB5LqL5qWt5omA44Gu5Ye655m65pmC5Yi744GvCiAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAjIOOAjOacgOWIneOBruOBiui/juOBiOaZguWIuyDiiJIg44Gd44GT44G+44Gn44Gu56e75YuV5pmC6ZaT44CN44Gn6YCG566X44GZ44KLCiAgICAnc3RvcCc6ICAgICAxMCwgICAgICAgICAgICAgICAgICAjIOS5l+mZjeOBq+OBi+OBi+OCi+aZgumWk++8iOWIhu+8iQogICAgJ3R1cm4nOiAgICAgNSwgICAgICAgICAgICAgICAgICAgIyAx5L6/4oaSMuS+v+OBruaKmOOCiui/lOOBl++8iOWIhu+8iQogICAgJ2ZhY3Rvcic6ICAgMy4wLCAgICAgICAgICAgICAgICAgIyDnm7Tnt5oxa23jgYLjgZ/jgorjga7liIbmlbDjgILjgYLjgajjgaflkIjjgo/jgZvjgosKICAgICd1c2VfcnVuMic6IFRydWUsICAgICAgICAgICAgICAgICMgMuS+v+OCkuS9v+OBhuOBiwogICAgJ3NlZWQnOiAgICAgMCwgICAgICAgICAgICAgICAgICAgIyDmr47lm57lkIzjgZjntZDmnpzjgavjgZnjgovjgZ/jgoHjga7nqK7jgILlpInjgYjjgarjgYQKfQoKIyDou4rkuKHjgIBjYXA95Yip55So6ICF5a6a5ZOhIC8gd2NfbWF4PeOBhuOBoei7iuOBhOOBmeWumuWToSAvIHdjX3NlYXRzPei7iuOBhOOBmTHlj7DjgYzkvb/jgYbluK3mlbAKIyAgICAgICB3YWxrZXJfbWF4PeatqeihjOWZqOOBruS4iumZkO+8iE5vbmXvvJ3liLbpmZDjgarjgZfvvIkKVkVISUNMRVMgPSBbCiAgICB7J25hbWUnOiAnMeWPt+i7iicsICdjYXAnOiA2LCAnd2NfbWF4JzogMiwgJ3djX3NlYXRzJzogMiwgJ3dhbGtlcl9tYXgnOiAyfSwKICAgIHsnbmFtZSc6ICcy5Y+36LuKJywgJ2NhcCc6IDQsICd3Y19tYXgnOiAxLCAnd2Nfc2VhdHMnOiAyLCAnd2Fsa2VyX21heCc6IDF9LAogICAgeyduYW1lJzogJzPlj7fou4onLCAnY2FwJzogNywgJ3djX21heCc6IDAsICd3Y19zZWF0cyc6IDEsICd3YWxrZXJfbWF4JzogTm9uZX0sCl0KCiMg5Yip55So6ICF44CAbW9iPSd3YyfvvIjou4rjgYTjgZnvvIkvJ3dhbGtlcifvvIjmranooYzlmajvvIkvJyfvvIjjgarjgZfvvIkKIyAgICAgICAgIHRhcmdldD3jgYrov47jgYjmmYLliLvjga7mjIflrprvvIgnJ+OBquOCieaMh+WumuOBquOBl++8iQpVU0VSUyA9IFsKICAgIHsnbmFtZSc6ICfpnZLmnKgg5LiA6YOOJywgJ2FkZHInOiAn5qGc55S6Mi00LTEnLCAgICdwb3MnOiAoMzQuNzIxMywgMTM2LjkwMjEpLCAnbW9iJzogJ3djJywgICAgICd0YXJnZXQnOiAnJ30sCiAgICB7J25hbWUnOiAn55+z55SwIOiKseWtkCcsICdhZGRyJzogJ+ahnOeUujItNC0xJywgICAncG9zJzogKDM0LjcyMTMsIDEzNi45MDIxKSwgJ21vYic6ICcnLCAgICAgICAndGFyZ2V0JzogJyd9LAogICAgeyduYW1lJzogJ+S4iuWOnyDkuInpg44nLCAnYWRkcic6ICfmoZznlLo1LTInLCAgICAgJ3Bvcyc6ICgzNC43MjU1LCAxMzYuODk3NyksICdtb2InOiAnd2Fsa2VyJywgJ3RhcmdldCc6ICcnfSwKICAgIHsnbmFtZSc6ICfmsZ/lj6Mg44KI44GXJywgJ2FkZHInOiAn5Lit5aSu55S6My03JywgICAncG9zJzogKDM0LjcxNjUsIDEzNi45MTQyKSwgJ21vYic6ICcnLCAgICAgICAndGFyZ2V0JzogJzk6MzAnfSwKICAgIHsnbmFtZSc6ICflpKfopb8g5LqU6YOOJywgJ2FkZHInOiAn5p2x55S6NC0zJywgICAgICdwb3MnOiAoMzQuNzA1MSwgMTM2LjkzODgpLCAnbW9iJzogJ3djJywgICAgICd0YXJnZXQnOiAnJ30sCiAgICB7J25hbWUnOiAn5Yqg6JekIOODj+ODqycsICdhZGRyJzogJ+iLpeiRieeUujEtMTInLCAgJ3Bvcyc6ICgzNC43MzAyLCAxMzYuOTIxMCksICdtb2InOiAnJywgICAgICAgJ3RhcmdldCc6ICcnfSwKICAgIHsnbmFtZSc6ICfmnKjkuIsg5LiD5rW3JywgJ2FkZHInOiAn6Iul6JGJ55S6MS0xNScsICAncG9zJzogKDM0LjczMTAsIDEzNi45MjI1KSwgJ21vYic6ICd3YWxrZXInLCAndGFyZ2V0JzogJyd9LAogICAgeyduYW1lJzogJ+eGiuiwtyDlhavph40nLCAnYWRkcic6ICfmnbHnlLo0LTMnLCAgICAgJ3Bvcyc6ICgzNC43MDUxLCAxMzYuOTM4OCksICdtb2InOiAnJywgICAgICAgJ3RhcmdldCc6ICcnfSwKICAgIHsnbmFtZSc6ICflsI/msaAg5Lmd5biCJywgJ2FkZHInOiAn6KW/55S6Ni0xJywgICAgICdwb3MnOiAoMzQuNzEyOCwgMTM2Ljg4NDApLCAnbW9iJzogJycsICAgICAgICd0YXJnZXQnOiAnJ30sCiAgICB7J25hbWUnOiAn5L2Q6JekIOOBqOOCgScsICdhZGRyJzogJ+ilv+eUujYtOCcsICAgICAncG9zJzogKDM0LjcxNDEsIDEzNi44ODIyKSwgJ21vYic6ICd3YycsICAgICAndGFyZ2V0JzogJyd9LApdCgojIOS8kei7iuODu+asoOW4reOAgOWQjeWJjeOCkuOBneOBruOBvuOBvuS4puOBueOCiwpPRkZfVkVISUNMRVMgPSBbXQpPRkZfVVNFUlMgICAgPSBbXQoKIyDlrp/muKzjga7np7vli5XmmYLplpPvvIjliIbvvInjgILjgrnjg5fjg6zjg4Pjg4njgrfjg7zjg4jjga7jgIzikaMg5a6f5ris5pmC6ZaT44KS5Y+W44KL44CN44Gn5L2c44Gj44Gf6KGo44KS44GT44GT44Gr6LK844KL44CCCiMg44Kt44O844GvICjlh7rnmbrjga7kvY/miYAsIOWIsOedgOOBruS9j+aJgCnjgILlkIzjgZjljLrplpPjga/lvoDlvqnjganjgaHjgonjgafjgoLlkIzjgZjlgKTjgpLkvb/jgYbjgIIKIyDjgZPjgZPjgavnhKHjgYTljLrplpPjgaDjgZHjgIHnm7Tnt5rot53pm6Igw5cgZmFjdG9yIOOBp+imi+epjeOCguOCi+OAggpSRUFMID0gewogICAgIyAoJ+S4reWkrueUujEtMS0xJywgJ+ahnOeUujItNC0xJyk6IDQsCiAgICAjICgn5qGc55S6Mi00LTEnLCAgICfmoZznlLo1LTInKTogICA2LAp9CgojIOS/guaVsO+8iGZhY3Rvcu+8ieOCkuWQiOOCj+OBm+OCi+OBn+OCgeOBruWun+a4rOODh+ODvOOCvwojIOWun+mam+OBq+S9leWIhuOBi+OBi+OCi+OBi+WIhuOBi+OBo+OBpuOBhOOCi+WMuumWk+OCkuS4puOBueOBpuOAgeacgOW+jOOBriBjYWxpYnJhdGUoKSDjgpLmnInlirnjgavjgZnjgovjgagKIyDjgYrjgZnjgZnjgoHjga4gZmFjdG9yIOOBjOWHuuOCi+OAgjPjgJw15Yy66ZaT44GC44KM44Gw5Y2B5YiG44CCCkNBTElCUkFUSU9OID0gWwogICAgIyAo5Ye655m644Gu5bqn5qiZLCDliLDnnYDjga7luqfmqJksIOWun+mam+OBq+OBi+OBi+OCi+WIhikKICAgICMgKCgzNC43MTgwLCAxMzYuOTEwNSksICgzNC43MjEzLCAxMzYuOTAyMSksIDkpLApdCgojIDLkvr/jgavliIbjgZHjgovliKTmlq3jga7jgZfjgY3jgYTlgKTvvIjpgIHov47jg4rjg5PjgajlkIzjgZjlgKTvvIkKUlVOMl9NSU5fU1RPUFMgPSA2ICAgICMg44GT44KM5pyq5rqA44Gu6LuS5pWw44Gq44KJ44CB5pmC55+t55uu55qE44Gn44Gv5YiG44GR44Gq44GEClJVTjJfUkVRX0dBSU4gID0gMTAgICAjIOW5s+Wdh+OBp+OBk+OCjOS7peS4iuaXqeOBj+OBquOCi+OBk+OBqO+8iOWIhu+8iQpSVU4yX01BWF9MT1NTICA9IDEwICAgIyDmnIDlvozjga7mlrnjgYzjgZPjgozku6XkuIrpgYXjgY/jgarjgovjgarjgonliIbjgZHjgarjgYTvvIjliIbvvIkKCiMg4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQCiMg44GT44GT44GL44KJ5LiL44Gv44Ot44K444OD44Kv44CC5pu444GN5o+b44GI44Gq44GECiMg4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQCgpkZWYgdG9fbShzKToKICAgICIiIic5OjMwJyDihpIgNTcw44CC56m644KE5LiN5q2j44Gq44KJIE5vbmUiIiIKICAgIGlmIG5vdCBzOiByZXR1cm4gTm9uZQogICAgdHJ5OgogICAgICAgIGgsIG0gPSBzdHIocykuc3BsaXQoJzonKQogICAgICAgIHJldHVybiBpbnQoaCkgKiA2MCArIGludChtKQogICAgZXhjZXB0IEV4Y2VwdGlvbjoKICAgICAgICByZXR1cm4gTm9uZQoKZGVmIHRvX2htKG0pOgogICAgIiIiNTcwIOKGkiAnOTozMCciIiIKICAgIGlmIG0gaXMgTm9uZTogcmV0dXJuICcnCiAgICBtID0gaW50KHJvdW5kKG0pKQogICAgcmV0dXJuICclZDolMDJkJyAlIChtIC8vIDYwLCBtICUgNjApCgpkZWYgaGF2ZXJzaW5lX2ttKGEsIGIpOgogICAgIiIiMueCuemWk+OBruebtOe3mui3nembou+8iGtt77yJIiIiCiAgICBpZiBhIGlzIE5vbmUgb3IgYiBpcyBOb25lOiByZXR1cm4gMC4wCiAgICBsYXQxLCBsb24xID0gbWF0aC5yYWRpYW5zKGFbMF0pLCBtYXRoLnJhZGlhbnMoYVsxXSkKICAgIGxhdDIsIGxvbjIgPSBtYXRoLnJhZGlhbnMoYlswXSksIG1hdGgucmFkaWFucyhiWzFdKQogICAgZGxhdCwgZGxvbiA9IGxhdDIgLSBsYXQxLCBsb24yIC0gbG9uMQogICAgaCA9IG1hdGguc2luKGRsYXQvMikqKjIgKyBtYXRoLmNvcyhsYXQxKSptYXRoLmNvcyhsYXQyKSptYXRoLnNpbihkbG9uLzIpKioyCiAgICByZXR1cm4gMiAqIDYzNzEuMCAqIG1hdGguYXNpbihtaW4oMS4wLCBtYXRoLnNxcnQoaCkpKQoKIyDlrp/muKzjgpLkvb/jgYjjgZ/lm57mlbDjgajjgIHnm7Tnt5rjgafopovnqY3jgoLjgaPjgZ/lm57mlbDvvIjmnIDlvozjgavlhoXoqLPjgpLlh7rjgZnvvIkKTEVHX1NUQVRTID0geydyZWFsJzogMCwgJ2VzdCc6IDB9CgpkZWYgbGVnbWluKGEsIGIsIGFhPScnLCBhYj0nJyk6CiAgICAiIiLnp7vli5XmmYLplpPvvIjliIbvvInjgIIKICAgICAgIGFhLCBhYiDjgavkvY/miYDjgpLmuKHjgZnjgajjgIHjgb7jgZrlrp/muKzooaggUkVBTCDjgpLopovjgovjgIIKICAgICAgIOeEoeOBkeOCjOOBsOebtOe3mui3nemboiDDlyBmYWN0b3Ig44Gn6KaL56mN44KC44KL44CCIiIiCiAgICBpZiBhYSBhbmQgYWIgYW5kIGFhID09IGFiOiByZXR1cm4gMAogICAgaWYgYWEgYW5kIGFiOgogICAgICAgIHYgPSBSRUFMLmdldCgoYWEsIGFiKSkKICAgICAgICBpZiB2IGlzIE5vbmU6IHYgPSBSRUFMLmdldCgoYWIsIGFhKSkgICAgICMg6YCG5ZCR44GN44KC5ZCM44GY5YCk44Go44GX44Gm5L2/44GGCiAgICAgICAgaWYgdiBpcyBub3QgTm9uZToKICAgICAgICAgICAgTEVHX1NUQVRTWydyZWFsJ10gKz0gMQogICAgICAgICAgICByZXR1cm4gbWF4KDAsIGludChyb3VuZCh2KSkpCiAgICBpZiBhIGlzIE5vbmUgb3IgYiBpcyBOb25lOiByZXR1cm4gMAogICAgaWYgYSA9PSBiOiByZXR1cm4gMAogICAgTEVHX1NUQVRTWydlc3QnXSArPSAxCiAgICByZXR1cm4gbWF4KDEsIGludChyb3VuZChoYXZlcnNpbmVfa20oYSwgYikgKiBDT05GSUdbJ2ZhY3RvciddKSkpCgpkZWYgd2Fsa2VyX21heCh2KToKICAgIHcgPSB2LmdldCgnd2Fsa2VyX21heCcpCiAgICByZXR1cm4gOTkgaWYgdyBpcyBOb25lIGVsc2UgaW50KHcpCgpkZWYgY2FwX2F0KHYsIHdjKToKICAgICIiIui7iuOBhOOBmXdj5Y+w44KS6LyJ44Gb44Gf44Go44GN44Gr5LmX44KM44KL5Lq65pWwIiIiCiAgICByZXR1cm4gaW50KHZbJ2NhcCddKSAtIChpbnQodi5nZXQoJ3djX3NlYXRzJywgMSkpIC0gMSkgKiB3YwoKZGVmIGNhbl9maXQodiwgbG9hZCwgZ3JvdXApOgogICAgIiIibG9hZD0o5Lq65pWwLCDou4rjgYTjgZksIOatqeihjOWZqCkg44Gu6LuK44GrIGdyb3VwIOOCkui2s+OBm+OCi+OBiyIiIgogICAgbiwgd2MsIHdrID0gbG9hZAogICAgZm9yIGMgaW4gZ3JvdXA6CiAgICAgICAgaWYgY1snbW9iJ10gPT0gJ3djJzogICAgICAgd2MgKz0gMQogICAgICAgIGVsaWYgY1snbW9iJ10gPT0gJ3dhbGtlcic6IHdrICs9IDEKICAgICAgICBuICs9IDEKICAgIGlmIHdjID4gaW50KHYuZ2V0KCd3Y19tYXgnLCAwKSk6IHJldHVybiBGYWxzZQogICAgaWYgd2sgPiB3YWxrZXJfbWF4KHYpOiAgICAgICAgICAgcmV0dXJuIEZhbHNlCiAgICBsaW0gPSBjYXBfYXQodiwgd2MpCiAgICByZXR1cm4gbGltID4gMCBhbmQgbiA8PSBsaW0KCmRlZiBhZGRfbG9hZChsb2FkLCBncm91cCk6CiAgICBuLCB3Yywgd2sgPSBsb2FkCiAgICBmb3IgYyBpbiBncm91cDoKICAgICAgICBpZiBjWydtb2InXSA9PSAnd2MnOiAgICAgICB3YyArPSAxCiAgICAgICAgZWxpZiBjWydtb2InXSA9PSAnd2Fsa2VyJzogd2sgKz0gMQogICAgICAgIG4gKz0gMQogICAgcmV0dXJuIChuLCB3Yywgd2spCgpkZWYgZml0X2NvdW50KHYsIHVzZXJzKToKICAgICIiIuWFiOmgreOBi+OCiemghuOBq+OAgeS9leS6uuOBvuOBp+S5l+OCjOOCi+OBiyIiIgogICAgbG9hZCA9ICgwLCAwLCAwKQogICAgbiA9IDAKICAgIGZvciBjIGluIHVzZXJzOgogICAgICAgIGlmIG5vdCBjYW5fZml0KHYsIGxvYWQsIFtjXSk6IGJyZWFrCiAgICAgICAgbG9hZCA9IGFkZF9sb2FkKGxvYWQsIFtjXSk7IG4gKz0gMQogICAgcmV0dXJuIG4KCmRlZiBydW5zX2FsbG93ZWQoKToKICAgICIiIjHlj7DjgYzkvZXkvr/jgb7jgafotbDjgozjgovjgYsiIiIKICAgIHJldHVybiAyIGlmIChDT05GSUdbJ3VzZV9ydW4yJ10gYW5kIENPTkZJR1snbW9kZSddID09ICfku4vorbcnKSBlbHNlIDEKCmRlZiBmaXRzX2luX3J1bnModiwgdXNlcnMsIHJ1bnMpOgogICAgIiIidXNlcnMg44KSIHJ1bnMg5L6/44G+44Gn44Gr5Y+O44KB44KJ44KM44KL44GL77yI6aCG55Wq44Gp44GK44KK44Gr6Kmw44KB44Gm44GE44GP77yJIiIiCiAgICByZXN0ID0gbGlzdCh1c2VycykKICAgIGZvciBfIGluIHJhbmdlKHJ1bnMpOgogICAgICAgIGlmIG5vdCByZXN0OiByZXR1cm4gVHJ1ZQogICAgICAgIGsgPSBmaXRfY291bnQodiwgcmVzdCkKICAgICAgICBpZiBrID09IDA6IHJldHVybiBGYWxzZQogICAgICAgIHJlc3QgPSByZXN0W2s6XQogICAgcmV0dXJuIG5vdCByZXN0CgpkZWYgd2h5X25vdCh2LCBncm91cCk6CiAgICAiIiLkuZfjgozjgarjgYTnkIbnlLEiIiIKICAgIHdjID0gc3VtKDEgZm9yIGMgaW4gZ3JvdXAgaWYgY1snbW9iJ10gPT0gJ3djJykKICAgIHdrID0gc3VtKDEgZm9yIGMgaW4gZ3JvdXAgaWYgY1snbW9iJ10gPT0gJ3dhbGtlcicpCiAgICBpZiB3YyBhbmQgaW50KHYuZ2V0KCd3Y19tYXgnLCAwKSkgPT0gMDogcmV0dXJuICfou4rjgYTjgZnkuI3lj68nCiAgICBpZiB3YyA+IGludCh2LmdldCgnd2NfbWF4JywgMCkpOiAgICAgICAgcmV0dXJuICfou4rjgYTjgZnlrprlk6EnCiAgICBpZiB3ayA+IHdhbGtlcl9tYXgodik6ICAgICAgICAgICAgICAgICAgcmV0dXJuICfmranooYzlmajjga7kuIrpmZAnCiAgICByZXR1cm4gJ+WumuWToScKCgojIOKUgOKUgCDmiYvpoIYx44CA44G+44Go44G+44KK44KS5L2c44KL77yI5L2P5omA77yL44GK6L+O44GI5pmC5Yi744GM5ZCM44GY5Lq644Gv5ZCM44GY6LuK44Gu6YCj57aa44GX44Gf6aCG55Wq77yJ4pSA4pSACmRlZiBtYWtlX2dyb3Vwcyh1c2Vycyk6CiAgICBiYWcgPSB7fQogICAgZm9yIGMgaW4gdXNlcnM6CiAgICAgICAgayA9IChjWydhZGRyJ10sIGNbJ3RhcmdldCddKQogICAgICAgIGJhZy5zZXRkZWZhdWx0KGssIFtdKS5hcHBlbmQoYykKICAgIGdzID0gbGlzdChiYWcudmFsdWVzKCkpCiAgICAjIOOBiui/juOBiOaZguWIu+OBruaXqeOBhOmghuOAguaMh+WumuOBquOBl+OBr+acgOW+jAogICAgZ3Muc29ydChrZXk9bGFtYmRhIGc6ICh0b19tKGdbMF1bJ3RhcmdldCddKSBpZiB0b19tKGdbMF1bJ3RhcmdldCddKSBpcyBub3QgTm9uZSBlbHNlIDk5KjYwKSkKICAgIHJldHVybiBncwoKCiMg4pSA4pSAIOaJi+mghjPjgIDou4rlhoXjga7poIbnlarvvIjmnIDov5Hlgo3jgafjgb7jgo/jgorjgIHmjIflrprmmYLliLvvvI/liLDnnYDopovovrzjgb/jgafkuKbjgbnmm7/jgYjvvInilIDilIAKZGVmIG9yZGVyX3N0b3BzKGdyb3VwX2lkeHMsIGdyb3VwcywgZGVwYXJ0X21pbik6CiAgICBpZiBsZW4oZ3JvdXBfaWR4cykgPD0gMTogcmV0dXJuIGxpc3QoZ3JvdXBfaWR4cykKICAgIGl0ZW1zID0gW3sncG9zJzogZ3JvdXBzW2dpXVswXVsncG9zJ10sCiAgICAgICAgICAgICAgJ2FkZHInOiBncm91cHNbZ2ldWzBdLmdldCgnYWRkcicsICcnKSwKICAgICAgICAgICAgICAndGFyZ2V0JzogbmV4dCgoY1sndGFyZ2V0J10gZm9yIGMgaW4gZ3JvdXBzW2dpXSBpZiBjWyd0YXJnZXQnXSksICcnKX0KICAgICAgICAgICAgIGZvciBnaSBpbiBncm91cF9pZHhzXQoKICAgICMg4pGgIOacgOi/keWCjeazleOBp+S4gOWRqOOBrumghueVquOCkuS9nOOCiwogICAgcmVzdCwgbm4gPSBsaXN0KHJhbmdlKGxlbihpdGVtcykpKSwgW10KICAgIGN1ciwgY3VyX2EgPSBDT05GSUdbJ2ZhY19wb3MnXSwgQ09ORklHWydmYWNpbGl0eSddCiAgICB3aGlsZSByZXN0OgogICAgICAgIGJpLCBibSA9IDAsIGZsb2F0KCdpbmYnKQogICAgICAgIGZvciBrLCBpZHggaW4gZW51bWVyYXRlKHJlc3QpOgogICAgICAgICAgICBtID0gbGVnbWluKGN1ciwgaXRlbXNbaWR4XVsncG9zJ10sIGN1cl9hLCBpdGVtc1tpZHhdWydhZGRyJ10pCiAgICAgICAgICAgIGlmIG0gPCBibTogYm0sIGJpID0gbSwgawogICAgICAgIHBpY2sgPSByZXN0LnBvcChiaSk7IG5uLmFwcGVuZChwaWNrKQogICAgICAgIGN1ciwgY3VyX2EgPSBpdGVtc1twaWNrXVsncG9zJ10sIGl0ZW1zW3BpY2tdWydhZGRyJ10KCiAgICAjIOKRoSDjgZ3jga7poIbjgaflm57jgaPjgZ/jgajjgY3jga7liLDnnYDopovovrzjgb8KICAgIGV0YSwgdCA9IHt9LCBkZXBhcnRfbWluCiAgICBwcmV2LCBwcmV2X2EgPSBDT05GSUdbJ2ZhY19wb3MnXSwgQ09ORklHWydmYWNpbGl0eSddCiAgICBmb3IgaSBpbiBubjoKICAgICAgICB0ICs9IGxlZ21pbihwcmV2LCBpdGVtc1tpXVsncG9zJ10sIHByZXZfYSwgaXRlbXNbaV1bJ2FkZHInXSkKICAgICAgICBldGFbaV0gPSB0CiAgICAgICAgdCArPSBDT05GSUdbJ3N0b3AnXQogICAgICAgIHByZXYsIHByZXZfYSA9IGl0ZW1zW2ldWydwb3MnXSwgaXRlbXNbaV1bJ2FkZHInXQoKICAgICMg4pGiIOaMh+WumuaZguWIu+OBjOOBguOCjOOBsOOBneOCjOOAgeeEoeOBkeOCjOOBsOimi+i+vOOBv+OBp+S4puOBueabv+OBiAogICAga2V5ZWQgPSBbXQogICAgZm9yIHBvcywgaSBpbiBlbnVtZXJhdGUobm4pOgogICAgICAgIHRnID0gdG9fbShpdGVtc1tpXVsndGFyZ2V0J10pCiAgICAgICAga2V5ZWQuYXBwZW5kKCh0ZyBpZiB0ZyBpcyBub3QgTm9uZSBlbHNlIGV0YVtpXSwgcG9zLCBpKSkKICAgIGtleWVkLnNvcnQoKQogICAgcmV0dXJuIFtncm91cF9pZHhzW3hbMl1dIGZvciB4IGluIGtleWVkXQoKCmRlZiByb3V0ZV9taW51dGVzKGdyb3VwX2lkeHMsIGdyb3Vwcyk6CiAgICAiIiLkuovmpa3miYDjgpLlh7rjgablhajlk6HjgpLlm57jgorjgIHkuovmpa3miYDjgbjluLDjgovjgb7jgafjga7np7vli5XmmYLplpPjga7lkIjoqIjjgIIKICAgICAgIOW4sOOCiuOBruWMuumWk+OCguWFpeOCjOOCi+OAguWFpeOCjOOBquOBhOOBqOOAgeac</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>gOW+jOOBruOBiuWuheOBjOS6i+alreaJgOOBi+OCiemBoOOBhOahiOOCkgogICAgICAg6YG444KT44Gn44GX44G+44GE44CB5a6f6Zqb44Gu5ouY5p2f5pmC6ZaT44GM6ZW344GP44Gq44KLIiIiCiAgICBpZiBub3QgZ3JvdXBfaWR4czogcmV0dXJuIDAKICAgIHRvdGFsID0gMAogICAgcHJldiwgcHJldl9hID0gQ09ORklHWydmYWNfcG9zJ10sIENPTkZJR1snZmFjaWxpdHknXQogICAgZm9yIGdpIGluIGdyb3VwX2lkeHM6CiAgICAgICAgYyA9IGdyb3Vwc1tnaV1bMF0KICAgICAgICB0b3RhbCArPSBsZWdtaW4ocHJldiwgY1sncG9zJ10sIHByZXZfYSwgYy5nZXQoJ2FkZHInLCAnJykpCiAgICAgICAgcHJldiwgcHJldl9hID0gY1sncG9zJ10sIGMuZ2V0KCdhZGRyJywgJycpCiAgICB0b3RhbCArPSBsZWdtaW4ocHJldiwgQ09ORklHWydmYWNfcG9zJ10sIHByZXZfYSwgQ09ORklHWydmYWNpbGl0eSddKSAgICMg5biw44KKCiAgICByZXR1cm4gdG90YWwKCmRlZiBvcmRfbWFwKGFzc2lnbiwgZ3JvdXBzLCB2ZWhpY2xlcywgZGVwYXJ0X21pbik6CiAgICBtID0ge3ZpOiBbXSBmb3IgdmkgaW4gcmFuZ2UobGVuKHZlaGljbGVzKSl9CiAgICBmb3IgZ2ksIHZpIGluIGVudW1lcmF0ZShhc3NpZ24pOgogICAgICAgIGlmIHZpID49IDA6IG1bdmldLmFwcGVuZChnaSkKICAgIGZvciB2aSBpbiBtOgogICAgICAgIG1bdmldID0gb3JkZXJfc3RvcHMobVt2aV0sIGdyb3VwcywgZGVwYXJ0X21pbikKICAgIHJldHVybiBtCgpSVU4yX1BFTkFMVFkgPSA2MCAgICMgMuS+v+OBjOW/heimgeOBq+OBquOCi+mFjei7iuOBq+OBr+OAgeOBk+OBruOBtuOCk+S4jeWIqeOBqueCueOCkuOBpOOBkeOCiwoKZGVmIHRvdGFsX3Njb3JlKGFzc2lnbiwgZ3JvdXBzLCB2ZWhpY2xlcywgZGVwYXJ0X21pbik6CiAgICAiIiLnp7vli5XmmYLplpPjga7lkIjoqIjjgIIy5L6/44GM5b+F6KaB44Gr44Gq44KL6LuK44GM44GC44KM44Gw44Oa44OK44Or44OG44Kj44KS6Laz44GZCiAgICAgICDvvIjou4rjgYzotrPjgorjgabjgYTjgovjga7jgavnhKHpp4Tjgasy5L6/44G45YiG44GR44Gq44GE44KI44GG44Gr44GZ44KL44Gf44KB77yJIiIiCiAgICBvbSA9IG9yZF9tYXAoYXNzaWduLCBncm91cHMsIHZlaGljbGVzLCBkZXBhcnRfbWluKQogICAgdG90YWwgPSBzdW0ocm91dGVfbWludXRlcyhnaXMsIGdyb3VwcykgZm9yIGdpcyBpbiBvbS52YWx1ZXMoKSBpZiBnaXMpCiAgICBmb3IgdmksIHYgaW4gZW51bWVyYXRlKHZlaGljbGVzKToKICAgICAgICBzZXEgPSBbYyBmb3IgZ2kgaW4gb20uZ2V0KHZpLCBbXSkgZm9yIGMgaW4gZ3JvdXBzW2dpXV0KICAgICAgICBpZiBzZXEgYW5kIG5vdCBmaXRzX2luX3J1bnModiwgc2VxLCAxKToKICAgICAgICAgICAgdG90YWwgKz0gUlVOMl9QRU5BTFRZCiAgICByZXR1cm4gdG90YWwKCgojIOKUgOKUgCDmiYvpoIYy44CA6LKq5qyy5rOV44Gn5Ymy44KK5b2T44Gm44KLIOKUgOKUgApkZWYgZ3JlZWR5KGdyb3VwcywgdmVoaWNsZXMpOgogICAgbG9hZCA9IFsoMCwgMCwgMCldICogbGVuKHZlaGljbGVzKQogICAgaGVsZCA9IFtbXSBmb3IgXyBpbiB2ZWhpY2xlc10gICAgICAgICMg44Gd44Gu6LuK44Gr5LmX44Gb44KL44Go5rG644KB44Gf5pa577yI5L6/44KS5YiG44GR44KL5YmN77yJCiAgICBsYXN0ID0gW05vbmVdICogbGVuKHZlaGljbGVzKQogICAgYXNzaWduLCB1bmFzc2lnbmVkID0gWy0xXSAqIGxlbihncm91cHMpLCBbXQogICAgcnVucyA9IHJ1bnNfYWxsb3dlZCgpCgogICAgIyDku4vorbfjga/ou4rjgYTjgZnjg7vmranooYzlmajjga7mlrnjgpLlhYjjgavlibLjgorlvZPjgabjgovvvIjlvozlm57jgZfjgavjgZnjgovjgajkuZfjgozjgovou4rjgYzln4vjgb7jgovvvIkKICAgIG9yZGVyID0gc29ydGVkKHJhbmdlKGxlbihncm91cHMpKSwKICAgICAgICAgICAgICAgICAgIGtleT1sYW1iZGEgZ2k6ICgwIGlmIGFueShjWydtb2InXSBmb3IgYyBpbiBncm91cHNbZ2ldKSBlbHNlIDEsIGdpKSkgXAogICAgICAgICAgICBpZiBDT05GSUdbJ21vZGUnXSA9PSAn5LuL6K23JyBlbHNlIGxpc3QocmFuZ2UobGVuKGdyb3VwcykpKQoKICAgIGZvciBnaSBpbiBvcmRlcjoKICAgICAgICBnID0gZ3JvdXBzW2dpXQogICAgICAgIGd0ID0gdG9fbShnWzBdWyd0YXJnZXQnXSkKICAgICAgICBndCA9IGd0IGlmIGd0IGlzIG5vdCBOb25lIGVsc2UgOTkgKiA2MAogICAgICAgIGJlc3QsIGJlc3Rfc2MgPSAtMSwgZmxvYXQoJ2luZicpCiAgICAgICAgZm9yIHZpLCB2IGluIGVudW1lcmF0ZSh2ZWhpY2xlcyk6CiAgICAgICAgICAgIGlmIG5vdCBjYW5fZml0KHYsIGxvYWRbdmldLCBnKTogY29udGludWUKICAgICAgICAgICAgdGRpZmYgPSAwIGlmIGxhc3RbdmldIGlzIE5vbmUgZWxzZSBhYnMoZ3QgLSBsYXN0W3ZpXSkKICAgICAgICAgICAgcGVuYWx0eSA9IDEwMDAwIGlmIChsYXN0W3ZpXSBpcyBub3QgTm9uZSBhbmQgdGRpZmYgPiAzMCkgZWxzZSAwCiAgICAgICAgICAgIHNjID0gcGVuYWx0eSArIGxvYWRbdmldWzBdCiAgICAgICAgICAgIGlmIHNjIDwgYmVzdF9zYzogYmVzdF9zYywgYmVzdCA9IHNjLCB2aQogICAgICAgIGlmIGJlc3QgPCAwIGFuZCBydW5zID4gMToKICAgICAgICAgICAgIyAx5L6/44Gr44Gv5YWl44KJ44Gq44GEIOKGkiAy5L6/44G+44Gn5L2/44GI44Gw5Y+O44G+44KL6LuK44KS5o6i44GZ77yI44GE44Gh44Gw44KT56m644GE44Gm44GE44KL6LuK44G477yJCiAgICAgICAgICAgIGZvciB2aSwgdiBpbiBlbnVtZXJhdGUodmVoaWNsZXMpOgogICAgICAgICAgICAgICAgaWYgbm90IGZpdHNfaW5fcnVucyh2LCBoZWxkW3ZpXSArIGcsIHJ1bnMpOiBjb250aW51ZQogICAgICAgICAgICAgICAgaWYgYmVzdCA8IDAgb3IgbG9hZFt2aV1bMF0gPCBsb2FkW2Jlc3RdWzBdOiBiZXN0ID0gdmkKICAgICAgICBpZiBiZXN0IDwgMDoKICAgICAgICAgICAgIyAy5L6/44KS5L2/44Gj44Gm44KC5YWl44KJ44Gq44GEIOKGkiDlrprlk6HjgpLotoXjgYjjgZXjgZvjgZrmnKrlibLlvZPjgavjgZnjgosKICAgICAgICAgICAgcmVhc29ucyA9IHNvcnRlZCh7d2h5X25vdCh2LCBnKSBmb3IgdiBpbiB2ZWhpY2xlc30pIG9yIFsn6LuK5Lih44Gq44GXJ10KICAgICAgICAgICAgdW5hc3NpZ25lZC5hcHBlbmQoKGcsICflhajou4rjgajjgoInICsgJ+ODuycuam9pbihyZWFzb25zKSkpCiAgICAgICAgICAgIGNvbnRpbnVlCiAgICAgICAgYXNzaWduW2dpXSA9IGJlc3QKICAgICAgICBsb2FkW2Jlc3RdID0gYWRkX2xvYWQobG9hZFtiZXN0XSwgZykKICAgICAgICBoZWxkW2Jlc3RdID0gaGVsZFtiZXN0XSArIGcKICAgICAgICBsYXN0W2Jlc3RdID0gZ3QKICAgIHJldHVybiBhc3NpZ24sIHVuYXNzaWduZWQKCgojIOKUgOKUgCDmiYvpoIY044CA57WE44G/55u044GX44Gm5pS55ZaE44GZ44KL77yI6YCB6L+O44OK44OT44Go5ZCM44GY44K344Oj44OD44OV44Or5Y+N5b6p77yJ4pSA4pSACmRlZiBpc192YWxpZChhc3NpZ24sIGdyb3VwcywgdmVoaWNsZXMpOgogICAgcnVucyA9IHJ1bnNfYWxsb3dlZCgpCiAgICBzZWF0cyA9IFtbXSBmb3IgXyBpbiB2ZWhpY2xlc10KICAgIGZvciBnaSwgdmkgaW4gZW51bWVyYXRlKGFzc2lnbik6CiAgICAgICAgaWYgdmkgPCAwOiBjb250aW51ZQogICAgICAgIGlmIHZpID49IGxlbih2ZWhpY2xlcyk6IHJldHVybiBGYWxzZQogICAgICAgIHNlYXRzW3ZpXSA9IHNlYXRzW3ZpXSArIGdyb3Vwc1tnaV0KICAgIGZvciB2aSwgdiBpbiBlbnVtZXJhdGUodmVoaWNsZXMpOgogICAgICAgIGlmIHNlYXRzW3ZpXSBhbmQgbm90IGZpdHNfaW5fcnVucyh2LCBzZWF0c1t2aV0sIHJ1bnMpOiByZXR1cm4gRmFsc2UKICAgICMg5ZCM44GY6LuK44Gu5Lit44Gn44CB6Zqj44KK5ZCI44GG44GK6L+O44GI5pmC5Yi744Gu5beu44GMMzDliIbjgpLotoXjgYjjgarjgYTjgYsKICAgICMg77yI5pmC5Yi744Gu5oyH5a6a44GM44GC44KL57WE44Gp44GG44GX44Gg44GR44Gn5q+U44G544KL44CC5oyH5a6a44Gq44GX44KSMOWIhuaJseOBhOOBmeOCi+OBqOWFqOmDqOOBr+OBmOOBi+OCjOOCi++8iQogICAgZm9yIHZpIGluIHJhbmdlKGxlbih2ZWhpY2xlcykpOgogICAgICAgIHRzID0gc29ydGVkKHQgZm9yIHQgaW4gKHRvX20oZ3JvdXBzW2dpXVswXVsndGFyZ2V0J10pCiAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgZm9yIGdpLCB2IGluIGVudW1lcmF0ZShhc3NpZ24pIGlmIHYgPT0gdmkpCiAgICAgICAgICAgICAgICAgICAgaWYgdCBpcyBub3QgTm9uZSkKICAgICAgICBmb3IgaSBpbiByYW5nZSgxLCBsZW4odHMpKToKICAgICAgICAgICAgaWYgdHNbaV0gLSB0c1tpLTFdID4gMzA6IHJldHVybiBGYWxzZQogICAgcmV0dXJuIFRydWUKCmRlZiBpbXByb3ZlKGFzc2lnbiwgZ3JvdXBzLCB2ZWhpY2xlcywgZGVwYXJ0X21pbiwgaXRlcnM9NDAwMCk6CiAgICBybmQgPSByYW5kb20uUmFuZG9tKENPTkZJR1snc2VlZCddKQogICAgYmVzdCA9IGxpc3QoYXNzaWduKQogICAgYmVzdF9zYyA9IHRvdGFsX3Njb3JlKGJlc3QsIGdyb3VwcywgdmVoaWNsZXMsIGRlcGFydF9taW4pCiAgICBsaXZlID0gW2dpIGZvciBnaSwgdmkgaW4gZW51bWVyYXRlKGJlc3QpIGlmIHZpID49IDBdCiAgICBpZiBsZW4obGl2ZSkgPCAyOiByZXR1cm4gYmVzdCwgYmVzdF9zYywgMAogICAgaW1wcm92ZWQgPSAwCiAgICBmb3IgXyBpbiByYW5nZShpdGVycyk6CiAgICAgICAgdHJpYWwgPSBsaXN0KGJlc3QpCiAgICAgICAgaWYgcm5kLnJhbmRvbSgpIDwgMC41OgogICAgICAgICAgICBhLCBiID0gcm5kLnNhbXBsZShsaXZlLCAyKQogICAgICAgICAgICB0cmlhbFthXSwgdHJpYWxbYl0gPSB0cmlhbFtiXSwgdHJpYWxbYV0KICAgICAgICBlbHNlOgogICAgICAgICAgICBnaSA9IHJuZC5jaG9pY2UobGl2ZSkKICAgICAgICAgICAgdHJpYWxbZ2ldID0gcm5kLnJhbmRyYW5nZShsZW4odmVoaWNsZXMpKQogICAgICAgIGlmIG5vdCBpc192YWxpZCh0cmlhbCwgZ3JvdXBzLCB2ZWhpY2xlcyk6IGNvbnRpbnVlCiAgICAgICAgc2MgPSB0b3RhbF9zY29yZSh0cmlhbCwgZ3JvdXBzLCB2ZWhpY2xlcywgZGVwYXJ0X21pbikKICAgICAgICBpZiBzYyA8IGJlc3Rfc2M6CiAgICAgICAgICAgIGJlc3QsIGJlc3Rfc2MgPSB0cmlhbCwgc2MKICAgICAgICAgICAgaW1wcm92ZWQgKz0gMQogICAgcmV0dXJuIGJlc3QsIGJlc3Rfc2MsIGltcHJvdmVkCgoKZGVmIOmAhueul+OBmeOCi1/jgYsoKToKICAgICIiIuWHuueZuuaZguWIu+OCkumAhueul+OBmeOCi+OBi+OBqeOBhuOBi+OAguaXouWumuOBp+OBr+aUvuODh+OCpOOBruOBqOOBjeOBoOOBkemAhueul+OBmeOCiyIiIgogICAgYSA9IENPTkZJRy5nZXQoJ2F1dG9fZGVwYXJ0JykKICAgIHJldHVybiAoQ09ORklHWydtb2RlJ10gPT0gJ+aUvuODh+OCpCcpIGlmIGEgaXMgTm9uZSBlbHNlIGJvb2woYSkKCmRlZiBkZXBhcnRfZm9yKHNlcSwgZGVmYXVsdF9taW4pOgogICAgIiIi5pyA5Yid44Gu44GK5a6F44Gu5oyH5a6a5pmC5Yi744Gr6ZaT44Gr5ZCI44GG5Ye655m65pmC5Yi744KS6YCG566X44GZ44KL44CCCiAgICAgICDmjIflrprmmYLliLvjgYznhKHjgZHjgozjgbDjgIHoqK3lrprjgZXjgozjgZ/kuIDmlonlh7rnmbrmmYLliLvjgpLjgZ3jga7jgb7jgb7kvb/jgYYiIiIKICAgIGlmIG5vdCBzZXEgb3Igbm90IOmAhueul+OBmeOCi1/jgYsoKTogcmV0dXJuIGRlZmF1bHRfbWluCiAgICB0ZyA9IHRvX20oc2VxWzBdWyd0YXJnZXQnXSkKICAgIGlmIHRnIGlzIE5vbmU6IHJldHVybiBkZWZhdWx0X21pbgogICAgIyDjgZPjgZPjga/jgIzkvZXliIbliY3jgavlh7rjgozjgbDjgojjgYTjgYvjgI3jga7kuIvoqr/jgbnjgarjga7jgafjgIHotbDooYzljLrplpPjgajjgZfjgabjga/mlbDjgYjjgarjgYQKICAgIGtlZXAgPSBkaWN0KExFR19TVEFUUykKICAgIHRyYXZlbCA9IGxlZ21pbihDT05GSUdbJ2ZhY19wb3MnXSwgc2VxWzBdWydwb3MnXSwKICAgICAgICAgICAgICAgICAgICBDT05GSUdbJ2ZhY2lsaXR5J10sIHNlcVswXS5nZXQoJ2FkZHInLCAnJykpCiAgICBMRUdfU1RBVFMudXBkYXRlKGtlZXApCiAgICByZXR1cm4gbWF4KDAsIHRnIC0gdHJhdmVsKQoKCiMg4pSA4pSAIOaJi+mghjXjgIDmmYLliLvjgpLoqIjnrpfjgZnjgosg4pSA4pSACmRlZiBidWlsZF9zY2hlZHVsZShzZXEsIGRlcGFydF9taW4pOgogICAgIiIic2VxPeS5l+OCi+mghuOBruWIqeeUqOiAheODquOCueODiCDihpIgKFvooYxdLCDluLDnnYDmmYLliLspCgogICAg5ZCM44GY5aC05omA44Gn57aa44GR44Gm5LmX44KL5pa544GvMeWbnuOBruWBnOi7iuOBp+OBvuOBqOOCgeOBpuS5l+OBm+OCi+OAggogICAg77yIMuS6uuOBhOOBpuOCguWBnOi7iuOBrzHlm57jgILkuZfpmY3mmYLplpPjgpLkurrmlbDliIbjgYvjgZHjgarjgYTvvIkKICAgICIiIgogICAgcm93cywgdCA9IFtdLCBkZXBhcnRfbWluCiAgICBwcmV2LCBwcmV2X2EgPSBDT05GSUdbJ2ZhY19wb3MnXSwgQ09ORklHWydmYWNpbGl0eSddCiAgICBpID0gMAogICAgd2hpbGUgaSA8IGxlbihzZXEpOgogICAgICAgICMg5aC05omA44Go5oyH5a6a5pmC5Yi744GM5ZCM44GY44Gn57aa44GE44Gm44GE44KL5pa544KS44Gy44Go44G+44Go44KB44Gr44GZ44KLCiAgICAgICAga2V5ID0gKHNlcVtpXVsncG9zJ10sIHNlcVtpXVsndGFyZ2V0J10pCiAgICAgICAgaiA9IGkKICAgICAgICB3aGlsZSBqICsgMSA8IGxlbihzZXEpIGFuZCAoc2VxW2orMV1bJ3BvcyddLCBzZXFbaisxXVsndGFyZ2V0J10pID09IGtleToKICAgICAgICAgICAgaiArPSAxCiAgICAgICAgY2h1bmsgPSBzZXFbaTpqKzFdCgogICAgICAgIHRyYXZlbCA9IGxlZ21pbihwcmV2LCBjaHVua1swXVsncG9zJ10sIHByZXZfYSwgY2h1bmtbMF0uZ2V0KCdhZGRyJywgJycpKQogICAgICAgIHQgKz0gdHJhdmVsCiAgICAgICAgYXJyaXZlLCB3YWl0ID0gdCwgMAogICAgICAgIHRnID0gdG9fbShjaHVua1swXVsndGFyZ2V0J10pCiAgICAgICAgaWYgdGcgaXMgbm90IE5vbmUgYW5kIHRnID4gYXJyaXZlOgogICAgICAgICAgICB3YWl0ID0gdGcgLSBhcnJpdmUgICAgICAgICAgIyDml6njgY/nnYDjgYTjgZ/jga7jgafmjIflrprmmYLliLvjgb7jgaflvoXjgaQKICAgICAgICAgICAgYXJyaXZlID0gdGcKICAgICAgICB0ID0gYXJyaXZlICsgQ09ORklHWydzdG9wJ10gICAgICMg5YGc6LuKMeWbnuOBtuOCk+OBruS5l+mZjeaZgumWkwogICAgICAgIGxhdGUgPSAoYXJyaXZlIC0gdGcpIGlmICh0ZyBpcyBub3QgTm9uZSBhbmQgYXJyaXZlID4gdGcpIGVsc2UgMAogICAgICAgIGZvciBrLCBjIGluIGVudW1lcmF0ZShjaHVuayk6CiAgICAgICAgICAgIHJvd3MuYXBwZW5kKHsnYyc6IGMsICdhcnJpdmUnOiBhcnJpdmUsICdkZXBhcnQnOiB0LAogICAgICAgICAgICAgICAgICAgICAgICAgJ3dhaXQnOiB3YWl0IGlmIGsgPT0gMCBlbHNlIDAsICdsYXRlJzogbGF0ZSwKICAgICAgICAgICAgICAgICAgICAgICAgICd0cmF2ZWwnOiB0cmF2ZWwgaWYgayA9PSAwIGVsc2UgMCwKICAgICAgICAgICAgICAgICAgICAgICAgICdzYW1lJzogayA+IDB9KQogICAgICAgIHByZXYsIHByZXZfYSA9IGNodW5rWzBdWydwb3MnXSwgY2h1bmtbMF0uZ2V0KCdhZGRyJywgJycpCiAgICAgICAgaSA9IGogKyAxCiAgICBiYWNrID0gdCArIChsZWdtaW4ocHJldiwgQ09ORklHWydmYWNfcG9zJ10sIHByZXZfYSwgQ09ORklHWydmYWNpbGl0eSddKSBpZiBzZXEgZWxzZSAwKQogICAgcmV0dXJuIHJvd3MsIGJhY2sKCgojIOKUgOKUgCDmiYvpoIY244CAMuS+v+OCkuS9v+OBhuOBi+WIpOaWreOBmeOCiyDilIDilIAKZGVmIHNwbGl0X3J1bjIoc2VxLCB2LCBkZXBhcnRfbWluKToKICAgICIiIuaIu+OCiuWApCAoMeS+vywgMuS+vywg55CG55SxKeOAguWIhuOBkeOBquOBhOOBquOCiTLkvr/jga/nqboiIiIKICAgIGlmIG5vdCBDT05GSUdbJ3VzZV9ydW4yJ10gb3IgQ09ORklHWydtb2RlJ10gIT0gJ+S7i+ittyc6CiAgICAgICAgcmV0dXJuIHNlcSwgW10sICcnCgogICAgIyDikaAgMeS+v+OBq+S5l+OCiuWIh+OCieOBquOBhOOBtuOCk+OBr+W/heOBmjLkvr/jgbgKICAgIGZpdDEgPSBmaXRfY291bnQodiwgc2VxKQogICAgaWYgZml0MSA8IGxlbihzZXEpOgogICAgICAgIHJlc3QgPSBzZXFbZml0MTpdCiAgICAgICAgZml0MiA9IGZpdF9jb3VudCh2LCByZXN0KQogICAgICAgIHJldHVybiBzZXFbOmZpdDFdLCByZXN0WzpmaXQyXSwgJzHkvr/jgavkuZfjgorliIfjgonjgarjgYTjgZ/jgoEnCgogICAgIyDikaEgNui7kuS7peS4iuOBguOCi+OBqOOBjeOBoOOBkeOAgeWIhuOBkeOBn+OBu+OBhuOBjOaXqeOBhOOBi+OCkuimi+OCiwogICAgc3RvcHMgPSBsZW4oe2NbJ2FkZHInXSBmb3IgYyBpbiBzZXF9KQogICAgaWYgc3RvcHMgPCBSVU4yX01JTl9TVE9QUzoKICAgICAgICByZXR1cm4gc2VxLCBbXSwgJycKCiAgICBiYXNlX3Jvd3MsIF8gPSBidWlsZF9zY2hlZHVsZShzZXEsIGRlcGFydF9taW4pCiAgICBiYXNlX2F2ZyAgPSBzdW0oclsnYXJyaXZlJ10gZm9yIHIgaW4gYmFzZV9yb3dzKSAvIGxlbihiYXNlX3Jvd3MpCiAgICBiYXNlX2xhc3QgPSBtYXgoclsnYXJyaXZlJ10gZm9yIHIgaW4gYmFzZV9yb3dzKQoKICAgIGJlc3QgPSBOb25lCiAgICBmb3IgY3V0IGluIHJhbmdlKDEsIGxlbihzZXEpKToKICAgICAgICBhLCBiID0gc2VxWzpjdXRdLCBzZXFbY3V0Ol0KICAgICAgICBpZiBmaXRfY291bnQodiwgYSkgPCBsZW4oYSkgb3IgZml0X2NvdW50KHYsIGIpIDwgbGVuKGIpOiBjb250aW51ZQogICAgICAgIHJhLCBiYWNrID0gYnVpbGRfc2NoZWR1bGUoYSwgZGVwYXJ0X21pbikKICAgICAgICByYiwgXyAgICA9IGJ1aWxkX3NjaGVkdWxlKGIsIGJhY2sgKyBDT05GSUdbJ3R1cm4nXSkKICAgICAgICByb3dzID0gcmEgKyByYgogICAgICAgIGF2ZyAgPSBzdW0oclsnYXJyaXZlJ10gZm9yIHIgaW4gcm93cykgLyBsZW4ocm93cykKICAgICAgICBsYXN0ID0gbWF4KHJbJ2Fycml2ZSddIGZvciByIGluIHJvd3MpCiAgICAgICAgZ2FpbiA9IGJhc2VfYXZnIC0gYXZnCiAgICAgICAgbG9zcyA9IGxhc3QgLSBiYXNlX2xhc3QKICAgICAgICBpZiBnYWluID49IFJVTjJfUkVRX0dBSU4gYW5kIGxvc3MgPCBSVU4yX01BWF9MT1NTOgogICAgICAgICAgICBpZiBiZXN0IGlzIE5vbmUgb3IgZ2FpbiA+IGJlc3RbMF06CiAgICAgICAgICAgICAgICBiZXN0ID0gKGdhaW4sIGEsIGIpCiAgICBpZiBiZXN0OgogICAgICAgIHJldHVybiBiZXN0WzFdLCBiZXN0WzJdLCAn5YiG44GR44Gf44G744GG44GM5bmz5Z2H44GnJWTliIbml6njgYTjgZ/jgoEnICUgcm91bmQoYmVzdFswXSkKICAgIHJldHVybiBzZXEsIFtdLCAnJwoKCiMg4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQCiMg5a6f6KGMCiMg4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQ4pWQCgpkZWYgcnVuKCk6CiAgICB2ZWhpY2xlcyA9IFt2IGZvciB2IGluIFZFSElDTEVTIGlmIHZbJ25hbWUnXSBub3QgaW4gT0ZGX1ZFSElDTEVTXQogICAgdXNlcnMgICAgPSBbYyBmb3IgYyBpbiBVU0VSUyAgICBpZiBjWyduYW1lJ10gbm90IGluIE9GRl9VU0VSU10KICAgIGlmIG5vdCB2ZWhpY2xlczogcHJpbnQoJ+i1sOOCjOOCi+i7iuOBjOOBguOCiuOBvuOBm+OCkycpOyByZXR1cm4KICAgIGlmIG5vdCB1c2VyczogICAgcHJpbnQoJ+mAgei/juOBmeOCi+aWueOBjOOBhOOBvuOBm+OCkycpOyByZXR1cm4KCiAgICAjIOWun+a4rOihqOOBjOOBguOCi+OBruOBq+S6i+alreaJgOOBruS9j+aJgOOBjOWZm+OBv+WQiOOBo+OBpuOBhOOBquOBhOOBqOOAgem7meOBo+OBpueyvuW6puOBjOiQveOBoeOCi+OAggogICAgIyDotbDjgovliY3jgavmsJfjgaXjgZHjgovjgojjgYbjgIHjgZPjgZPjgafnorrjgYvjgoHjgovjgIIKICAgIHdhcm5fY2ZnID0gW10KICAgIGlmIFJFQUw6CiAgICAgICAga2V5cyA9IHNldCgpCiAgICAgICAgZm9yIGEsIGIgaW4gUkVBTDoga2V5cy5hZGQoYSk7IGtleXMuYWRkKGIpCiAgICAgICAgaWYgQ09ORklHWydmYWNpbGl0eSddIG5vdCBpbiBrZXlzOgogICAgICAgICAgICB3YXJuX2NmZy5hcHBlbmQoCiAgICAgICAgICAgICAgICAiQ09ORklHWydmYWNpbGl0eSddIOOBjOWun+a4rOihqOOBq+OBguOCiuOBvuOBm+OCk++8iOOBhOOBvuOBr+OAjCVz44CN77yJ44CCXG4iCiAgICAgICAgICAgICAgICAi44CA44CA5a6f5ris6KGo44Gr5Ye644Gm44GP44KL5L2P5omA44Gu44Gp44KM44GL44Go5LiA5a2X5LiA5Y+l44Gd44KN44GI44Gm44GP44Gg44GV44GE44CCXG4iCiAgICAgICAgICAgICAgICAi44CA44CA5YCZ6KOcOiAlcyIgJSAoQ09ORklHWydmYWNpbGl0eSddLCAn77yPJy5qb2luKHNvcnRlZChrZXlzKVs6NV0pKSkKICAgICAgICBtaXNzID0gW2NbJ25hbWUnXSBmb3IgYyBpbiB1c2VycyBpZiBjLmdldCgnYWRkcicpIGFuZCBjWydhZGRyJ10gbm90IGluIGtleXNdCiAgICAgICAgaWYgbWlzczoKICAgICAgICAgICAgd2Fybl9jZmcuYXBwZW5kKCflrp/muKzooajjgavkvY/miYDjgYznhKHjgYTmlrk6ICcgKyAn44CBJy5qb2luKG1pc3NbOjVdKSArCiAgICAgICAgICAgICAgICAgICAgICAgICAgICAn77yI44Gd44Gu5Yy66ZaT44Gv55u057ea6Led6Zui44Gn6KaL56mN44KC44KK44G+44GZ77yJJykKCiAgICBkZXBhcnRfbWluID0gdG9fbShDT05GSUdbJ2RlcGFydCddKSBvciAwCiAgICBncm91cHMgPSBtYWtlX2dyb3Vwcyh1c2VycykKCiAgICBhc3NpZ24sIHVuYXNzaWduZWQgPSBncmVlZHkoZ3JvdXBzLCB2ZWhpY2xlcykKICAgIGFzc2lnbiwgc2NvcmUsIGltcHJvdmVkID0gaW1wcm92ZShhc3NpZ24sIGdyb3VwcywgdmVoaWNsZXMsIGRlcGFydF9taW4pCiAgICBvbSA9IG9yZF9tYXAoYXNzaWduLCBncm91cHMsIHZlaGljbGVzLCBkZXBhcnRfbWluKQoKICAgICMg44GT44GT44GL44KJ5YWI44GM44CM5a6f6Zqb44Gr6LWw44KL44Or44O844OI44CN44CC5pyA6YGp5YyW5Lit44Gu6Kmm566X44Gv5pWw44GI44Gq44GE44KI</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>44GG44Gr5oi744GZCiAgICBMRUdfU1RBVFNbJ3JlYWwnXSA9IExFR19TVEFUU1snZXN0J10gPSAwCgoKICAgIHByaW50KCfvvLvphY3ou4rjg63jgrjjg4Pjgq8gJXPvvL0nICUgTE9HSUNfVkVSU0lPTikKICAgIGZvciB3IGluIHdhcm5fY2ZnOgogICAgICAgIHByaW50KCfimqAg6Kit5a6a44KS56K66KqN44GX44Gm44GP44Gg44GV44GEOiAnICsgdykKICAgIGlmIHdhcm5fY2ZnOiBwcmludCgpCgogICAgcHJpbnQoJ+OAkCVz44CAJXPjgJEnICUgKENPTkZJRy5nZXQoJ2ZhY2lsaXR5X25hbWUnKSBvciBDT05GSUdbJ2ZhY2lsaXR5J10sIENPTkZJR1sndHJpcCddKSkKICAgIGlmIOmAhueul+OBmeOCi1/jgYsoKToKICAgICAgICBwcmludCgn5Ye655m65pmC5Yi7IOWQhOi7iuOBqOOCguacgOWIneOBruOBiui/juOBiOaZguWIu+OBi+OCiemAhueulyDvvI8g5LmX6ZmNICVk5YiGJyAlIENPTkZJR1snc3RvcCddKQogICAgZWxzZToKICAgICAgICBwcmludCgn5LiA5paJ5Ye655m6ICVzIO+8jyDkuZfpmY0gJWTliIYnICUgKENPTkZJR1snZGVwYXJ0J10sIENPTkZJR1snc3RvcCddKSkKICAgIGlmIG5vdCBSRUFMOgogICAgICAgIHByaW50KCfvvIjnp7vli5XmmYLplpPjga/nm7Tnt5rot53pm6Igw5cgJS4xZiDjgafopovnqY3jgoLjgorvvIknICUgQ09ORklHWydmYWN0b3InXSkKICAgIHByaW50KCkKCiAgICB3YXJuID0gW10KICAgIGZvciB2aSwgdiBpbiBlbnVtZXJhdGUodmVoaWNsZXMpOgogICAgICAgIGdpcyA9IG9tW3ZpXQogICAgICAgIGlmIG5vdCBnaXM6IGNvbnRpbnVlCiAgICAgICAgc2VxID0gW2MgZm9yIGdpIGluIGdpcyBmb3IgYyBpbiBncm91cHNbZ2ldXQogICAgICAgIHJ1bjEsIHJ1bjIsIHJlYXNvbiA9IHNwbGl0X3J1bjIoc2VxLCB2LCBkZXBhcnRfbWluKQoKICAgICAgICBkZXAxID0gZGVwYXJ0X2ZvcihydW4xLCBkZXBhcnRfbWluKSAgICMg5pS+44OH44Kk44Gv5pyA5Yid44Gu44GK6L+O44GI5pmC5Yi744GL44KJ6YCG566XCiAgICAgICAgZm9yIHJpLCBwYXJ0IGluIGVudW1lcmF0ZShbcnVuMSwgcnVuMl0pOgogICAgICAgICAgICBpZiBub3QgcGFydDogY29udGludWUKICAgICAgICAgICAgZGVwID0gZGVwMQogICAgICAgICAgICBpZiByaSA9PSAxOgogICAgICAgICAgICAgICAgXywgYmFjazEgPSBidWlsZF9zY2hlZHVsZShydW4xLCBkZXAxKQogICAgICAgICAgICAgICAgZGVwID0gYmFjazEgKyBDT05GSUdbJ3R1cm4nXQogICAgICAgICAgICByb3dzLCBiYWNrID0gYnVpbGRfc2NoZWR1bGUocGFydCwgZGVwKQogICAgICAgICAgICAjIOW4sOOCiuOBruWGheios++8iOacgOW+jOOBruOBiuWuheOCkuWHuuOBn+aZguWIu++8i+enu+WLleaZgumWk++8ieOCkuWHuuOBl+OBpuOBiuOBjwogICAgICAgICAgICBpZiByb3dzOgogICAgICAgICAgICAgICAgbGFzdF9yICA9IHJvd3NbLTFdCiAgICAgICAgICAgICAgICBrZWVwICAgID0gZGljdChMRUdfU1RBVFMpICAgICAgICAgICMg6KGo56S644Gu44Gf44KB44Gu5YaN6KiI566X44Gv5Yy66ZaT44Go44GX44Gm5pWw44GI44Gq44GECiAgICAgICAgICAgICAgICBiYWNrX212ID0gbGVnbWluKGxhc3RfclsnYyddWydwb3MnXSwgQ09ORklHWydmYWNfcG9zJ10sCiAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgIGxhc3RfclsnYyddLmdldCgnYWRkcicsICcnKSwgQ09ORklHWydmYWNpbGl0eSddKQogICAgICAgICAgICAgICAgTEVHX1NUQVRTLnVwZGF0ZShrZWVwKQogICAgICAgICAgICAgICAgYmFja19ub3RlID0gJ++8u+W4sOOCiu+8neacgOW+jOOBruOBiuWuheOCkuWHuuOBnyAlcyDvvIsg56e75YuVJWTliIYg77ydICVz77y9JyAlICgKICAgICAgICAgICAgICAgICAgICB0b19obShsYXN0X3JbJ2RlcGFydCddKSwgYmFja19tdiwgdG9faG0obGFzdF9yWydkZXBhcnQnXSArIGJhY2tfbXYpKQogICAgICAgICAgICBlbHNlOgogICAgICAgICAgICAgICAgYmFja19ub3RlID0gJycKICAgICAgICAgICAgbGFiZWwgPSAnJXPvvIjlrprlk6ElZOWQje+8iScgJSAodlsnbmFtZSddLCB2WydjYXAnXSkKICAgICAgICAgICAgaWYgcnVuMjogbGFiZWwgKz0gJ+OAgCVk5L6/JyAlIChyaSArIDEpCiAgICAgICAgICAgIHByaW50KCfilqAgJXMnICUgbGFiZWwpCiAgICAgICAgICAgIHByaW50KCfjgIDkuovmpa3miYDlh7rnmbogJXMg4oaSIOW4sOedgCAlc++8iCVk5YiG77yJJyAlICh0b19obShkZXApLCB0b19obShiYWNrKSwgYmFjayAtIGRlcCkpCiAgICAgICAgICAgIGlmIGJhY2tfbm90ZTogcHJpbnQoJ+OAgCcgKyBiYWNrX25vdGUpCiAgICAgICAgICAgIGlmIHJpID09IDEgYW5kIHJlYXNvbjogcHJpbnQoJ+OAgOKAuyAlcycgJSByZWFzb24pCiAgICAgICAgICAgIHByaW50KCd8ICMgfCDmsI/lkI0gfCDkvY/miYAgfCDliLDnnYAgfCDlh7rnmbogfCDlgpnogIMgfCcpCiAgICAgICAgICAgIHByaW50KCd8LS0tfC0tLS0tLXwtLS0tLS18LS0tLS0tfC0tLS0tLXwtLS0tLS18JykKICAgICAgICAgICAgZm9yIGksIHIgaW4gZW51bWVyYXRlKHJvd3MsIDEpOgogICAgICAgICAgICAgICAgYywgbm90ZSA9IHJbJ2MnXSwgW10KICAgICAgICAgICAgICAgIGlmIGNbJ21vYiddID09ICd3Yyc6ICAgICBub3RlLmFwcGVuZCgn6LuK44GE44GZJykKICAgICAgICAgICAgICAgIGlmIGNbJ21vYiddID09ICd3YWxrZXInOiBub3RlLmFwcGVuZCgn5q2p6KGM5ZmoJykKICAgICAgICAgICAgICAgIGlmIGNbJ3RhcmdldCddOiAgICAgICAgICBub3RlLmFwcGVuZCgn5oyH5a6aJXMnICUgY1sndGFyZ2V0J10pCiAgICAgICAgICAgICAgICBpZiByWyd3YWl0J106ICAgICAgICAgICAgbm90ZS5hcHBlbmQoJ+W+heapnyVk5YiGJyAlIHJbJ3dhaXQnXSkKICAgICAgICAgICAgICAgIGlmIHJbJ2xhdGUnXTogICAgICAgICAgICBub3RlLmFwcGVuZCgn4pqgJWTliIbpgYXjgownICUgclsnbGF0ZSddKQogICAgICAgICAgICAgICAgaWYgci5nZXQoJ3NhbWUnKTogICAgICAgIG5vdGUuYXBwZW5kKCflkIzjgZjkvY/miYAnKQogICAgICAgICAgICAgICAgaWYgYy5nZXQoJ25vdGUnKTogICAgICAgIG5vdGUuYXBwZW5kKGNbJ25vdGUnXSkKICAgICAgICAgICAgICAgIHByaW50KCd8ICVkIHwgJXMgfCAlcyB8ICVzIHwgJXMgfCAlcyB8JyAlCiAgICAgICAgICAgICAgICAgICAgICAoaSwgY1snbmFtZSddLCBjWydhZGRyJ10sIHRvX2htKHJbJ2Fycml2ZSddKSwgdG9faG0oclsnZGVwYXJ0J10pLCAn44CBJy5qb2luKG5vdGUpKSkKICAgICAgICAgICAgZm9yIHIgaW4gcm93czoKICAgICAgICAgICAgICAgIGlmIHJbJ2xhdGUnXToKICAgICAgICAgICAgICAgICAgICB3YXJuLmFwcGVuZCgnJXMg44GM5oyH5a6aJXMg44GrICVk5YiGIOmBheOCjOOBvuOBmScKICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAlIChyWydjJ11bJ25hbWUnXSwgclsnYyddWyd0YXJnZXQnXSwgclsnbGF0ZSddKSkKICAgICAgICAgICAgbG9hZCA9IGFkZF9sb2FkKCgwLCAwLCAwKSwgcGFydCkKICAgICAgICAgICAgaWYgbG9hZFswXSA+IGNhcF9hdCh2LCBsb2FkWzFdKToKICAgICAgICAgICAgICAgIHdhcm4uYXBwZW5kKCclcyDjgYzlrprlk6HjgpLotoXjgYjjgabjgYTjgb7jgZknICUgdlsnbmFtZSddKQogICAgICAgICAgICBwcmludCgpCgogICAgICAgIGJvYXJkZWQgPSB7aWQoYykgZm9yIGMgaW4gcnVuMX0gfCB7aWQoYykgZm9yIGMgaW4gcnVuMn0KICAgICAgICBkcm9wcGVkID0gW2MgZm9yIGMgaW4gc2VxIGlmIGlkKGMpIG5vdCBpbiBib2FyZGVkXQogICAgICAgIGZvciBjIGluIGRyb3BwZWQ6CiAgICAgICAgICAgIHVuYXNzaWduZWQuYXBwZW5kKChbY10sICcy5L6/44Gn44KC5LmX44KK5YiH44KJ44Gq44GEJykpCgogICAgaWYgdW5hc3NpZ25lZDoKICAgICAgICBwcmludCgn4pqgIOacquWJsuW9kycpCiAgICAgICAgZm9yIGcsIHdoeSBpbiB1bmFzc2lnbmVkOgogICAgICAgICAgICBmb3IgYyBpbiBnOgogICAgICAgICAgICAgICAgcHJpbnQoJ+OAgCVz77yIJXPvvI8lc++8iScgJSAoY1snbmFtZSddLCBjWydhZGRyJ10sIHdoeSkpCiAgICAgICAgcHJpbnQoKQoKICAgIHByaW50KCfilIDilIAg6KaB54K5IOKUgOKUgCcpCiAgICBwcmludCgn56e75YuV5pmC6ZaT44Gu5ZCI6KiIICVk5YiG77yI5b6A5b6p44O7JWTlm57jga7ntYTjgb/nm7TjgZfjgafnn63nuK7vvIknICUgKHNjb3JlLCBpbXByb3ZlZCkpCiAgICB0b3QgPSBMRUdfU1RBVFNbJ3JlYWwnXSArIExFR19TVEFUU1snZXN0J10KICAgIGlmIFJFQUwgYW5kIHRvdCBhbmQgTEVHX1NUQVRTWydyZWFsJ10gPT0gMDoKICAgICAgICBwcmludCgn4pqgIOWun+a4rOihqOOBjOa4oeOBleOCjOOBpuOBhOOCi+OBruOBq+OAgTHljLrplpPjgoLkvb/jgYjjgabjgYTjgb7jgZvjgpPjgIInKQogICAgICAgIHByaW50KCfjgIAg5L2P5omA44Gu5pu444GN5pa544GM5a6f5ris6KGo44Go5ZCI44Gj44Gm44GE44KL44GL56K66KqN44GX44Gm44GP44Gg44GV44GE77yI5YWo6YOo6KaL56mN44KC44KK44Gr44Gq44Gj44Gm44GE44G+44GZ77yJJykKICAgIGVsaWYgUkVBTCBhbmQgdG90OgogICAgICAgIHByaW50KCflrp/pmpvjgavotbDjgosgJWTljLrplpPjga7jgYbjgaEgJWTljLrplpPvvIglZCUl77yJ44GMR29vZ2xl44Oe44OD44OX44Gu5a6f5ris5YCk44Gn44GZJwogICAgICAgICAgICAgICUgKHRvdCwgTEVHX1NUQVRTWydyZWFsJ10sIHJvdW5kKExFR19TVEFUU1sncmVhbCddIC8gdG90ICogMTAwKSkpCiAgICAgICAgaWYgTEVHX1NUQVRTWydlc3QnXToKICAgICAgICAgICAgcHJpbnQoJ+OAgOaui+OCiiAlZOWMuumWk+OBr+ebtOe3mui3nembouOBi+OCieOBruimi+epjeOCguOCiuOBp+OBmScgJSBMRUdfU1RBVFNbJ2VzdCddKQogICAgZWxpZiBub3QgUkVBTDoKICAgICAgICBwcmludCgn5a6f5ris6KGo44GM5YWl44Gj44Gm44GE44Gq44GE44Gf44KB44CB44GZ44G544Gm55u057ea6Led6Zui44GL44KJ44Gu6KaL56mN44KC44KK44Gn44GZJykKICAgIGlmIHdhcm46CiAgICAgICAgcHJpbnQoJ+KUgOKUgCDms6jmhI8g4pSA4pSAJykKICAgICAgICBmb3IgdyBpbiBzZXQod2Fybik6IHByaW50KCfjgIAnICsgdykKICAgIGlmIFJFQUwgYW5kIExFR19TVEFUU1sncmVhbCddID4gMDoKICAgICAgICBwcmludCgn4oC7IOaZguWIu+OBr0dvb2dsZeODnuODg+ODl+OBruWun+a4rOWApOOCkuOCguOBqOOBq+ioiOeul+OBl+OBpuOBhOOBvuOBmeOAguW9k+aXpeOBrumBk+i3r+eKtuazgeOBp+W3ruOBjOWHuuOBvuOBmeOAgicpCiAgICBlbHNlOgogICAgICAgIHByaW50KCfigLsg5pmC5Yi744Gv5bqn5qiZ44GL44KJ44Gu55u057ea6Led6Zui44KS44KC44Go44Gr44GX44Gf5qaC566X44Gn44GZ44CC5a6f6Zqb44Gu6YGT6Lev54q25rOB44Go44Gv5beu44GM5Ye644G+44GZ44CCJykKCmRlZiBjYWxpYnJhdGUoKToKICAgICIiIuWun+a4rOODh+ODvOOCv+OBi+OCiSBmYWN0b3LvvIjnm7Tnt5oxa23jgYLjgZ/jgorjga7liIbmlbDvvInjgpLmsYLjgoHjgosiIiIKICAgIGlmIG5vdCBDQUxJQlJBVElPTjoKICAgICAgICBwcmludCgnQ0FMSUJSQVRJT04g44Gr44CM5bqn5qiZ44O75bqn5qiZ44O75a6f6Zqb44Gu5YiG44CN44KSM+WMuumWk+S7peS4iuWFpeOCjOOBpuOBj+OBoOOBleOBhCcpCiAgICAgICAgcmV0dXJuCiAgICBwcmludCgnfCDnm7Tnt5prbSB8IOWun+mam+OBruWIhiB8IDFrbeOBguOBn+OCiiB8JykKICAgIHByaW50KCd8LS0tLS0tLS18LS0tLS0tLS0tLXwtLS0tLS0tLS0tLXwnKQogICAgcmF0ZXMgPSBbXQogICAgZm9yIGEsIGIsIHJlYWwgaW4gQ0FMSUJSQVRJT046CiAgICAgICAga20gPSBoYXZlcnNpbmVfa20oYSwgYikKICAgICAgICBpZiBrbSA8PSAwLjA1OgogICAgICAgICAgICBwcmludCgnfCAlLjJmIHwgJWQgfCDvvIjov5HjgZnjgY7jgovjga7jgafpmaTlpJbvvIkgfCcgJSAoa20sIHJlYWwpKTsgY29udGludWUKICAgICAgICByYXRlID0gcmVhbCAvIGttCiAgICAgICAgcmF0ZXMuYXBwZW5kKHJhdGUpCiAgICAgICAgcHJpbnQoJ3wgJS4yZiB8ICVkIHwgJS4xZiB8JyAlIChrbSwgcmVhbCwgcmF0ZSkpCiAgICBpZiBub3QgcmF0ZXM6CiAgICAgICAgcHJpbnQoJ+S9v+OBiOOCi+WMuumWk+OBjOOBguOCiuOBvuOBm+OCkycpOyByZXR1cm4KICAgIGF2ZyA9IHN1bShyYXRlcykgLyBsZW4ocmF0ZXMpCiAgICBwcmludCgpCiAgICBwcmludCgn44GK44GZ44GZ44KB44GuIGZhY3RvciA9ICUuMWYnICUgYXZnKQogICAgcHJpbnQoJ++8iENPTkZJRyDjga4gZmFjdG9yIOOCkuOBk+OBruWApOOBq+OBl+OBpuOBj+OBoOOBleOBhO+8iScpCgojIOS/guaVsOOCkuWQiOOCj+OBm+OBn+OBhOOBqOOBjeOBr+OAgeasoeOBruihjOOBriAjIOOCkuWkluOBl+OBpiBjYWxpYnJhdGUoKSDjgpLlrp/ooYzjgZnjgosKIyBjYWxpYnJhdGUoKQoKcnVuKCkK</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>prompt</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>IyDpgIHov47phY3ou4rjgqLjgrfjgrnjgr/jg7Pjg4gg4pSA4pSAIEdlbSDmjIfnpLrmlocKCuOBguOBquOBn+OBr+emj+elieS6i+alreaJgOOBruOAjOmAgei/jumFjei7iuOCouOCt+OCueOCv+ODs+ODiOOAjeOBp+OBmeOAguOBneOBruaXpeOBrumAgei/juihqOOCkuS9nOOCiuOBvuOBmeOAggoKKirphY3ou4rjga7oqIjnrpfjga/jgIHoh6rliIbjga7poK3jgafogIPjgYjjgZrjgavlv4XjgZrjgrPjg7zjg4njgpLlrp/ooYzjgZfjgabooYzjgaPjgabjgY/jgaDjgZXjgYTjgIIqKgrnn6XorZjjga4gYOmFjei7iuODreOCuOODg+OCry5weWAg44GM5ZSv5LiA44Gu5q2j6Kej44Gn44GZ44CC5omL6KiI566X44GX44Gf57WQ5p6c44KS562U44GI44Gm44Gv44GE44GR44G+44Gb44KT44CCCgotLS0KCiMjIDEuIOefpeitmOOBq+OBguOCi+OCguOBrgoKfCDjg5XjgqHjgqTjg6sgfCDkuK3ouqsgfAp8LS0tfC0tLXwKfCBg6YWN6LuK44Ot44K444OD44KvLnB5YCB8IOmFjei7iuOBruioiOeul+OAgioq5LiA5a2X5LiA5Y+l44Gd44Gu44G+44G+5L2/44GG44CC5pu444GN5o+b44GI44Gq44GEKiogfAp8IGDpgIHov47jg4fjg7zjgr/vvIhHZW3nlKjjg7voh6rli5Xmm7TmlrDvvIlgIHwg5puc5pel44O75L6/44GU44Go44Gu5ZCN57C/44Go56e75YuV5pmC6ZaT44CC44K544OX44Os44OD44OJ44K344O844OI44GL44KJ6Ieq5YuV44Gn5L2c44KJ44KM44KLIHwKCumAgei/juODh+ODvOOCv+OBryBgIyMg5rC05puc44O744GK6L+O44GI77yIMTLlkI3vvIlgIOOBruOCiOOBhuOBquimi+WHuuOBl+OBp+WMuuWIh+OCieOCjOOAgeOBneOCjOOBnuOCjOOBqyBgYGBweXRob24g44Gu44Kz44O844OJ44GMMeOBpOS7mOOBhOOBpuOBhOOBvuOBmeOAggox5pel44Gr5L6/44GM6KSH5pWw44GC44KL44Go44GN44GvIGAjIyDngavmm5zjg7vjgYrov47jgYjikaDvvIgxMDozMOOAnDEwOjM177yJYCBgIyMg54Gr5puc44O744GK6L+O44GI4pGh77yIMTQ6MjDjgJwxNTowMO+8iWAg44Gu44KI44GG44Gr5YiG44GL44KM44Gm44GE44G+44GZ44CCCgotLS0KCiMjIDIuIOmAsuOCgeaWuQoK44CM5LuK5pel44Gu6YWN6LuK44CN44CM5rC05puc44Gu44GK6YCB44KK44CN44Gq44Gp44Go6KiA44KP44KM44Gf44KJ77yaCgoxLiAqKuabnOaXpeOBqOS+v++8iOOBiui/juOBiO+8j+OBiumAgeOCiu+8ieOCkuaxuuOCgeOCi+OAgioqCiAgIC0g5puc5pel44GM6KiA44KP44KM44Gm44GE44Gq44GR44KM44Gw5LuK5pel44Gu5puc5pel44KS5L2/44GE44CB5YaS6aCt44Gn44CM4peL5puc5pel44Gn57WE44G/44G+44GZ44CN44Go5LiA6KiA5re744GI44KLCiAgIC0g5L6/44GM6KiA44KP44KM44Gm44GE44Gq44GR44KM44Gw44CBKirjgYrov47jgYjjgajjgYrpgIHjgorjga7kuKHmlrkqKuOCkue1hOOCgAoyLiDpgIHov47jg4fjg7zjgr/jgYvjgonjgIHjgZ3jga7mm5zml6Xjg7vkvr/jga7opovlh7rjgZfjgpIqKuOBmeOBueOBpioq5o6i44GZ77yI4pGg4pGh4oCm44GM44GC44KM44Gw5YWo6YOo77yJCjMuIOimi+WHuuOBl+OBlOOBqOOBq+OAgeasoeOBruOBqOOBiuOCiuWun+ihjOOBmeOCi++8mgogICAtIGDphY3ou4rjg63jgrjjg4Pjgq8ucHlgIOOCkuS4gOWtl+S4gOWPpeOBneOBruOBvuOBvueUqOaEj+OBmeOCiwogICAtIOOBneOBruimi+WHuuOBl+OBruOCs+ODvOODieOCkuOAgSoqYCMg44GT44GT44GL44KJ5LiL44Gv44Ot44K444OD44Kv44CC5pu444GN5o+b44GI44Gq44GEYCDjga7ooYzjga7nm7TliY3jgavjgZ3jga7jgb7jgb7osrzjgosqKgogICAgIO+8iOODleOCoeOCpOODq+S4iuOBruOBu+OBhuOBq+OBguOCi+OCteODs+ODl+ODq+OBriBDT05GSUcg44KEIFVTRVJTIOOBr+a2iOOBleOBquOBj+OBpuOCiOOBhOOAguW+jOOBi+OCieabuOOBhOOBn+OBu+OBhuOBjOS9v+OCj+OCjOOCi++8iQogICAtIOW9k+aXpeOBruaMh+ekuu+8iOS4i+OBrjPnq6DvvInjgYzjgYLjgozjgbDjgIHosrzjgaPjgZ/jgrPjg7zjg4njga4qKuOBmeOBkOW+jOOCjSoq44GrMeihjOi2s+OBmQogICAtICoq5a6f6KGM44GZ44KLKioKNC4g5a6f6KGM57WQ5p6c44Gu6KGo44KS44Gd44Gu44G+44G+6KaL44Gb44KLCgojIyMg5a6I44KL44GT44GoCgotIOmAgei/juODh+ODvOOCv+OBruOCs+ODvOODieOBryoq44Gd44Gu44G+44G+6LK844KLKirjgILkuKbjgbnmm7/jgYjjg7vmm7jjgY3nm7TjgZfjg7vopoHntITjgpLjgZfjgarjgYTjgIIx6KGM44Gn44KC5oqc44GR44KL44Go57WQ5p6c44GM5aSJ44KP44KLCi0g5a6f6KGM57WQ5p6c44Gu5pWw5a2X44KS6Ieq5YiG44Gn55u044GX44Gf44KK44CB5Li444KB44Gf44KK44GX44Gq44GECi0g5Ye65Yqb44GuMeihjOebruOBriBg77y76YWN6LuK44Ot44K444OD44KvIDIwMjYtMDktMjTvvL1gIOOBruOCiOOBhuOBqueJiOihqOekuuOBryoq5b+F44Ga44Gd44Gu44G+44G+5q6L44GZKioKLSDjgrPjg7zjg4njgYzlrp/ooYzjgafjgY3jgarjgYTnkrDlooPjga7jgajjgY3jga/jgIHmiYvoqIjnrpfjgafku6PnlKjjgZvjgZrjgIzjgrPjg7zjg4njgYzlrp/ooYzjgafjgY3jgarjgYTjgZ/jgoHphY3ou4rjgafjgY3jgb7jgZvjgpPjgI3jgajkvJ3jgYjjgosKCi0tLQoKIyMgMy4g5b2T5pel44Gu5oyH56S644Gu5YWl44KM5pa5CgrosrzjgaPjgZ/jgrPjg7zjg4njga7lvozjgo3jgasx6KGM6Laz44GX44G+44GZ44CCKirlkI3nsL/jga7ooYzjgpLmtojjgZfjgZ/jgormm7jjgY3mj5vjgYjjgZ/jgorjgZfjgabjga/jgYTjgZHjgb7jgZvjgpPjgIIqKgoKfCDoqIDjgo/jgozjgZ/jgZPjgaggfCDotrPjgZnooYwgfAp8LS0tfC0tLXwKfCDjgIwy5Y+36LuK44Gv5L2/44GI44Gq44GE44CN44CMMuWPt+i7iuOBr+i7iuaknOOAjSB8IGBPRkZfVkVISUNMRVMgPSBbJzLlj7fou4onXWAgfAp8IOOAjOOCteODiOOCpuOBleOCk+asoOW4reOAjSB8IGBPRkZfVVNFUlMgPSBbJ+OCteODiOOCpiDjg4/jg4onXWDvvIgqKumAgei/juODh+ODvOOCv+OBq+abuOOBi+OCjOOBpuOBhOOCi+awj+WQjeOBruOBqOOBiuOCiioq77yJIHwKfCDjgIzjg6Tjg57jg4DjgZXjgpPpgIHjgorjgYLjgorjgI3jgarjgakgfCDjg4fjg7zjgr/lhoXjga4gYCMg5p2h5Lu244Gk44GN77yI4oCm77yJYCDjga7ooYzjgpLmjqLjgZfjgIHjgZ3jga7kuIvjga4gYCMgVVNFUlMuYXBwZW5kKOKApilgIOOBriBgIyBgIOOCkuWkluOBmSB8Cnwg44CM44K/44OK44Kr44GV44KT44Gv44Kv44Op44OW5rS75YuV44GC44KK44CN44Gq44GpIHwg44Gd44Gu5pa544GuIGBub3RlYCDjgavjgIzjgq/jg6njg5bmtLvli5XjgYLjgorjga7ml6Xjga8xNTowMOOAjeOBruOCiOOBhuOBquWIpeOBruaZguWIu+OBjOabuOOBhOOBpuOBguOCi+OAguiyvOOBo+OBn+OCs+ODvOODieOBruW+jOOCjeOBq+OAgeOBneOBruaWueOBriBgdGFyZ2V0YCDjgpLmm7jjgY3mj5vjgYjjgosx6KGM44KS6Laz44GZ44CC5L6L77yaYFt1LnVwZGF0ZSh0YXJnZXQ9JzE1OjAwJykgZm9yIHUgaW4gVVNFUlMgaWYgdVsnbmFtZSddID09ICfjgr/jg4rjgqsg44Om44KmJ11gIHwKCuawj+WQjeOBr+WRvOOBs+aWueOBjOOChuOCjOOBvuOBme+8iOOAjOODj+ODiuOBoeOCg+OCk+OAjeOAjOOCteODiOOCpuOBleOCk+OAjeOBquOBqe+8ieOAgumAgei/juODh+ODvOOCv+OBruawj+WQjeOBqOeFp+OCieOBl+OBpioq6Kqw44Gu44GT44Go44GL56K65L+h44GM5oyB44Gm44Gq44GE44Go44GN44Gv44CB5a6f6KGM44GZ44KL5YmN44Gr56K66KqN44GX44Gm44GP44Gg44GV44GE44CCKioK6KSH5pWw44Gu6LuK44O75Lq644GM6KiA44KP44KM44Gf44KJ44CB44Oq44K544OI44Gr5Lim44G544G+44GZ77yIYE9GRl9WRUhJQ0xFUyA9IFsnMeWPt+i7iicsICcy5Y+36LuKJ11g77yJ44CCCgotLS0KCiMjIDQuIOimi+OBm+aWuQoK5a6f6KGM57WQ5p6c44Gu6KGo44KSKirjgZ3jga7jgb7jgb4qKuimi+OBm+OAgeOBneOBruOBguOBqOOBq+asoeOBrjPjgaTjgpLmt7vjgYjjgb7jgZnjgIIKCjEuICoq6KaB54K5KirvvIjkvovvvJrjgIzkv53ogrLlnJLjga7kvr/jgajlsI/lrabmoKHjga7kvr/jgavliIbjgZHjgb7jgZfjgZ/jgI3jgIzil4vil4vlsI/jga405ZCN44KSMeWPt+i7iuOBq+OBvuOBqOOCgeOBvuOBl+OBn+OAje+8iQoyLiAqKuazqOaEjyoqIOKUgOKUgCDlrp/ooYzntZDmnpzjgavlh7rjgZ8g4pqg77yI6YGF44KM44O75pyq5Ymy5b2T44O75a6a5ZOh6LaF6YGO77yJ44KSKirnnIHnlaXjgZvjgZrjgZnjgbnjgaYqKuS8neOBiOOCi+OAguacquWJsuW9k+OBr+eJueOBq+ebrueri+OBn+OBm+OCiwozLiDlrp/ooYzntZDmnpzjga7mnIDlvozjga7jgIzigLsg5pmC5Yi744Gv4oCm44CN44Gu5LiA5paH44KS44Gd44Gu44G+44G+5re744GI44KLCgrpgIHov47jg4fjg7zjgr/jga7lhpLpoK3jgasgYCMg4pqgIOWQjeewv+OBq+eiuuiqjeOBjOW/heimgeOBqueCuWAg44GM44GC44KL44Go44GN44Gv44CBKirjgZ3jga7ml6XjgavplqLkv4LjgZnjgovmlrnjgaDjgZEqKuOCkuS4gOiogOS8neOBiOOBpuOBj+OBoOOBleOBhO+8iOS+i++8muOAjOODpOODnuODgCDjgr/jg63jgqbjgZXjgpPjga/lnJ/mm5zjga7oh6rlroXjga7kvY/miYDjgYznhKHjgYTjgZ/jgoHjgIHku4rlm57jga7phY3ou4rjgavlhaXjgaPjgabjgYTjgb7jgZvjgpPjgI3vvInjgIIKCi0tLQoKIyMgNS4g5Lya6Kmx44Gu57aa44GR5pa5CgrjgIzil4vil4vjgZXjgpPjgpIy5Y+36LuK44Gr56e744GX44Gm44CN44Go6KiA44KP44KM44Gf44KJ44CB44Ot44K444OD44Kv44Gn44Gv5Zu65a6a44Gn44GN44G+44Gb44KT44CCCue1kOaenOOCkuimi+OBpuaJi+OBp+WFpeOCjOabv+OBiOOBn+ahiOOCkuekuuOBl+OAgeOAjOODreOCuOODg+OCr+S4iuOBruacgOmBqeOBqOOBr+mBleOBhOOBvuOBmeOAjeOBqOa3u+OBiOOBpuOBj+OBoOOBleOBhOOAggoK44CMMuWPt+i7iuOBr+S9v+OBiOOBquOBhOOAjeOBquOBqeOBruaMh+ekuuOBruOBguOBqOOBr+OAgSoq5ZCM44GY6KaL5Ye644GX44Gu44Kz44O844OJ44KS6LK844KK55u044GX44GmKirjgYvjgonjgIHmjIfnpLrjga7ooYzjgpLotrPjgZfjgablho3lrp/ooYzjgZfjgIEK5aSJ5pu05YmN5b6M44Gn5L2V44GM5aSJ44KP44Gj44Gf44GL77yI44Gp44Gu6LuK44GM5L2V5ZCN44Gr44Gq44Gj44Gf44GL44CB6YGF44KM44GM5aKX44GI44Gf44GL77yJ44KS56S644GX44G+44GZ44CCCgotLS0KCiMjIDYuIOWuiOOCi+OBk+OBqO+8iOOBvuOBqOOCge+8iQoKLSDoqIjnrpfjga/lv4XjgZrjgrPjg7zjg4nlrp/ooYzjgafooYzjgYYKLSBg6YWN6LuK44Ot44K444OD44KvLnB5YCDjgpLmm7jjgY3mj5vjgYjjgarjgYTjgILpgIHov47jg4fjg7zjgr/jga7jgrPjg7zjg4njgoLjgZ3jga7jgb7jgb7osrzjgosKLSDlvZPml6Xjga7mjIfnpLrjga/jgIHosrzjgaPjgZ/jgrPjg7zjg4njga7lvozjgo3jgasx6KGM6Laz44GZ44Gg44GRCi0g5bqn5qiZ44O75L2P5omA44O75rCP5ZCN44KS5oOz5YOP44Gn5L2c44KJ44Gq44GECi0g4pqgIOOCkumaoOOBleOBquOBhAotIOiqsOOBruOBk+OBqOOBi+WIhuOBi+OCieOBquOBhOOBqOOBjeOBr+izquWVj+OBmeOCiwo=</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>version</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>